--- a/estimates_PS2025.xlsx
+++ b/estimates_PS2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\GitHub\tibor-pal.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BBB578-BA65-4B83-B9DB-95B32750B851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F2597C-608C-4CED-8C74-F252BECE5AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{898E4DB8-E74C-49BD-9493-76D0D230C2FB}"/>
   </bookViews>
@@ -505,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9DA81B-324A-4AF1-9159-7E70301473AF}">
-  <dimension ref="A1:T261"/>
+  <dimension ref="A1:T262"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -585,10 +585,10 @@
         <v>22282</v>
       </c>
       <c r="B2" s="5">
-        <v>5.0032769443196701</v>
+        <v>5.1830044703354998</v>
       </c>
       <c r="C2" s="5">
-        <v>3.9738914279499302</v>
+        <v>3.86749687579188</v>
       </c>
       <c r="D2" s="6">
         <v>3.8251154304433501</v>
@@ -597,16 +597,16 @@
         <v>5.1248381323175201</v>
       </c>
       <c r="F2" s="6">
-        <v>-2.2562377838112302</v>
+        <v>-2.6655642517861202</v>
       </c>
       <c r="G2" s="6">
-        <v>-0.145865049036527</v>
+        <v>-0.14722049490341499</v>
       </c>
       <c r="H2" s="6">
         <v>4.0038986779857198E-2</v>
       </c>
       <c r="I2" s="6">
-        <v>0.69210903033645699</v>
+        <v>0.72748509218064705</v>
       </c>
       <c r="J2" s="6">
         <v>4.9636142428236302E-2</v>
@@ -647,10 +647,10 @@
         <v>22372</v>
       </c>
       <c r="B3" s="5">
-        <v>5.2922385011052002</v>
+        <v>5.44477562777291</v>
       </c>
       <c r="C3" s="5">
-        <v>3.9526792146885801</v>
+        <v>3.8545806412723098</v>
       </c>
       <c r="D3" s="6">
         <v>3.8153533955324601</v>
@@ -659,16 +659,16 @@
         <v>5.3632765567691596</v>
       </c>
       <c r="F3" s="6">
-        <v>-1.8054543854837599</v>
+        <v>-2.4116945325656598</v>
       </c>
       <c r="G3" s="6">
-        <v>-0.147623369912528</v>
+        <v>-0.14838994609481099</v>
       </c>
       <c r="H3" s="6">
         <v>3.98916450777132E-2</v>
       </c>
       <c r="I3" s="6">
-        <v>0.66293523438315005</v>
+        <v>0.69743172723911095</v>
       </c>
       <c r="J3" s="6">
         <v>0.24794565180323999</v>
@@ -709,10 +709,10 @@
         <v>22463</v>
       </c>
       <c r="B4" s="6">
-        <v>5.1199106343731904</v>
+        <v>5.2092234543861897</v>
       </c>
       <c r="C4" s="6">
-        <v>3.9239431257527002</v>
+        <v>3.8378936177853902</v>
       </c>
       <c r="D4" s="6">
         <v>3.80269375142425</v>
@@ -721,16 +721,16 @@
         <v>5.1676419373056799</v>
       </c>
       <c r="F4" s="6">
-        <v>-1.02392600136386</v>
+        <v>-1.6659164690089501</v>
       </c>
       <c r="G4" s="6">
-        <v>-0.132026250195975</v>
+        <v>-0.13673947326681901</v>
       </c>
       <c r="H4" s="6">
         <v>3.97146429777262E-2</v>
       </c>
       <c r="I4" s="6">
-        <v>0.65435240781178805</v>
+        <v>0.68540873702632998</v>
       </c>
       <c r="J4" s="6">
         <v>0.63130038444588499</v>
@@ -771,10 +771,10 @@
         <v>22555</v>
       </c>
       <c r="B5" s="6">
-        <v>4.97883182521519</v>
+        <v>4.9857469180148701</v>
       </c>
       <c r="C5" s="6">
-        <v>3.88850235354424</v>
+        <v>3.8191888436606098</v>
       </c>
       <c r="D5" s="6">
         <v>3.7883533754065701</v>
@@ -783,16 +783,16 @@
         <v>4.9813633649710001</v>
       </c>
       <c r="F5" s="6">
-        <v>-0.19694052640301199</v>
+        <v>-0.83333021439307198</v>
       </c>
       <c r="G5" s="6">
-        <v>-0.117065308066946</v>
+        <v>-0.124593537500531</v>
       </c>
       <c r="H5" s="6">
         <v>3.9813716405990601E-2</v>
       </c>
       <c r="I5" s="6">
-        <v>0.63506498279657797</v>
+        <v>0.66519285847445098</v>
       </c>
       <c r="J5" s="6">
         <v>1.1198969572927899E-2</v>
@@ -833,10 +833,10 @@
         <v>22647</v>
       </c>
       <c r="B6" s="6">
-        <v>4.74657073514493</v>
+        <v>4.7275267928834896</v>
       </c>
       <c r="C6" s="6">
-        <v>3.85062755423909</v>
+        <v>3.80138825880791</v>
       </c>
       <c r="D6" s="6">
         <v>3.7744243800671602</v>
@@ -845,16 +845,16 @@
         <v>4.7432712465264801</v>
       </c>
       <c r="F6" s="6">
-        <v>0.60818127158620405</v>
+        <v>3.28764896989924E-2</v>
       </c>
       <c r="G6" s="6">
-        <v>-9.8870690143809503E-2</v>
+        <v>-0.11154994414618299</v>
       </c>
       <c r="H6" s="6">
         <v>3.9762288557270702E-2</v>
       </c>
       <c r="I6" s="6">
-        <v>0.61832276339852899</v>
+        <v>0.64729463816877197</v>
       </c>
       <c r="J6" s="6">
         <v>0.41121890667181399</v>
@@ -895,10 +895,10 @@
         <v>22737</v>
       </c>
       <c r="B7" s="6">
-        <v>4.0325915739270499</v>
+        <v>4.1520152910928996</v>
       </c>
       <c r="C7" s="6">
-        <v>3.84241446717667</v>
+        <v>3.7923784037146602</v>
       </c>
       <c r="D7" s="6">
         <v>3.7664865050965499</v>
@@ -907,16 +907,16 @@
         <v>4.2033929249041204</v>
       </c>
       <c r="F7" s="6">
-        <v>0.94049064715733299</v>
+        <v>0.655386882711809</v>
       </c>
       <c r="G7" s="6">
-        <v>-6.3003251197854104E-2</v>
+        <v>-8.7512215143419406E-2</v>
       </c>
       <c r="H7" s="6">
         <v>3.9760494105272701E-2</v>
       </c>
       <c r="I7" s="6">
-        <v>0.58675189648473103</v>
+        <v>0.61437867992536599</v>
       </c>
       <c r="J7" s="6">
         <v>0.39471918010089002</v>
@@ -957,10 +957,10 @@
         <v>22828</v>
       </c>
       <c r="B8" s="6">
-        <v>4.0336424329820799</v>
+        <v>4.1219919924017798</v>
       </c>
       <c r="C8" s="6">
-        <v>3.8334858980305402</v>
+        <v>3.7840013784787501</v>
       </c>
       <c r="D8" s="6">
         <v>3.7588504138316501</v>
@@ -969,16 +969,16 @@
         <v>4.1722014873166797</v>
       </c>
       <c r="F8" s="6">
-        <v>1.24574963717208</v>
+        <v>0.96595090950097495</v>
       </c>
       <c r="G8" s="6">
-        <v>-6.3129312778787805E-2</v>
+        <v>-8.6471938116868402E-2</v>
       </c>
       <c r="H8" s="6">
         <v>3.9730993844109198E-2</v>
       </c>
       <c r="I8" s="6">
-        <v>0.563116259499712</v>
+        <v>0.58949611293979198</v>
       </c>
       <c r="J8" s="6">
         <v>0.32139411627694398</v>
@@ -1019,10 +1019,10 @@
         <v>22920</v>
       </c>
       <c r="B9" s="6">
-        <v>3.92646749759923</v>
+        <v>3.9305759670735498</v>
       </c>
       <c r="C9" s="6">
-        <v>3.83180708978671</v>
+        <v>3.7801184195528599</v>
       </c>
       <c r="D9" s="6">
         <v>3.75512458842418</v>
@@ -1031,16 +1031,16 @@
         <v>3.9556072573583321</v>
       </c>
       <c r="F9" s="6">
-        <v>1.0022523282909199</v>
+        <v>0.80289239433534498</v>
       </c>
       <c r="G9" s="6">
-        <v>-5.8955760029506803E-2</v>
+        <v>-7.8987990476890105E-2</v>
       </c>
       <c r="H9" s="6">
         <v>3.9626157456553901E-2</v>
       </c>
       <c r="I9" s="6">
-        <v>0.58080797101590897</v>
+        <v>0.60510888200338797</v>
       </c>
       <c r="J9" s="6">
         <v>-0.22749143333431801</v>
@@ -1081,10 +1081,10 @@
         <v>23012</v>
       </c>
       <c r="B10" s="6">
-        <v>3.9355101941580601</v>
+        <v>3.9272881922395002</v>
       </c>
       <c r="C10" s="6">
-        <v>3.8294780719060602</v>
+        <v>3.7760208993511499</v>
       </c>
       <c r="D10" s="6">
         <v>3.7512292668361198</v>
@@ -1093,16 +1093,16 @@
         <v>3.9423144031087962</v>
       </c>
       <c r="F10" s="6">
-        <v>1.17227990562412</v>
+        <v>0.95489851534284798</v>
       </c>
       <c r="G10" s="6">
-        <v>-5.9497708338692501E-2</v>
+        <v>-7.9042302123460806E-2</v>
       </c>
       <c r="H10" s="6">
         <v>3.9656903718199903E-2</v>
       </c>
       <c r="I10" s="6">
-        <v>0.56106761136702299</v>
+        <v>0.58499748136947305</v>
       </c>
       <c r="J10" s="6">
         <v>0.25103991152670702</v>
@@ -1143,10 +1143,10 @@
         <v>23102</v>
       </c>
       <c r="B11" s="6">
-        <v>3.92902374185863</v>
+        <v>3.9144182930492901</v>
       </c>
       <c r="C11" s="6">
-        <v>3.8290282226150998</v>
+        <v>3.7717040201913599</v>
       </c>
       <c r="D11" s="6">
         <v>3.7471036722618001</v>
@@ -1155,16 +1155,16 @@
         <v>3.9172591913289359</v>
       </c>
       <c r="F11" s="6">
-        <v>1.38923029253357</v>
+        <v>1.1692506553937401</v>
       </c>
       <c r="G11" s="6">
-        <v>-5.94755409250491E-2</v>
+        <v>-7.8680158104848699E-2</v>
       </c>
       <c r="H11" s="6">
         <v>3.96840639471936E-2</v>
       </c>
       <c r="I11" s="6">
-        <v>0.54279487334578702</v>
+        <v>0.56494569564362895</v>
       </c>
       <c r="J11" s="6">
         <v>0.46806024010118202</v>
@@ -1205,10 +1205,10 @@
         <v>23193</v>
       </c>
       <c r="B12" s="6">
-        <v>4.2543898718990896</v>
+        <v>4.1423486055082002</v>
       </c>
       <c r="C12" s="6">
-        <v>3.8075829956090601</v>
+        <v>3.76077933283905</v>
       </c>
       <c r="D12" s="6">
         <v>3.7375968243539499</v>
@@ -1217,16 +1217,16 @@
         <v>4.1784819088086804</v>
       </c>
       <c r="F12" s="6">
-        <v>2.1028214763542201</v>
+        <v>1.6537306883260501</v>
       </c>
       <c r="G12" s="6">
-        <v>-7.0049734085150195E-2</v>
+        <v>-8.6713395592713405E-2</v>
       </c>
       <c r="H12" s="6">
         <v>3.9697075264022399E-2</v>
       </c>
       <c r="I12" s="6">
-        <v>0.52471971416663798</v>
+        <v>0.545025602989334</v>
       </c>
       <c r="J12" s="6">
         <v>0.54423216388354101</v>
@@ -1267,10 +1267,10 @@
         <v>23285</v>
       </c>
       <c r="B13" s="6">
-        <v>4.15991699106692</v>
+        <v>4.0198796917545998</v>
       </c>
       <c r="C13" s="6">
-        <v>3.7905386840116102</v>
+        <v>3.7526741584656</v>
       </c>
       <c r="D13" s="6">
         <v>3.7303337679369899</v>
@@ -1279,16 +1279,16 @@
         <v>4.0236936219021597</v>
       </c>
       <c r="F13" s="6">
-        <v>2.35833724654572</v>
+        <v>2.0558104579569099</v>
       </c>
       <c r="G13" s="6">
-        <v>-6.6951334991989006E-2</v>
+        <v>-8.1750642800712994E-2</v>
       </c>
       <c r="H13" s="6">
         <v>3.9880689680378799E-2</v>
       </c>
       <c r="I13" s="6">
-        <v>0.53621839890787504</v>
+        <v>0.55195612467643995</v>
       </c>
       <c r="J13" s="6">
         <v>0.87205378977058701</v>
@@ -1329,10 +1329,10 @@
         <v>23377</v>
       </c>
       <c r="B14" s="6">
-        <v>4.2639347101393801</v>
+        <v>4.14096397712445</v>
       </c>
       <c r="C14" s="6">
-        <v>3.7670296284723999</v>
+        <v>3.7408335895248399</v>
       </c>
       <c r="D14" s="6">
         <v>3.7199606041948199</v>
@@ -1341,16 +1341,16 @@
         <v>4.1634875102150799</v>
       </c>
       <c r="F14" s="6">
-        <v>2.9225429528641498</v>
+        <v>2.4221219889010399</v>
       </c>
       <c r="G14" s="6">
-        <v>-7.0448602222022205E-2</v>
+        <v>-8.6058093178012995E-2</v>
       </c>
       <c r="H14" s="6">
         <v>3.9804988468630897E-2</v>
       </c>
       <c r="I14" s="6">
-        <v>0.51707007328886301</v>
+        <v>0.53414887807762801</v>
       </c>
       <c r="J14" s="6">
         <v>0.78669441133018003</v>
@@ -1391,10 +1391,10 @@
         <v>23468</v>
       </c>
       <c r="B15" s="6">
-        <v>4.2357869274758704</v>
+        <v>4.0968298457067096</v>
       </c>
       <c r="C15" s="6">
-        <v>3.7457282615995799</v>
+        <v>3.72987433169674</v>
       </c>
       <c r="D15" s="6">
         <v>3.7103386107384302</v>
@@ -1403,16 +1403,16 @@
         <v>4.1337332105597202</v>
       </c>
       <c r="F15" s="6">
-        <v>2.9753829986134401</v>
+        <v>2.5310767323898098</v>
       </c>
       <c r="G15" s="6">
-        <v>-6.8434429193540799E-2</v>
+        <v>-8.4085998940488502E-2</v>
       </c>
       <c r="H15" s="6">
         <v>3.9475776211299503E-2</v>
       </c>
       <c r="I15" s="6">
-        <v>0.54086613663391003</v>
+        <v>0.56055606123891399</v>
       </c>
       <c r="J15" s="6">
         <v>0.25672220362745402</v>
@@ -1453,10 +1453,10 @@
         <v>23559</v>
       </c>
       <c r="B16" s="6">
-        <v>4.2988227037913003</v>
+        <v>4.1412895751973799</v>
       </c>
       <c r="C16" s="6">
-        <v>3.7199971287170701</v>
+        <v>3.7173577456831599</v>
       </c>
       <c r="D16" s="6">
         <v>3.6994235252127901</v>
@@ -1465,16 +1465,16 @@
         <v>4.1958055151652403</v>
       </c>
       <c r="F16" s="6">
-        <v>3.2215700762786201</v>
+        <v>2.7196227154503299</v>
       </c>
       <c r="G16" s="6">
-        <v>-7.0290432794605798E-2</v>
+        <v>-8.6035526201963697E-2</v>
       </c>
       <c r="H16" s="6">
         <v>3.92773391320742E-2</v>
       </c>
       <c r="I16" s="6">
-        <v>0.53753819356559296</v>
+        <v>0.55734622196208194</v>
       </c>
       <c r="J16" s="6">
         <v>0.22413123042560801</v>
@@ -1515,10 +1515,10 @@
         <v>23651</v>
       </c>
       <c r="B17" s="6">
-        <v>4.0321896374022801</v>
+        <v>3.93627911354025</v>
       </c>
       <c r="C17" s="6">
-        <v>3.7094102869615</v>
+        <v>3.7102995653236501</v>
       </c>
       <c r="D17" s="6">
         <v>3.6929948927460199</v>
@@ -1527,16 +1527,16 @@
         <v>3.981435275820568</v>
       </c>
       <c r="F17" s="6">
-        <v>2.9850892674615501</v>
+        <v>2.7084070007133501</v>
       </c>
       <c r="G17" s="6">
-        <v>-6.0329714277546999E-2</v>
+        <v>-7.7204494024854006E-2</v>
       </c>
       <c r="H17" s="6">
         <v>3.9044937638487702E-2</v>
       </c>
       <c r="I17" s="6">
-        <v>0.53579539532440701</v>
+        <v>0.55531741611688101</v>
       </c>
       <c r="J17" s="6">
         <v>3.3418497924465503E-2</v>
@@ -1577,10 +1577,10 @@
         <v>23743</v>
       </c>
       <c r="B18" s="6">
-        <v>4.1747677019138996</v>
+        <v>4.1038098634698699</v>
       </c>
       <c r="C18" s="6">
-        <v>3.69008637026251</v>
+        <v>3.6973943403017202</v>
       </c>
       <c r="D18" s="6">
         <v>3.6821716902133499</v>
@@ -1589,16 +1589,16 @@
         <v>4.1435412870560402</v>
       </c>
       <c r="F18" s="6">
-        <v>3.5841883644405401</v>
+        <v>3.0324862101526802</v>
       </c>
       <c r="G18" s="6">
-        <v>-6.3867636747810402E-2</v>
+        <v>-8.2462537537732999E-2</v>
       </c>
       <c r="H18" s="6">
         <v>3.91572243973883E-2</v>
       </c>
       <c r="I18" s="6">
-        <v>0.52496319132908098</v>
+        <v>0.54289355975822695</v>
       </c>
       <c r="J18" s="6">
         <v>0.63721798935536</v>
@@ -1639,10 +1639,10 @@
         <v>23833</v>
       </c>
       <c r="B19" s="6">
-        <v>4.1711864221664001</v>
+        <v>4.0981220454094798</v>
       </c>
       <c r="C19" s="6">
-        <v>3.6721449049733499</v>
+        <v>3.6840518506297202</v>
       </c>
       <c r="D19" s="6">
         <v>3.6713406133110298</v>
@@ -1651,16 +1651,16 @@
         <v>4.1448829327069596</v>
       </c>
       <c r="F19" s="6">
-        <v>3.7883140746029702</v>
+        <v>3.2158817543023601</v>
       </c>
       <c r="G19" s="6">
-        <v>-6.3779473168594794E-2</v>
+        <v>-8.2459889975611697E-2</v>
       </c>
       <c r="H19" s="6">
         <v>3.90079117217315E-2</v>
       </c>
       <c r="I19" s="6">
-        <v>0.51074203531824403</v>
+        <v>0.53011838803859601</v>
       </c>
       <c r="J19" s="6">
         <v>0.36458738522272999</v>
@@ -1701,10 +1701,10 @@
         <v>23924</v>
       </c>
       <c r="B20" s="6">
-        <v>4.2806982618140603</v>
+        <v>4.1982375944596999</v>
       </c>
       <c r="C20" s="6">
-        <v>3.6490017587618002</v>
+        <v>3.6667865136373501</v>
       </c>
       <c r="D20" s="6">
         <v>3.65683849502182</v>
@@ -1713,16 +1713,16 @@
         <v>4.26642177392824</v>
       </c>
       <c r="F20" s="6">
-        <v>4.3497583404603697</v>
+        <v>3.6534330357322902</v>
       </c>
       <c r="G20" s="6">
-        <v>-6.5758593979604402E-2</v>
+        <v>-8.5136797591529603E-2</v>
       </c>
       <c r="H20" s="6">
         <v>3.8906912559505999E-2</v>
       </c>
       <c r="I20" s="6">
-        <v>0.49575989302084</v>
+        <v>0.51536085150372501</v>
       </c>
       <c r="J20" s="6">
         <v>0.42746122672248998</v>
@@ -1763,10 +1763,10 @@
         <v>24016</v>
       </c>
       <c r="B21" s="6">
-        <v>4.3838041406330497</v>
+        <v>4.29241666724712</v>
       </c>
       <c r="C21" s="6">
-        <v>3.6205049389490198</v>
+        <v>3.6457259686585699</v>
       </c>
       <c r="D21" s="6">
         <v>3.6388893659815702</v>
@@ -1775,16 +1775,16 @@
         <v>4.3780585766290399</v>
       </c>
       <c r="F21" s="6">
-        <v>5.0369113768587699</v>
+        <v>4.1606714906450897</v>
       </c>
       <c r="G21" s="6">
-        <v>-6.7864788032280104E-2</v>
+        <v>-8.8007412478209895E-2</v>
       </c>
       <c r="H21" s="6">
         <v>3.8855155381478601E-2</v>
       </c>
       <c r="I21" s="6">
-        <v>0.48146022061473998</v>
+        <v>0.50074598771920997</v>
       </c>
       <c r="J21" s="6">
         <v>0.49827602486491801</v>
@@ -1825,10 +1825,10 @@
         <v>24108</v>
       </c>
       <c r="B22" s="6">
-        <v>4.4876057047127</v>
+        <v>4.4046769511908499</v>
       </c>
       <c r="C22" s="6">
-        <v>3.5840581186837301</v>
+        <v>3.6209563474836202</v>
       </c>
       <c r="D22" s="6">
         <v>3.6177270186993602</v>
@@ -1837,16 +1837,16 @@
         <v>4.4762535007984798</v>
       </c>
       <c r="F22" s="6">
-        <v>6.1400864922615597</v>
+        <v>4.9672699131175504</v>
       </c>
       <c r="G22" s="6">
-        <v>-7.0825962382188704E-2</v>
+        <v>-9.1782309684448601E-2</v>
       </c>
       <c r="H22" s="6">
         <v>3.9233360120331601E-2</v>
       </c>
       <c r="I22" s="6">
-        <v>0.50366805977410201</v>
+        <v>0.52067225389064598</v>
       </c>
       <c r="J22" s="6">
         <v>1.6218662422210599</v>
@@ -1887,10 +1887,10 @@
         <v>24198</v>
       </c>
       <c r="B23" s="6">
-        <v>4.2517804487591597</v>
+        <v>4.2995820610616704</v>
       </c>
       <c r="C23" s="6">
-        <v>3.5550298318873601</v>
+        <v>3.5990668613836201</v>
       </c>
       <c r="D23" s="6">
         <v>3.5988343483929501</v>
@@ -1899,16 +1899,16 @@
         <v>4.2988981841385598</v>
       </c>
       <c r="F23" s="6">
-        <v>6.9954354582176297</v>
+        <v>5.7153783064972004</v>
       </c>
       <c r="G23" s="6">
-        <v>-6.7002606461104897E-2</v>
+        <v>-8.7584002660662297E-2</v>
       </c>
       <c r="H23" s="6">
         <v>4.0449754319989303E-2</v>
       </c>
       <c r="I23" s="6">
-        <v>0.77191766862795297</v>
+        <v>0.78097744130033997</v>
       </c>
       <c r="J23" s="6">
         <v>2.51486401335027</v>
@@ -1949,10 +1949,10 @@
         <v>24289</v>
       </c>
       <c r="B24" s="6">
-        <v>4.2387447090384098</v>
+        <v>4.2921059459400999</v>
       </c>
       <c r="C24" s="6">
-        <v>3.52528890101321</v>
+        <v>3.57685763889224</v>
       </c>
       <c r="D24" s="6">
         <v>3.5795823284191601</v>
@@ -1961,16 +1961,16 @@
         <v>4.2820750374378003</v>
       </c>
       <c r="F24" s="6">
-        <v>6.9315575890372001</v>
+        <v>5.6771498069386999</v>
       </c>
       <c r="G24" s="6">
-        <v>-6.70057773539285E-2</v>
+        <v>-8.7341529048448399E-2</v>
       </c>
       <c r="H24" s="6">
         <v>4.0637075046256903E-2</v>
       </c>
       <c r="I24" s="6">
-        <v>0.73479028740605801</v>
+        <v>0.74368168199213203</v>
       </c>
       <c r="J24" s="6">
         <v>2.3495652623784702</v>
@@ -2011,10 +2011,10 @@
         <v>24381</v>
       </c>
       <c r="B25" s="6">
-        <v>4.2224302502896904</v>
+        <v>4.2865189993624204</v>
       </c>
       <c r="C25" s="6">
-        <v>3.49446513160211</v>
+        <v>3.5541114909141802</v>
       </c>
       <c r="D25" s="6">
         <v>3.5597926764037999</v>
@@ -2023,16 +2023,16 @@
         <v>4.2673126419361997</v>
       </c>
       <c r="F25" s="6">
-        <v>6.8517130577661796</v>
+        <v>5.5731081243142198</v>
       </c>
       <c r="G25" s="6">
-        <v>-6.6803354111596797E-2</v>
+        <v>-8.7057192372582304E-2</v>
       </c>
       <c r="H25" s="6">
         <v>4.0792947968521599E-2</v>
       </c>
       <c r="I25" s="6">
-        <v>0.69556544179029201</v>
+        <v>0.70606925438092205</v>
       </c>
       <c r="J25" s="6">
         <v>2.6284537599339899</v>
@@ -2073,10 +2073,10 @@
         <v>24473</v>
       </c>
       <c r="B26" s="6">
-        <v>4.2526780574630001</v>
+        <v>4.2759846248102802</v>
       </c>
       <c r="C26" s="6">
-        <v>3.4606745332976998</v>
+        <v>3.5305703868559202</v>
       </c>
       <c r="D26" s="6">
         <v>3.5392884496314401</v>
@@ -2085,16 +2085,16 @@
         <v>4.2948480732714804</v>
       </c>
       <c r="F26" s="6">
-        <v>5.9820834566940597</v>
+        <v>4.9913502822815898</v>
       </c>
       <c r="G26" s="6">
-        <v>-6.6587361351895705E-2</v>
+        <v>-8.7002690743751096E-2</v>
       </c>
       <c r="H26" s="6">
         <v>4.0223488867603997E-2</v>
       </c>
       <c r="I26" s="6">
-        <v>0.810388563055363</v>
+        <v>0.82045340403363798</v>
       </c>
       <c r="J26" s="6">
         <v>1.4712613659173801</v>
@@ -2135,10 +2135,10 @@
         <v>24563</v>
       </c>
       <c r="B27" s="6">
-        <v>3.9596829414144499</v>
+        <v>4.1014473545071599</v>
       </c>
       <c r="C27" s="6">
-        <v>3.4406384102293002</v>
+        <v>3.5117357924228099</v>
       </c>
       <c r="D27" s="6">
         <v>3.5226265526394398</v>
@@ -2147,16 +2147,16 @@
         <v>4.1183794697008</v>
       </c>
       <c r="F27" s="6">
-        <v>5.7105068637101803</v>
+        <v>4.8192601486933899</v>
       </c>
       <c r="G27" s="6">
-        <v>-5.8472561062394297E-2</v>
+        <v>-7.7965674627638704E-2</v>
       </c>
       <c r="H27" s="6">
         <v>4.0165154962069897E-2</v>
       </c>
       <c r="I27" s="6">
-        <v>0.75216670016750498</v>
+        <v>0.76134101072141103</v>
       </c>
       <c r="J27" s="6">
         <v>1.88300536490722</v>
@@ -2197,10 +2197,10 @@
         <v>24654</v>
       </c>
       <c r="B28" s="6">
-        <v>3.99271656311657</v>
+        <v>4.1281582912622001</v>
       </c>
       <c r="C28" s="6">
-        <v>3.4177256497989998</v>
+        <v>3.4913563848751301</v>
       </c>
       <c r="D28" s="6">
         <v>3.5048448441184998</v>
@@ -2209,16 +2209,16 @@
         <v>4.1268348431410002</v>
       </c>
       <c r="F28" s="6">
-        <v>5.7315147340075301</v>
+        <v>4.7502358054953202</v>
       </c>
       <c r="G28" s="6">
-        <v>-5.9854895546286202E-2</v>
+        <v>-7.9315321639483002E-2</v>
       </c>
       <c r="H28" s="6">
         <v>4.0365423878773302E-2</v>
       </c>
       <c r="I28" s="6">
-        <v>0.72594973256789297</v>
+        <v>0.74107570828667602</v>
       </c>
       <c r="J28" s="6">
         <v>2.7956881612656299</v>
@@ -2259,10 +2259,10 @@
         <v>24746</v>
       </c>
       <c r="B29" s="6">
-        <v>3.9422027491803702</v>
+        <v>4.09719102279122</v>
       </c>
       <c r="C29" s="6">
-        <v>3.3980723821480701</v>
+        <v>3.4712078258983499</v>
       </c>
       <c r="D29" s="6">
         <v>3.4872646788662198</v>
@@ -2271,16 +2271,16 @@
         <v>4.0764041755641198</v>
       </c>
       <c r="F29" s="6">
-        <v>5.9673469366735503</v>
+        <v>4.8558323474574099</v>
       </c>
       <c r="G29" s="6">
-        <v>-5.7994414861033898E-2</v>
+        <v>-7.6123913953739394E-2</v>
       </c>
       <c r="H29" s="6">
         <v>4.05532872386506E-2</v>
       </c>
       <c r="I29" s="6">
-        <v>0.70245477654403998</v>
+        <v>0.71896780542072902</v>
       </c>
       <c r="J29" s="6">
         <v>3.0861378289513701</v>
@@ -2321,10 +2321,10 @@
         <v>24838</v>
       </c>
       <c r="B30" s="6">
-        <v>4.2506740075096303</v>
+        <v>4.2843050316546103</v>
       </c>
       <c r="C30" s="6">
-        <v>3.3577730203725502</v>
+        <v>3.4428561567348601</v>
       </c>
       <c r="D30" s="6">
         <v>3.4634611860191198</v>
@@ -2333,16 +2333,16 @@
         <v>4.2375450891130404</v>
       </c>
       <c r="F30" s="6">
-        <v>6.4841802132502799</v>
+        <v>5.0546845321198397</v>
       </c>
       <c r="G30" s="6">
-        <v>-7.3201738923734203E-2</v>
+        <v>-9.2014430024478205E-2</v>
       </c>
       <c r="H30" s="6">
         <v>4.0822271095020103E-2</v>
       </c>
       <c r="I30" s="6">
-        <v>0.71725198241028698</v>
+        <v>0.73166269049548605</v>
       </c>
       <c r="J30" s="6">
         <v>3.71157351352783</v>
@@ -2383,10 +2383,10 @@
         <v>24929</v>
       </c>
       <c r="B31" s="6">
-        <v>4.2776534284839798</v>
+        <v>4.3207465797326501</v>
       </c>
       <c r="C31" s="6">
-        <v>3.3142832884645301</v>
+        <v>3.4126227921030101</v>
       </c>
       <c r="D31" s="6">
         <v>3.4382367944588901</v>
@@ -2395,16 +2395,16 @@
         <v>4.2612738194404001</v>
       </c>
       <c r="F31" s="6">
-        <v>7.1466350953361397</v>
+        <v>5.4952076974044504</v>
       </c>
       <c r="G31" s="6">
-        <v>-7.5308961670833605E-2</v>
+        <v>-9.5714071776127702E-2</v>
       </c>
       <c r="H31" s="6">
         <v>4.0930565618132297E-2</v>
       </c>
       <c r="I31" s="6">
-        <v>0.67805821641478303</v>
+        <v>0.69321209424889896</v>
       </c>
       <c r="J31" s="6">
         <v>3.64594609166469</v>
@@ -2445,10 +2445,10 @@
         <v>25020</v>
       </c>
       <c r="B32" s="6">
-        <v>4.18243978507184</v>
+        <v>4.2279379432976603</v>
       </c>
       <c r="C32" s="6">
-        <v>3.27391294785251</v>
+        <v>3.3846307982633199</v>
       </c>
       <c r="D32" s="6">
         <v>3.4148560167192898</v>
@@ -2457,16 +2457,16 @@
         <v>4.1805092185905197</v>
       </c>
       <c r="F32" s="6">
-        <v>7.17952070340624</v>
+        <v>5.6484204606285902</v>
       </c>
       <c r="G32" s="6">
-        <v>-6.9682885092388805E-2</v>
+        <v>-8.6891632963451093E-2</v>
       </c>
       <c r="H32" s="6">
         <v>4.0825743113149897E-2</v>
       </c>
       <c r="I32" s="6">
-        <v>0.64196933671310896</v>
+        <v>0.65651863350621198</v>
       </c>
       <c r="J32" s="6">
         <v>3.4968285635543102</v>
@@ -2507,10 +2507,10 @@
         <v>25112</v>
       </c>
       <c r="B33" s="6">
-        <v>4.0572878791308096</v>
+        <v>4.1264089171082103</v>
       </c>
       <c r="C33" s="6">
-        <v>3.2390752082666601</v>
+        <v>3.35928356673951</v>
       </c>
       <c r="D33" s="6">
         <v>3.3935341437112698</v>
@@ -2519,16 +2519,16 @@
         <v>4.08337915161444</v>
       </c>
       <c r="F33" s="6">
-        <v>7.0297452355202399</v>
+        <v>5.6001692191672401</v>
       </c>
       <c r="G33" s="6">
-        <v>-6.4259050335916196E-2</v>
+        <v>-7.9336500001336505E-2</v>
       </c>
       <c r="H33" s="6">
         <v>4.0809763741119602E-2</v>
       </c>
       <c r="I33" s="6">
-        <v>0.60675373236105301</v>
+        <v>0.62139603475441196</v>
       </c>
       <c r="J33" s="6">
         <v>3.65792970905976</v>
@@ -2569,10 +2569,10 @@
         <v>25204</v>
       </c>
       <c r="B34" s="6">
-        <v>4.20622200121778</v>
+        <v>4.19702359765731</v>
       </c>
       <c r="C34" s="6">
-        <v>3.1935849364537501</v>
+        <v>3.32991997787052</v>
       </c>
       <c r="D34" s="6">
         <v>3.3690154011124198</v>
@@ -2581,16 +2581,16 @@
         <v>4.1765134367563999</v>
       </c>
       <c r="F34" s="6">
-        <v>6.7574259175173097</v>
+        <v>5.3870823252153697</v>
       </c>
       <c r="G34" s="6">
-        <v>-7.0501221904394798E-2</v>
+        <v>-8.5668118517492106E-2</v>
       </c>
       <c r="H34" s="6">
         <v>4.0565091853868099E-2</v>
       </c>
       <c r="I34" s="6">
-        <v>0.60259664057548601</v>
+        <v>0.61548928813959602</v>
       </c>
       <c r="J34" s="6">
         <v>3.4340061407776998</v>
@@ -2631,10 +2631,10 @@
         <v>25294</v>
       </c>
       <c r="B35" s="6">
-        <v>4.0366387934400896</v>
+        <v>4.0926911631889302</v>
       </c>
       <c r="C35" s="6">
-        <v>3.1551273881012301</v>
+        <v>3.3039519983327801</v>
       </c>
       <c r="D35" s="6">
         <v>3.3471635921687501</v>
@@ -2643,16 +2643,16 @@
         <v>4.07010784171504</v>
       </c>
       <c r="F35" s="6">
-        <v>6.7005906820898504</v>
+        <v>5.37139533467007</v>
       </c>
       <c r="G35" s="6">
-        <v>-6.3144779966784803E-2</v>
+        <v>-7.7724334052247004E-2</v>
       </c>
       <c r="H35" s="6">
         <v>4.0601152931549901E-2</v>
       </c>
       <c r="I35" s="6">
-        <v>0.573240643397398</v>
+        <v>0.58716767994378605</v>
       </c>
       <c r="J35" s="6">
         <v>3.8423129497445001</v>
@@ -2693,10 +2693,10 @@
         <v>25385</v>
       </c>
       <c r="B36" s="6">
-        <v>4.0260201682648802</v>
+        <v>4.0720008190219499</v>
       </c>
       <c r="C36" s="6">
-        <v>3.11467082446784</v>
+        <v>3.2779999937800199</v>
       </c>
       <c r="D36" s="6">
         <v>3.3252299710166899</v>
@@ -2705,16 +2705,16 @@
         <v>4.0666520589361603</v>
       </c>
       <c r="F36" s="6">
-        <v>6.18294651919439</v>
+        <v>4.9738135604123999</v>
       </c>
       <c r="G36" s="6">
-        <v>-6.2957837226217603E-2</v>
+        <v>-7.7467677408148194E-2</v>
       </c>
       <c r="H36" s="6">
         <v>4.0437299972004598E-2</v>
       </c>
       <c r="I36" s="6">
-        <v>0.55901311982690305</v>
+        <v>0.57229841490733202</v>
       </c>
       <c r="J36" s="6">
         <v>3.5321067507616899</v>
@@ -2755,10 +2755,10 @@
         <v>25477</v>
       </c>
       <c r="B37" s="6">
-        <v>3.77201458106676</v>
+        <v>3.9162084936574701</v>
       </c>
       <c r="C37" s="6">
-        <v>3.0867930654661402</v>
+        <v>3.2576853158261398</v>
       </c>
       <c r="D37" s="6">
         <v>3.30773382792218</v>
@@ -2767,16 +2767,16 @@
         <v>3.915618489368256</v>
       </c>
       <c r="F37" s="6">
-        <v>5.3601804738840402</v>
+        <v>4.3787952108456203</v>
       </c>
       <c r="G37" s="6">
-        <v>-6.5978357490033196E-2</v>
+        <v>-8.0221213405524905E-2</v>
       </c>
       <c r="H37" s="6">
         <v>4.0372649181884102E-2</v>
       </c>
       <c r="I37" s="6">
-        <v>0.53808729195303495</v>
+        <v>0.55094942754130105</v>
       </c>
       <c r="J37" s="6">
         <v>3.5889842873329201</v>
@@ -2817,10 +2817,10 @@
         <v>25569</v>
       </c>
       <c r="B38" s="6">
-        <v>3.7289253563523399</v>
+        <v>3.8602618608157599</v>
       </c>
       <c r="C38" s="6">
-        <v>3.0608090165151198</v>
+        <v>3.2385291152233302</v>
       </c>
       <c r="D38" s="6">
         <v>3.29110109934367</v>
@@ -2829,16 +2829,16 @@
         <v>3.8892838211411802</v>
       </c>
       <c r="F38" s="6">
-        <v>4.0921280798237403</v>
+        <v>3.37840832489599</v>
       </c>
       <c r="G38" s="6">
-        <v>-6.7093610720290603E-2</v>
+        <v>-8.1646004573381004E-2</v>
       </c>
       <c r="H38" s="6">
         <v>4.0144178753061997E-2</v>
       </c>
       <c r="I38" s="6">
-        <v>0.54860251311610297</v>
+        <v>0.560185851339006</v>
       </c>
       <c r="J38" s="6">
         <v>3.2136455487169</v>
@@ -2879,10 +2879,10 @@
         <v>25659</v>
       </c>
       <c r="B39" s="6">
-        <v>3.7011621343656098</v>
+        <v>3.8393440245572599</v>
       </c>
       <c r="C39" s="6">
-        <v>3.03547275682635</v>
+        <v>3.2195314731522102</v>
       </c>
       <c r="D39" s="6">
         <v>3.27454129884245</v>
@@ -2891,16 +2891,16 @@
         <v>3.8744175136947039</v>
       </c>
       <c r="F39" s="6">
-        <v>3.2030454023725401</v>
+        <v>2.6272862364970702</v>
       </c>
       <c r="G39" s="6">
-        <v>-6.7582183515179695E-2</v>
+        <v>-8.2147009750060396E-2</v>
       </c>
       <c r="H39" s="6">
         <v>4.01020571092216E-2</v>
       </c>
       <c r="I39" s="6">
-        <v>0.52880080725265</v>
+        <v>0.54040327226969798</v>
       </c>
       <c r="J39" s="6">
         <v>3.4041629498941601</v>
@@ -2941,10 +2941,10 @@
         <v>25750</v>
       </c>
       <c r="B40" s="6">
-        <v>3.8001835526988499</v>
+        <v>3.8990631311127402</v>
       </c>
       <c r="C40" s="6">
-        <v>3.0013337612327899</v>
+        <v>3.19764591143552</v>
       </c>
       <c r="D40" s="6">
         <v>3.2556188018358498</v>
@@ -2953,16 +2953,16 @@
         <v>3.946724344411864</v>
       </c>
       <c r="F40" s="6">
-        <v>2.5698620077258201</v>
+        <v>2.0860099602268698</v>
       </c>
       <c r="G40" s="6">
-        <v>-6.6651964743417794E-2</v>
+        <v>-8.1381340422649606E-2</v>
       </c>
       <c r="H40" s="6">
         <v>4.0037837295723501E-2</v>
       </c>
       <c r="I40" s="6">
-        <v>0.51553752610794801</v>
+        <v>0.52736849471362102</v>
       </c>
       <c r="J40" s="6">
         <v>3.3633435010846702</v>
@@ -3003,10 +3003,10 @@
         <v>25842</v>
       </c>
       <c r="B41" s="6">
-        <v>3.32237995403568</v>
+        <v>3.66949876243963</v>
       </c>
       <c r="C41" s="6">
-        <v>2.9921510764956998</v>
+        <v>3.1861040254474799</v>
       </c>
       <c r="D41" s="6">
         <v>3.2449855240532601</v>
@@ -3015,16 +3015,16 @@
         <v>3.6557295779716319</v>
       </c>
       <c r="F41" s="6">
-        <v>2.7100270607021999</v>
+        <v>2.1415511388341901</v>
       </c>
       <c r="G41" s="6">
-        <v>-6.2975407136486097E-2</v>
+        <v>-7.4863358328239205E-2</v>
       </c>
       <c r="H41" s="6">
         <v>4.0371756936773598E-2</v>
       </c>
       <c r="I41" s="6">
-        <v>0.63742866357897199</v>
+        <v>0.66237301878988097</v>
       </c>
       <c r="J41" s="6">
         <v>4.0463855788957801</v>
@@ -3065,10 +3065,10 @@
         <v>25934</v>
       </c>
       <c r="B42" s="6">
-        <v>3.36434327597811</v>
+        <v>3.7280265551455001</v>
       </c>
       <c r="C42" s="6">
-        <v>2.9800877547833</v>
+        <v>3.17187152769836</v>
       </c>
       <c r="D42" s="6">
         <v>3.2324239615996402</v>
@@ -3077,16 +3077,16 @@
         <v>3.711825083913824</v>
       </c>
       <c r="F42" s="6">
-        <v>3.35447194930373</v>
+        <v>2.3288445333802201</v>
       </c>
       <c r="G42" s="6">
-        <v>-6.4111691511082203E-2</v>
+        <v>-7.8452495559595006E-2</v>
       </c>
       <c r="H42" s="6">
         <v>4.0338404993010502E-2</v>
       </c>
       <c r="I42" s="6">
-        <v>0.60545413567552597</v>
+        <v>0.62935425052786198</v>
       </c>
       <c r="J42" s="6">
         <v>3.9419693622135199</v>
@@ -3127,10 +3127,10 @@
         <v>26024</v>
       </c>
       <c r="B43" s="6">
-        <v>3.3472555827000199</v>
+        <v>3.6922360939912</v>
       </c>
       <c r="C43" s="6">
-        <v>2.9685570927960598</v>
+        <v>3.1583485196255299</v>
       </c>
       <c r="D43" s="6">
         <v>3.2205514427829298</v>
@@ -3139,16 +3139,16 @@
         <v>3.695374179804384</v>
       </c>
       <c r="F43" s="6">
-        <v>3.0152699162378598</v>
+        <v>2.1751733220380598</v>
       </c>
       <c r="G43" s="6">
-        <v>-6.3049294175953702E-2</v>
+        <v>-7.5980909062590904E-2</v>
       </c>
       <c r="H43" s="6">
         <v>4.0226195933245001E-2</v>
       </c>
       <c r="I43" s="6">
-        <v>0.60759048168194396</v>
+        <v>0.62546899364985797</v>
       </c>
       <c r="J43" s="6">
         <v>3.4252829173676398</v>
@@ -3189,10 +3189,10 @@
         <v>26115</v>
       </c>
       <c r="B44" s="6">
-        <v>3.3495470021341101</v>
+        <v>3.6466556279436699</v>
       </c>
       <c r="C44" s="6">
-        <v>2.95715561334096</v>
+        <v>3.1453427781266998</v>
       </c>
       <c r="D44" s="6">
         <v>3.2092122599367801</v>
@@ -3201,16 +3201,16 @@
         <v>3.6995682352130399</v>
       </c>
       <c r="F44" s="6">
-        <v>2.3602140813318901</v>
+        <v>1.7790010700622401</v>
       </c>
       <c r="G44" s="6">
-        <v>-6.25985779116595E-2</v>
+        <v>-7.3970717240610301E-2</v>
       </c>
       <c r="H44" s="6">
         <v>4.0038437852588399E-2</v>
       </c>
       <c r="I44" s="6">
-        <v>0.71931769848077298</v>
+        <v>0.72400074550381799</v>
       </c>
       <c r="J44" s="6">
         <v>2.6679236487710098</v>
@@ -3251,10 +3251,10 @@
         <v>26207</v>
       </c>
       <c r="B45" s="6">
-        <v>3.3033918990119302</v>
+        <v>3.54467168929237</v>
       </c>
       <c r="C45" s="6">
-        <v>2.94986209086488</v>
+        <v>3.1344897911633498</v>
       </c>
       <c r="D45" s="6">
         <v>3.2001345235936598</v>
@@ -3263,16 +3263,16 @@
         <v>3.6550717067172318</v>
       </c>
       <c r="F45" s="6">
-        <v>1.1347460459606999</v>
+        <v>0.83769746596828998</v>
       </c>
       <c r="G45" s="6">
-        <v>-5.9486028416958103E-2</v>
+        <v>-6.8383093515876403E-2</v>
       </c>
       <c r="H45" s="6">
         <v>3.9834848184443702E-2</v>
       </c>
       <c r="I45" s="6">
-        <v>1.1730737403244</v>
+        <v>1.1627495199890701</v>
       </c>
       <c r="J45" s="6">
         <v>1.58370449708919</v>
@@ -3313,10 +3313,10 @@
         <v>26299</v>
       </c>
       <c r="B46" s="6">
-        <v>3.41817207335149</v>
+        <v>3.6125825575019599</v>
       </c>
       <c r="C46" s="6">
-        <v>2.9373968023316199</v>
+        <v>3.1209384547161898</v>
       </c>
       <c r="D46" s="6">
         <v>3.1885569108718199</v>
@@ -3325,16 +3325,16 @@
         <v>3.7252772529250282</v>
       </c>
       <c r="F46" s="6">
-        <v>1.62376869988003</v>
+        <v>1.2648223095907301</v>
       </c>
       <c r="G46" s="6">
-        <v>-6.3553522379932503E-2</v>
+        <v>-7.2674872122631101E-2</v>
       </c>
       <c r="H46" s="6">
         <v>3.98502639132561E-2</v>
       </c>
       <c r="I46" s="6">
-        <v>1.0577023541741799</v>
+        <v>1.0582854040468099</v>
       </c>
       <c r="J46" s="6">
         <v>2.7236253436503199</v>
@@ -3375,10 +3375,10 @@
         <v>26390</v>
       </c>
       <c r="B47" s="6">
-        <v>3.54856033395528</v>
+        <v>3.6840788754184799</v>
       </c>
       <c r="C47" s="6">
-        <v>2.9187317276554801</v>
+        <v>3.10407272101292</v>
       </c>
       <c r="D47" s="6">
         <v>3.1741407071598</v>
@@ -3387,16 +3387,16 @@
         <v>3.8184485321232762</v>
       </c>
       <c r="F47" s="6">
-        <v>2.1184392185174401</v>
+        <v>1.6588042967669001</v>
       </c>
       <c r="G47" s="6">
-        <v>-6.9606783489132601E-2</v>
+        <v>-7.9987218628257195E-2</v>
       </c>
       <c r="H47" s="6">
         <v>3.9812554309181E-2</v>
       </c>
       <c r="I47" s="6">
-        <v>1.0081120454389201</v>
+        <v>1.0183472765167401</v>
       </c>
       <c r="J47" s="6">
         <v>1.8793868151541699</v>
@@ -3437,10 +3437,10 @@
         <v>26481</v>
       </c>
       <c r="B48" s="6">
-        <v>3.4567011441278299</v>
+        <v>3.6228420549198801</v>
       </c>
       <c r="C48" s="6">
-        <v>2.90443076571459</v>
+        <v>3.08872397397369</v>
       </c>
       <c r="D48" s="6">
         <v>3.1612337120583498</v>
@@ -3449,16 +3449,16 @@
         <v>3.7557585378868201</v>
       </c>
       <c r="F48" s="6">
-        <v>2.6052515200158299</v>
+        <v>2.1707978687552401</v>
       </c>
       <c r="G48" s="6">
-        <v>-6.4820028009484304E-2</v>
+        <v>-7.4283888694429798E-2</v>
       </c>
       <c r="H48" s="6">
         <v>3.9811324489725498E-2</v>
       </c>
       <c r="I48" s="6">
-        <v>0.90779326794961201</v>
+        <v>0.920227591522632</v>
       </c>
       <c r="J48" s="6">
         <v>2.1312620906664201</v>
@@ -3499,10 +3499,10 @@
         <v>26573</v>
       </c>
       <c r="B49" s="6">
-        <v>3.5524569200042801</v>
+        <v>3.6642028504327802</v>
       </c>
       <c r="C49" s="6">
-        <v>2.8862648677335199</v>
+        <v>3.0709073911685598</v>
       </c>
       <c r="D49" s="6">
         <v>3.1463307369461502</v>
@@ -3511,16 +3511,16 @@
         <v>3.8101113540443081</v>
       </c>
       <c r="F49" s="6">
-        <v>2.7788616062404699</v>
+        <v>2.3727272410349101</v>
       </c>
       <c r="G49" s="6">
-        <v>-6.75766744751186E-2</v>
+        <v>-7.7009735386063899E-2</v>
       </c>
       <c r="H49" s="6">
         <v>3.9763867653441198E-2</v>
       </c>
       <c r="I49" s="6">
-        <v>0.84394910711346305</v>
+        <v>0.85981487218796104</v>
       </c>
       <c r="J49" s="6">
         <v>1.68208418100775</v>
@@ -3561,10 +3561,10 @@
         <v>26665</v>
       </c>
       <c r="B50" s="6">
-        <v>3.81518116333715</v>
+        <v>3.81953627144487</v>
       </c>
       <c r="C50" s="6">
-        <v>2.8540803359768301</v>
+        <v>3.0467379539476398</v>
       </c>
       <c r="D50" s="6">
         <v>3.1261943540935899</v>
@@ -3573,16 +3573,16 @@
         <v>3.9620691359387439</v>
       </c>
       <c r="F50" s="6">
-        <v>3.2129829899556599</v>
+        <v>2.6971151487969101</v>
       </c>
       <c r="G50" s="6">
-        <v>-7.4994467005996407E-2</v>
+        <v>-8.4828064262568503E-2</v>
       </c>
       <c r="H50" s="6">
         <v>3.9754354541398397E-2</v>
       </c>
       <c r="I50" s="6">
-        <v>0.77467375060650301</v>
+        <v>0.79132410206119097</v>
       </c>
       <c r="J50" s="6">
         <v>2.1454036278840598</v>
@@ -3623,10 +3623,10 @@
         <v>26755</v>
       </c>
       <c r="B51" s="6">
-        <v>3.7509938353791399</v>
+        <v>3.8379473229984198</v>
       </c>
       <c r="C51" s="6">
-        <v>2.8223723902256799</v>
+        <v>3.0231677779947002</v>
       </c>
       <c r="D51" s="6">
         <v>3.1064823578727099</v>
@@ -3635,16 +3635,16 @@
         <v>3.9047648949889919</v>
       </c>
       <c r="F51" s="6">
-        <v>4.8318431457852897</v>
+        <v>3.8806465543170798</v>
       </c>
       <c r="G51" s="6">
-        <v>-7.4305914366302503E-2</v>
+        <v>-8.4145826594547807E-2</v>
       </c>
       <c r="H51" s="6">
         <v>4.0197683357015998E-2</v>
       </c>
       <c r="I51" s="6">
-        <v>1.4598306151476399</v>
+        <v>1.46269783353365</v>
       </c>
       <c r="J51" s="6">
         <v>3.2069531961148598</v>
@@ -3685,10 +3685,10 @@
         <v>26846</v>
       </c>
       <c r="B52" s="6">
-        <v>3.4722900506837702</v>
+        <v>3.6600175462842901</v>
       </c>
       <c r="C52" s="6">
-        <v>2.80210464715331</v>
+        <v>3.0050435919641498</v>
       </c>
       <c r="D52" s="6">
         <v>3.0912122470249699</v>
@@ -3697,16 +3697,16 @@
         <v>3.7399854775779522</v>
       </c>
       <c r="F52" s="6">
-        <v>4.5341999547802603</v>
+        <v>3.7599645274417499</v>
       </c>
       <c r="G52" s="6">
-        <v>-7.9390543956953705E-2</v>
+        <v>-8.8701955890419307E-2</v>
       </c>
       <c r="H52" s="6">
         <v>4.0248653801225498E-2</v>
       </c>
       <c r="I52" s="6">
-        <v>1.2893310555453601</v>
+        <v>1.2935851211518099</v>
       </c>
       <c r="J52" s="6">
         <v>4.0751843953886899</v>
@@ -3747,10 +3747,10 @@
         <v>26938</v>
       </c>
       <c r="B53" s="6">
-        <v>3.5486078101448602</v>
+        <v>3.7210480850339498</v>
       </c>
       <c r="C53" s="6">
-        <v>2.7776428015419699</v>
+        <v>2.9850175615484198</v>
       </c>
       <c r="D53" s="6">
         <v>3.0743789760750202</v>
@@ -3759,16 +3759,16 @@
         <v>3.7869516407801802</v>
       </c>
       <c r="F53" s="6">
-        <v>4.0933771809032997</v>
+        <v>3.2766192319380698</v>
       </c>
       <c r="G53" s="6">
-        <v>-7.4522759971395305E-2</v>
+        <v>-8.3573144408362401E-2</v>
       </c>
       <c r="H53" s="6">
         <v>4.0311556606257501E-2</v>
       </c>
       <c r="I53" s="6">
-        <v>1.1651479208217701</v>
+        <v>1.17065278902248</v>
       </c>
       <c r="J53" s="6">
         <v>4.6757178996427999</v>
@@ -3809,10 +3809,10 @@
         <v>27030</v>
       </c>
       <c r="B54" s="6">
-        <v>3.3790063133936599</v>
+        <v>3.62325192808132</v>
       </c>
       <c r="C54" s="6">
-        <v>2.7598037913312701</v>
+        <v>2.9683617519910501</v>
       </c>
       <c r="D54" s="6">
         <v>3.0603127743390499</v>
@@ -3821,16 +3821,16 @@
         <v>3.6718210065280239</v>
       </c>
       <c r="F54" s="6">
-        <v>3.41968532383919</v>
+        <v>2.6581150244782101</v>
       </c>
       <c r="G54" s="6">
-        <v>-8.65848107912255E-2</v>
+        <v>-9.5749558849290595E-2</v>
       </c>
       <c r="H54" s="6">
         <v>4.0452344770014602E-2</v>
       </c>
       <c r="I54" s="6">
-        <v>1.16341701045871</v>
+        <v>1.1727368275244301</v>
       </c>
       <c r="J54" s="6">
         <v>5.4582040853974796</v>
@@ -3871,10 +3871,10 @@
         <v>27120</v>
       </c>
       <c r="B55" s="6">
-        <v>3.4009110949975998</v>
+        <v>3.6739923707002902</v>
       </c>
       <c r="C55" s="6">
-        <v>2.7399685333188399</v>
+        <v>2.9514581863213998</v>
       </c>
       <c r="D55" s="6">
         <v>3.0459888845266399</v>
@@ -3883,16 +3883,16 @@
         <v>3.6676476305727479</v>
       </c>
       <c r="F55" s="6">
-        <v>3.4907161562753699</v>
+        <v>2.3789064901469601</v>
       </c>
       <c r="G55" s="6">
-        <v>-8.5130100360951394E-2</v>
+        <v>-9.4672041602960402E-2</v>
       </c>
       <c r="H55" s="6">
         <v>4.06898274772945E-2</v>
       </c>
       <c r="I55" s="6">
-        <v>1.8688048091844001</v>
+        <v>1.88132813280272</v>
       </c>
       <c r="J55" s="6">
         <v>6.2816956751011004</v>
@@ -3933,10 +3933,10 @@
         <v>27211</v>
       </c>
       <c r="B56" s="6">
-        <v>3.1756330684882301</v>
+        <v>3.5309760785562401</v>
       </c>
       <c r="C56" s="6">
-        <v>2.7287049150810598</v>
+        <v>2.9392640803648402</v>
       </c>
       <c r="D56" s="6">
         <v>3.0356268226665302</v>
@@ -3945,16 +3945,16 @@
         <v>3.520737209035516</v>
       </c>
       <c r="F56" s="6">
-        <v>2.7981274650087999</v>
+        <v>1.67538141492571</v>
       </c>
       <c r="G56" s="6">
-        <v>-9.3743889689552398E-2</v>
+        <v>-0.10191267747331199</v>
       </c>
       <c r="H56" s="6">
         <v>4.07645670040723E-2</v>
       </c>
       <c r="I56" s="6">
-        <v>1.8657185470748601</v>
+        <v>1.87002129766209</v>
       </c>
       <c r="J56" s="6">
         <v>6.8763834300505602</v>
@@ -3995,10 +3995,10 @@
         <v>27303</v>
       </c>
       <c r="B57" s="6">
-        <v>3.1285541398291801</v>
+        <v>3.4878095090413401</v>
       </c>
       <c r="C57" s="6">
-        <v>2.7190802518880002</v>
+        <v>2.9288529229645799</v>
       </c>
       <c r="D57" s="6">
         <v>3.0266509910637001</v>
@@ -4007,16 +4007,16 @@
         <v>3.484899720572912</v>
       </c>
       <c r="F57" s="6">
-        <v>1.6623577204217099</v>
+        <v>0.72914675956292296</v>
       </c>
       <c r="G57" s="6">
-        <v>-9.6257932653171605E-2</v>
+        <v>-0.104939872827035</v>
       </c>
       <c r="H57" s="6">
         <v>4.0766042353253602E-2</v>
       </c>
       <c r="I57" s="6">
-        <v>1.5747149190416301</v>
+        <v>1.58594417336938</v>
       </c>
       <c r="J57" s="6">
         <v>7.1556314755090797</v>
@@ -4057,10 +4057,10 @@
         <v>27395</v>
       </c>
       <c r="B58" s="6">
-        <v>2.8188976577420202</v>
+        <v>3.2678118825112601</v>
       </c>
       <c r="C58" s="6">
-        <v>2.72214232653439</v>
+        <v>2.9246946307126902</v>
       </c>
       <c r="D58" s="6">
         <v>3.02290626450195</v>
@@ -4069,16 +4069,16 @@
         <v>3.3122377546755359</v>
       </c>
       <c r="F58" s="6">
-        <v>0.42488493756218298</v>
+        <v>-0.24193688038974401</v>
       </c>
       <c r="G58" s="6">
-        <v>-9.2461644629079007E-2</v>
+        <v>-9.6687943998939194E-2</v>
       </c>
       <c r="H58" s="6">
         <v>4.0731646084122101E-2</v>
       </c>
       <c r="I58" s="6">
-        <v>1.49345698554637</v>
+        <v>1.502236707072</v>
       </c>
       <c r="J58" s="6">
         <v>5.6073750485448404</v>
@@ -4119,10 +4119,10 @@
         <v>27485</v>
       </c>
       <c r="B59" s="6">
-        <v>2.8523159733699099</v>
+        <v>3.2550850802089299</v>
       </c>
       <c r="C59" s="6">
-        <v>2.7237608155131001</v>
+        <v>2.92020448236407</v>
       </c>
       <c r="D59" s="6">
         <v>3.0189206760007301</v>
@@ -4131,16 +4131,16 @@
         <v>3.3255206933091039</v>
       </c>
       <c r="F59" s="6">
-        <v>-0.184299295408835</v>
+        <v>-0.68445781603145395</v>
       </c>
       <c r="G59" s="6">
-        <v>-9.7038514257717506E-2</v>
+        <v>-9.8090191054106005E-2</v>
       </c>
       <c r="H59" s="6">
         <v>4.0732289035939999E-2</v>
       </c>
       <c r="I59" s="6">
-        <v>1.63228534645109</v>
+        <v>1.61533378631211</v>
       </c>
       <c r="J59" s="6">
         <v>4.7026205765642004</v>
@@ -4181,10 +4181,10 @@
         <v>27576</v>
       </c>
       <c r="B60" s="6">
-        <v>2.9315562664144998</v>
+        <v>3.28089651121965</v>
       </c>
       <c r="C60" s="6">
-        <v>2.7221747987350899</v>
+        <v>2.9147222931376899</v>
       </c>
       <c r="D60" s="6">
         <v>3.01411988034838</v>
@@ -4193,16 +4193,16 @@
         <v>3.3592607086475601</v>
       </c>
       <c r="F60" s="6">
-        <v>0.36988870691777698</v>
+        <v>-0.181225048329793</v>
       </c>
       <c r="G60" s="6">
-        <v>-0.11400492503085501</v>
+        <v>-0.10785780398039201</v>
       </c>
       <c r="H60" s="6">
         <v>4.0746494142740702E-2</v>
       </c>
       <c r="I60" s="6">
-        <v>1.49331008708005</v>
+        <v>1.4723685548493</v>
       </c>
       <c r="J60" s="6">
         <v>4.8162390775456601</v>
@@ -4243,10 +4243,10 @@
         <v>27668</v>
       </c>
       <c r="B61" s="6">
-        <v>2.8504010768998298</v>
+        <v>3.2162327051931299</v>
       </c>
       <c r="C61" s="6">
-        <v>2.7239303789681002</v>
+        <v>2.91107493499814</v>
       </c>
       <c r="D61" s="6">
         <v>3.0108067496654898</v>
@@ -4255,16 +4255,16 @@
         <v>3.3057805353324641</v>
       </c>
       <c r="F61" s="6">
-        <v>1.30326501433024</v>
+        <v>0.67473755194816898</v>
       </c>
       <c r="G61" s="6">
-        <v>-9.7564407474600406E-2</v>
+        <v>-9.3043644913137893E-2</v>
       </c>
       <c r="H61" s="6">
         <v>4.0749255562879901E-2</v>
       </c>
       <c r="I61" s="6">
-        <v>1.2934922544891201</v>
+        <v>1.2816859417067199</v>
       </c>
       <c r="J61" s="6">
         <v>5.1858152754996496</v>
@@ -4305,10 +4305,10 @@
         <v>27760</v>
       </c>
       <c r="B62" s="6">
-        <v>3.0545022964421999</v>
+        <v>3.2976696514838202</v>
       </c>
       <c r="C62" s="6">
-        <v>2.71765484547922</v>
+        <v>2.9052816377500799</v>
       </c>
       <c r="D62" s="6">
         <v>3.00550572809744</v>
@@ -4317,16 +4317,16 @@
         <v>3.3868854057572721</v>
       </c>
       <c r="F62" s="6">
-        <v>2.0682983496178098</v>
+        <v>1.4811056402746801</v>
       </c>
       <c r="G62" s="6">
-        <v>-0.12786263918040799</v>
+        <v>-0.10754552416034301</v>
       </c>
       <c r="H62" s="6">
         <v>4.0742364248292397E-2</v>
       </c>
       <c r="I62" s="6">
-        <v>1.1475859934299699</v>
+        <v>1.1430574868275001</v>
       </c>
       <c r="J62" s="6">
         <v>4.9984917367041799</v>
@@ -4367,10 +4367,10 @@
         <v>27851</v>
       </c>
       <c r="B63" s="6">
-        <v>2.7337665048659301</v>
+        <v>3.0934419467118</v>
       </c>
       <c r="C63" s="6">
-        <v>2.7248020458573898</v>
+        <v>2.9058189080202799</v>
       </c>
       <c r="D63" s="6">
         <v>3.00512571485483</v>
@@ -4379,16 +4379,16 @@
         <v>3.2417156922002239</v>
       </c>
       <c r="F63" s="6">
-        <v>2.5344943749681801</v>
+        <v>2.1845571250595399</v>
       </c>
       <c r="G63" s="6">
-        <v>-7.7246976423676006E-2</v>
+        <v>-7.7070835041785801E-2</v>
       </c>
       <c r="H63" s="6">
         <v>4.0656817191781998E-2</v>
       </c>
       <c r="I63" s="6">
-        <v>1.1301859161141301</v>
+        <v>1.1286495986106699</v>
       </c>
       <c r="J63" s="6">
         <v>3.82742805064888</v>
@@ -4429,10 +4429,10 @@
         <v>27942</v>
       </c>
       <c r="B64" s="6">
-        <v>2.6485376186237</v>
+        <v>3.0290253403945999</v>
       </c>
       <c r="C64" s="6">
-        <v>2.7367326341324598</v>
+        <v>2.9094444640637098</v>
       </c>
       <c r="D64" s="6">
         <v>3.0070111161764701</v>
@@ -4441,16 +4441,16 @@
         <v>3.1686961953488</v>
       </c>
       <c r="F64" s="6">
-        <v>3.1172994680000601</v>
+        <v>2.7768989156580801</v>
       </c>
       <c r="G64" s="6">
-        <v>-6.9809990731303895E-2</v>
+        <v>-6.8965227790296096E-2</v>
       </c>
       <c r="H64" s="6">
         <v>4.0720663081081597E-2</v>
       </c>
       <c r="I64" s="6">
-        <v>1.0317827928221801</v>
+        <v>1.0416123353233799</v>
       </c>
       <c r="J64" s="6">
         <v>4.6209313790618101</v>
@@ -4491,10 +4491,10 @@
         <v>28034</v>
       </c>
       <c r="B65" s="6">
-        <v>2.6223989700155101</v>
+        <v>3.00166132365954</v>
       </c>
       <c r="C65" s="6">
-        <v>2.75106246903337</v>
+        <v>2.9144744204364401</v>
       </c>
       <c r="D65" s="6">
         <v>3.0099678725603098</v>
@@ -4503,16 +4503,16 @@
         <v>3.1382349377459402</v>
       </c>
       <c r="F65" s="6">
-        <v>3.37341132288583</v>
+        <v>3.0315274978322599</v>
       </c>
       <c r="G65" s="6">
-        <v>-6.79319298411179E-2</v>
+        <v>-6.6378626444824507E-2</v>
       </c>
       <c r="H65" s="6">
         <v>4.0730018275446797E-2</v>
       </c>
       <c r="I65" s="6">
-        <v>0.92732672544110695</v>
+        <v>0.93966616790544299</v>
       </c>
       <c r="J65" s="6">
         <v>4.9662430214872302</v>
@@ -4553,10 +4553,10 @@
         <v>28126</v>
       </c>
       <c r="B66" s="6">
-        <v>2.6900369972571201</v>
+        <v>3.0335272193768099</v>
       </c>
       <c r="C66" s="6">
-        <v>2.7636030182415099</v>
+        <v>2.9187975514931401</v>
       </c>
       <c r="D66" s="6">
         <v>3.0123470702586901</v>
@@ -4565,16 +4565,16 @@
         <v>3.1547923965885358</v>
       </c>
       <c r="F66" s="6">
-        <v>3.8456127800508901</v>
+        <v>3.3985586014750901</v>
       </c>
       <c r="G66" s="6">
-        <v>-7.2177823464497803E-2</v>
+        <v>-6.8239518709251407E-2</v>
       </c>
       <c r="H66" s="6">
         <v>4.0802497849030298E-2</v>
       </c>
       <c r="I66" s="6">
-        <v>0.86079221937124994</v>
+        <v>0.87471886889091099</v>
       </c>
       <c r="J66" s="6">
         <v>5.3461129581926103</v>
@@ -4615,10 +4615,10 @@
         <v>28216</v>
       </c>
       <c r="B67" s="6">
-        <v>2.9011242067104202</v>
+        <v>3.1230852563812701</v>
       </c>
       <c r="C67" s="6">
-        <v>2.76478061224197</v>
+        <v>2.9188720292981101</v>
       </c>
       <c r="D67" s="6">
         <v>3.0113444287599398</v>
@@ -4627,16 +4627,16 @@
         <v>3.2637309971766282</v>
       </c>
       <c r="F67" s="6">
-        <v>4.0598912307074801</v>
+        <v>3.6412825979315402</v>
       </c>
       <c r="G67" s="6">
-        <v>-9.4491080606983802E-2</v>
+        <v>-8.0006227878550398E-2</v>
       </c>
       <c r="H67" s="6">
         <v>4.0736488826463503E-2</v>
       </c>
       <c r="I67" s="6">
-        <v>0.79637904907175905</v>
+        <v>0.81259706238738405</v>
       </c>
       <c r="J67" s="6">
         <v>5.0904462904363701</v>
@@ -4677,10 +4677,10 @@
         <v>28307</v>
       </c>
       <c r="B68" s="6">
-        <v>2.9781201211162598</v>
+        <v>3.1787345401526999</v>
       </c>
       <c r="C68" s="6">
-        <v>2.7627334772876901</v>
+        <v>2.9175506635131301</v>
       </c>
       <c r="D68" s="6">
         <v>3.00918501465212</v>
@@ -4689,16 +4689,16 @@
         <v>3.3049555503982959</v>
       </c>
       <c r="F68" s="6">
-        <v>4.9070733630693404</v>
+        <v>4.3199316669980599</v>
       </c>
       <c r="G68" s="6">
-        <v>-0.10542481893557901</v>
+        <v>-8.7065701143754101E-2</v>
       </c>
       <c r="H68" s="6">
         <v>4.07880942582073E-2</v>
       </c>
       <c r="I68" s="6">
-        <v>0.73898780939381103</v>
+        <v>0.75650665441462595</v>
       </c>
       <c r="J68" s="6">
         <v>5.4911132036128301</v>
@@ -4739,10 +4739,10 @@
         <v>28399</v>
       </c>
       <c r="B69" s="6">
-        <v>2.5423805686748802</v>
+        <v>2.9407382450349</v>
       </c>
       <c r="C69" s="6">
-        <v>2.7824143375244401</v>
+        <v>2.9244881793722901</v>
       </c>
       <c r="D69" s="6">
         <v>3.0137852192269001</v>
@@ -4751,16 +4751,16 @@
         <v>3.1164841516122199</v>
       </c>
       <c r="F69" s="6">
-        <v>4.9741675705977304</v>
+        <v>4.5411509654013598</v>
       </c>
       <c r="G69" s="6">
-        <v>-6.0422135273186503E-2</v>
+        <v>-6.3562664918970294E-2</v>
       </c>
       <c r="H69" s="6">
         <v>4.0474824082545199E-2</v>
       </c>
       <c r="I69" s="6">
-        <v>0.76169383663698298</v>
+        <v>0.77568083892490602</v>
       </c>
       <c r="J69" s="6">
         <v>4.5928341723173904</v>
@@ -4801,10 +4801,10 @@
         <v>28491</v>
       </c>
       <c r="B70" s="6">
-        <v>2.5166569225299602</v>
+        <v>2.9091710197480598</v>
       </c>
       <c r="C70" s="6">
-        <v>2.8050965669289498</v>
+        <v>2.9326645909420899</v>
       </c>
       <c r="D70" s="6">
         <v>3.0193672922064301</v>
@@ -4813,16 +4813,16 @@
         <v>3.086512498371532</v>
       </c>
       <c r="F70" s="6">
-        <v>4.8168862547593703</v>
+        <v>4.50275815568091</v>
       </c>
       <c r="G70" s="6">
-        <v>-5.9483387647183902E-2</v>
+        <v>-6.1673101729546202E-2</v>
       </c>
       <c r="H70" s="6">
         <v>4.0460166802506303E-2</v>
       </c>
       <c r="I70" s="6">
-        <v>0.70717678096782499</v>
+        <v>0.72158259850568995</v>
       </c>
       <c r="J70" s="6">
         <v>4.9693603901465497</v>
@@ -4863,10 +4863,10 @@
         <v>28581</v>
       </c>
       <c r="B71" s="6">
-        <v>2.82400114464579</v>
+        <v>3.1566888156609001</v>
       </c>
       <c r="C71" s="6">
-        <v>2.8101420921104698</v>
+        <v>2.9307431130722299</v>
       </c>
       <c r="D71" s="6">
         <v>3.0168056444831501</v>
@@ -4875,16 +4875,16 @@
         <v>3.3305292132630919</v>
       </c>
       <c r="F71" s="6">
-        <v>6.1822447033536596</v>
+        <v>5.3192793909642004</v>
       </c>
       <c r="G71" s="6">
-        <v>-6.9125051415794697E-2</v>
+        <v>-7.3514519446558499E-2</v>
       </c>
       <c r="H71" s="6">
         <v>4.06105722107995E-2</v>
       </c>
       <c r="I71" s="6">
-        <v>0.68044673130626798</v>
+        <v>0.69681909469967096</v>
       </c>
       <c r="J71" s="6">
         <v>5.8396292205941602</v>
@@ -4925,10 +4925,10 @@
         <v>28672</v>
       </c>
       <c r="B72" s="6">
-        <v>2.8194458307196899</v>
+        <v>3.1529285646221301</v>
       </c>
       <c r="C72" s="6">
-        <v>2.8152740139433199</v>
+        <v>2.9290081879580199</v>
       </c>
       <c r="D72" s="6">
         <v>3.0144808456522401</v>
@@ -4937,16 +4937,16 @@
         <v>3.327964112533492</v>
       </c>
       <c r="F72" s="6">
-        <v>6.6196610761572297</v>
+        <v>5.8442375615051096</v>
       </c>
       <c r="G72" s="6">
-        <v>-6.9225419627065105E-2</v>
+        <v>-7.3459996568606301E-2</v>
       </c>
       <c r="H72" s="6">
         <v>4.0590405895867203E-2</v>
       </c>
       <c r="I72" s="6">
-        <v>0.63920961993334002</v>
+        <v>0.655558355378419</v>
       </c>
       <c r="J72" s="6">
         <v>5.84529029540343</v>
@@ -4987,10 +4987,10 @@
         <v>28764</v>
       </c>
       <c r="B73" s="6">
-        <v>2.83317603010192</v>
+        <v>3.1727270014519902</v>
       </c>
       <c r="C73" s="6">
-        <v>2.8194298613176501</v>
+        <v>2.9269763209000801</v>
       </c>
       <c r="D73" s="6">
         <v>3.01200748590953</v>
@@ -4999,16 +4999,16 @@
         <v>3.3306964530530561</v>
       </c>
       <c r="F73" s="6">
-        <v>7.3632308875927501</v>
+        <v>6.3781327398328402</v>
       </c>
       <c r="G73" s="6">
-        <v>-6.9523364497362405E-2</v>
+        <v>-7.3742791871340099E-2</v>
       </c>
       <c r="H73" s="6">
         <v>4.0744309312910301E-2</v>
       </c>
       <c r="I73" s="6">
-        <v>0.61164094385435597</v>
+        <v>0.62968242841711297</v>
       </c>
       <c r="J73" s="6">
         <v>6.1727181003374598</v>
@@ -5049,10 +5049,10 @@
         <v>28856</v>
       </c>
       <c r="B74" s="6">
-        <v>2.7746329644178598</v>
+        <v>3.07226940226268</v>
       </c>
       <c r="C74" s="6">
-        <v>2.8243945296741102</v>
+        <v>2.9256107995804599</v>
       </c>
       <c r="D74" s="6">
         <v>3.0102841471002</v>
@@ -5061,16 +5061,16 @@
         <v>3.325940839539276</v>
       </c>
       <c r="F74" s="6">
-        <v>4.8113047221551701</v>
+        <v>4.7687173756288503</v>
       </c>
       <c r="G74" s="6">
-        <v>-6.9745770595992698E-2</v>
+        <v>-7.3687511573024403E-2</v>
       </c>
       <c r="H74" s="6">
         <v>3.9849213394284697E-2</v>
       </c>
       <c r="I74" s="6">
-        <v>0.98701722958026294</v>
+        <v>0.99787424081028298</v>
       </c>
       <c r="J74" s="6">
         <v>5.0262362802257803</v>
@@ -5111,10 +5111,10 @@
         <v>28946</v>
       </c>
       <c r="B75" s="6">
-        <v>2.7701518170504098</v>
+        <v>3.0955421880646399</v>
       </c>
       <c r="C75" s="6">
-        <v>2.83015046134217</v>
+        <v>2.92476565308012</v>
       </c>
       <c r="D75" s="6">
         <v>3.00913166227267</v>
@@ -5123,16 +5123,16 @@
         <v>3.2881665180277801</v>
       </c>
       <c r="F75" s="6">
-        <v>5.4126988173372297</v>
+        <v>4.9769059297083196</v>
       </c>
       <c r="G75" s="6">
-        <v>-7.0211080503266396E-2</v>
+        <v>-7.4046614678973E-2</v>
       </c>
       <c r="H75" s="6">
         <v>4.0263832319168497E-2</v>
       </c>
       <c r="I75" s="6">
-        <v>1.3231034753004101</v>
+        <v>1.3682495271891499</v>
       </c>
       <c r="J75" s="6">
         <v>5.9794910623726496</v>
@@ -5173,10 +5173,10 @@
         <v>29037</v>
       </c>
       <c r="B76" s="6">
-        <v>2.8180481916315099</v>
+        <v>3.1257419954588501</v>
       </c>
       <c r="C76" s="6">
-        <v>2.83344364269945</v>
+        <v>2.9227288632260402</v>
       </c>
       <c r="D76" s="6">
         <v>3.0067353535621701</v>
@@ -5185,16 +5185,16 @@
         <v>3.3334383326569479</v>
       </c>
       <c r="F76" s="6">
-        <v>4.79140980981549</v>
+        <v>4.4617850814329403</v>
       </c>
       <c r="G76" s="6">
-        <v>-6.89909310621271E-2</v>
+        <v>-7.3159085418554107E-2</v>
       </c>
       <c r="H76" s="6">
         <v>4.0196591764588098E-2</v>
       </c>
       <c r="I76" s="6">
-        <v>1.1791712483379</v>
+        <v>1.2230460770927301</v>
       </c>
       <c r="J76" s="6">
         <v>6.2812524217489702</v>
@@ -5235,10 +5235,10 @@
         <v>29129</v>
       </c>
       <c r="B77" s="6">
-        <v>2.7952810149620602</v>
+        <v>3.1217525397240502</v>
       </c>
       <c r="C77" s="6">
-        <v>2.8375787579668699</v>
+        <v>2.9212780551080302</v>
       </c>
       <c r="D77" s="6">
         <v>3.0048779986691598</v>
@@ -5247,16 +5247,16 @@
         <v>3.3132739837232119</v>
       </c>
       <c r="F77" s="6">
-        <v>4.6494158895560496</v>
+        <v>4.2033366843653504</v>
       </c>
       <c r="G77" s="6">
-        <v>-6.9558513567827898E-2</v>
+        <v>-7.3484132914735698E-2</v>
       </c>
       <c r="H77" s="6">
         <v>4.0291883598760202E-2</v>
       </c>
       <c r="I77" s="6">
-        <v>1.0830645376536601</v>
+        <v>1.12414869417729</v>
       </c>
       <c r="J77" s="6">
         <v>6.93731774451867</v>
@@ -5297,10 +5297,10 @@
         <v>29221</v>
       </c>
       <c r="B78" s="6">
-        <v>2.8310056493346298</v>
+        <v>3.1625421157663101</v>
       </c>
       <c r="C78" s="6">
-        <v>2.8388661577514398</v>
+        <v>2.9196275139824799</v>
       </c>
       <c r="D78" s="6">
         <v>3.0027085479589899</v>
@@ -5309,16 +5309,16 @@
         <v>3.3237880057312599</v>
       </c>
       <c r="F78" s="6">
-        <v>4.6742970985680996</v>
+        <v>3.9658191963995901</v>
       </c>
       <c r="G78" s="6">
-        <v>-6.7552805916293701E-2</v>
+        <v>-7.2032958473091893E-2</v>
       </c>
       <c r="H78" s="6">
         <v>4.0485062360466499E-2</v>
       </c>
       <c r="I78" s="6">
-        <v>1.12994315080156</v>
+        <v>1.1647064465345001</v>
       </c>
       <c r="J78" s="6">
         <v>7.7595931771900499</v>
@@ -5359,10 +5359,10 @@
         <v>29312</v>
       </c>
       <c r="B79" s="6">
-        <v>2.2832807138108802</v>
+        <v>2.83860837682824</v>
       </c>
       <c r="C79" s="6">
-        <v>2.8678365011143101</v>
+        <v>2.9294183565708298</v>
       </c>
       <c r="D79" s="6">
         <v>3.0106426815623402</v>
@@ -5371,16 +5371,16 @@
         <v>3.0112990482351121</v>
       </c>
       <c r="F79" s="6">
-        <v>4.2434734341284202</v>
+        <v>3.5588560163652101</v>
       </c>
       <c r="G79" s="6">
-        <v>-0.14708018822243701</v>
+        <v>-0.120876584371697</v>
       </c>
       <c r="H79" s="6">
         <v>4.0428557531471801E-2</v>
       </c>
       <c r="I79" s="6">
-        <v>1.0161604126811199</v>
+        <v>1.04699700072973</v>
       </c>
       <c r="J79" s="6">
         <v>7.5120097069004004</v>
@@ -5421,10 +5421,10 @@
         <v>29403</v>
       </c>
       <c r="B80" s="6">
-        <v>2.3168416291668601</v>
+        <v>2.8646958392219699</v>
       </c>
       <c r="C80" s="6">
-        <v>2.8950316815924002</v>
+        <v>2.9381324785737402</v>
       </c>
       <c r="D80" s="6">
         <v>3.0178459536933899</v>
@@ -5433,16 +5433,16 @@
         <v>3.024132587032248</v>
       </c>
       <c r="F80" s="6">
-        <v>2.7617764397526798</v>
+        <v>2.2479990762508399</v>
       </c>
       <c r="G80" s="6">
-        <v>-0.13799792840436001</v>
+        <v>-0.115570650199797</v>
       </c>
       <c r="H80" s="6">
         <v>4.0422056193245397E-2</v>
       </c>
       <c r="I80" s="6">
-        <v>0.91531258049696895</v>
+        <v>0.94376860135609397</v>
       </c>
       <c r="J80" s="6">
         <v>7.50795760525682</v>
@@ -5483,10 +5483,10 @@
         <v>29495</v>
       </c>
       <c r="B81" s="6">
-        <v>2.4584420307740502</v>
+        <v>3.0117682343477101</v>
       </c>
       <c r="C81" s="6">
-        <v>2.9171542826293599</v>
+        <v>2.9432993205611102</v>
       </c>
       <c r="D81" s="6">
         <v>3.0220636228650002</v>
@@ -5495,16 +5495,16 @@
         <v>3.102210389680768</v>
       </c>
       <c r="F81" s="6">
-        <v>3.2147005999959202</v>
+        <v>2.31620628084409</v>
       </c>
       <c r="G81" s="6">
-        <v>-0.13065571679670801</v>
+        <v>-0.11266451148277599</v>
       </c>
       <c r="H81" s="6">
         <v>4.04942460590276E-2</v>
       </c>
       <c r="I81" s="6">
-        <v>0.86102528168316295</v>
+        <v>0.89552174964892395</v>
       </c>
       <c r="J81" s="6">
         <v>8.1169121361513401</v>
@@ -5545,10 +5545,10 @@
         <v>29587</v>
       </c>
       <c r="B82" s="6">
-        <v>2.57209133916668</v>
+        <v>3.09297911420696</v>
       </c>
       <c r="C82" s="6">
-        <v>2.9354169842526301</v>
+        <v>2.9466189056898999</v>
       </c>
       <c r="D82" s="6">
         <v>3.02445683321021</v>
@@ -5557,16 +5557,16 @@
         <v>3.1906394077346039</v>
       </c>
       <c r="F82" s="6">
-        <v>3.0996137752767399</v>
+        <v>1.8457707511861401</v>
       </c>
       <c r="G82" s="6">
-        <v>-0.117339754220372</v>
+        <v>-0.104940030106097</v>
       </c>
       <c r="H82" s="6">
         <v>4.04033571084704E-2</v>
       </c>
       <c r="I82" s="6">
-        <v>0.83977122674203197</v>
+        <v>0.86168929852811205</v>
       </c>
       <c r="J82" s="6">
         <v>7.8268891519972703</v>
@@ -5607,10 +5607,10 @@
         <v>29677</v>
       </c>
       <c r="B83" s="6">
-        <v>2.47934789130503</v>
+        <v>2.9947629344020901</v>
       </c>
       <c r="C83" s="6">
-        <v>2.9554799979436202</v>
+        <v>2.9510877838843799</v>
       </c>
       <c r="D83" s="6">
         <v>3.0277386727759898</v>
@@ -5619,16 +5619,16 @@
         <v>3.1535854123334639</v>
       </c>
       <c r="F83" s="6">
-        <v>0.87414131843360099</v>
+        <v>0.46139844418689802</v>
       </c>
       <c r="G83" s="6">
-        <v>-0.13615401889373699</v>
+        <v>-0.11685793234936701</v>
       </c>
       <c r="H83" s="6">
         <v>4.02570449993171E-2</v>
       </c>
       <c r="I83" s="6">
-        <v>0.97428731149692305</v>
+        <v>0.96712681089611596</v>
       </c>
       <c r="J83" s="6">
         <v>6.5490458568081804</v>
@@ -5669,10 +5669,10 @@
         <v>29768</v>
       </c>
       <c r="B84" s="6">
-        <v>2.7744261339286398</v>
+        <v>3.1719224773476502</v>
       </c>
       <c r="C84" s="6">
-        <v>2.9661571769339599</v>
+        <v>2.9522037203046398</v>
       </c>
       <c r="D84" s="6">
         <v>3.0277236941151799</v>
@@ -5681,16 +5681,16 @@
         <v>3.3243270786749681</v>
       </c>
       <c r="F84" s="6">
-        <v>-0.57359711934827795</v>
+        <v>-0.99238652018925699</v>
       </c>
       <c r="G84" s="6">
-        <v>-6.4116495414240707E-2</v>
+        <v>-7.6350245452465895E-2</v>
       </c>
       <c r="H84" s="6">
         <v>4.02460397617131E-2</v>
       </c>
       <c r="I84" s="6">
-        <v>0.94047068211830098</v>
+        <v>0.92672049484801999</v>
       </c>
       <c r="J84" s="6">
         <v>6.3939943984710697</v>
@@ -5731,10 +5731,10 @@
         <v>29860</v>
       </c>
       <c r="B85" s="6">
-        <v>2.6997438277529202</v>
+        <v>3.0976197383747701</v>
       </c>
       <c r="C85" s="6">
-        <v>2.9792044552120398</v>
+        <v>2.95557883276068</v>
       </c>
       <c r="D85" s="6">
         <v>3.0295186438725699</v>
@@ -5743,16 +5743,16 @@
         <v>3.2771374466044598</v>
       </c>
       <c r="F85" s="6">
-        <v>-2.3940192620279999</v>
+        <v>-2.3200317354254598</v>
       </c>
       <c r="G85" s="6">
-        <v>-7.2399510956757798E-2</v>
+        <v>-8.5302590876475307E-2</v>
       </c>
       <c r="H85" s="6">
         <v>4.0263558698614199E-2</v>
       </c>
       <c r="I85" s="6">
-        <v>0.89592073463424704</v>
+        <v>0.878758962201588</v>
       </c>
       <c r="J85" s="6">
         <v>5.9940805794598102</v>
@@ -5793,10 +5793,10 @@
         <v>29952</v>
       </c>
       <c r="B86" s="6">
-        <v>2.5801856824432399</v>
+        <v>2.9379208797910201</v>
       </c>
       <c r="C86" s="6">
-        <v>2.9966988793107099</v>
+        <v>2.9619932249197101</v>
       </c>
       <c r="D86" s="6">
         <v>3.0337877607578898</v>
@@ -5805,16 +5805,16 @@
         <v>3.18541914268142</v>
       </c>
       <c r="F86" s="6">
-        <v>-5.0530945359205903</v>
+        <v>-4.0687272222022601</v>
       </c>
       <c r="G86" s="6">
-        <v>-8.5647389623420306E-2</v>
+        <v>-0.103526712074767</v>
       </c>
       <c r="H86" s="6">
         <v>4.0416457493298898E-2</v>
       </c>
       <c r="I86" s="6">
-        <v>0.99185072571629396</v>
+        <v>0.97470285132608803</v>
       </c>
       <c r="J86" s="6">
         <v>4.7613733460834098</v>
@@ -5855,10 +5855,10 @@
         <v>30042</v>
       </c>
       <c r="B87" s="6">
-        <v>2.6836057871413801</v>
+        <v>2.9957646063733399</v>
       </c>
       <c r="C87" s="6">
-        <v>3.01012193482546</v>
+        <v>2.9667514147549499</v>
       </c>
       <c r="D87" s="6">
         <v>3.03634323690819</v>
@@ -5867,16 +5867,16 @@
         <v>3.2607146475420881</v>
       </c>
       <c r="F87" s="6">
-        <v>-6.5717543449970304</v>
+        <v>-5.4552968756888696</v>
       </c>
       <c r="G87" s="6">
-        <v>-7.2838728538596895E-2</v>
+        <v>-9.0879821409286701E-2</v>
       </c>
       <c r="H87" s="6">
         <v>4.0559750841283999E-2</v>
       </c>
       <c r="I87" s="6">
-        <v>0.94399170444766001</v>
+        <v>0.93047511020316298</v>
       </c>
       <c r="J87" s="6">
         <v>4.4859023393965796</v>
@@ -5917,10 +5917,10 @@
         <v>30133</v>
       </c>
       <c r="B88" s="6">
-        <v>2.6359769685539698</v>
+        <v>2.98899740376579</v>
       </c>
       <c r="C88" s="6">
-        <v>3.0262025278418601</v>
+        <v>2.97227939821697</v>
       </c>
       <c r="D88" s="6">
         <v>3.03962833223436</v>
@@ -5929,16 +5929,16 @@
         <v>3.2321404868680559</v>
       </c>
       <c r="F88" s="6">
-        <v>-7.06099006746319</v>
+        <v>-6.1959338319188699</v>
       </c>
       <c r="G88" s="6">
-        <v>-7.8966515561483805E-2</v>
+        <v>-9.5285856685312198E-2</v>
       </c>
       <c r="H88" s="6">
         <v>4.0397531993454597E-2</v>
       </c>
       <c r="I88" s="6">
-        <v>0.881036347169465</v>
+        <v>0.87980183414232904</v>
       </c>
       <c r="J88" s="6">
         <v>4.9366133736632101</v>
@@ -5979,10 +5979,10 @@
         <v>30225</v>
       </c>
       <c r="B89" s="6">
-        <v>2.6361181347664999</v>
+        <v>2.9784466415985</v>
       </c>
       <c r="C89" s="6">
-        <v>3.0435025413712</v>
+        <v>2.9772911104473798</v>
       </c>
       <c r="D89" s="6">
         <v>3.0425677198984902</v>
@@ -5991,16 +5991,16 @@
         <v>3.2357700886073282</v>
       </c>
       <c r="F89" s="6">
-        <v>-8.0585109744404804</v>
+        <v>-7.1436432293260204</v>
       </c>
       <c r="G89" s="6">
-        <v>-7.8229465596067499E-2</v>
+        <v>-9.4392062972505797E-2</v>
       </c>
       <c r="H89" s="6">
         <v>4.0530050756970797E-2</v>
       </c>
       <c r="I89" s="6">
-        <v>0.81783580702908598</v>
+        <v>0.82023921042214298</v>
       </c>
       <c r="J89" s="6">
         <v>4.3121664622519296</v>
@@ -6041,10 +6041,10 @@
         <v>30317</v>
       </c>
       <c r="B90" s="6">
-        <v>2.86079030597107</v>
+        <v>3.1070362953839701</v>
       </c>
       <c r="C90" s="6">
-        <v>3.0532985987091399</v>
+        <v>2.9777331937539202</v>
       </c>
       <c r="D90" s="6">
         <v>3.0417631073797899</v>
@@ -6053,16 +6053,16 @@
         <v>3.3511798725040278</v>
       </c>
       <c r="F90" s="6">
-        <v>-8.5233014280302708</v>
+        <v>-7.4989059394002897</v>
       </c>
       <c r="G90" s="6">
-        <v>-6.8650176234281393E-2</v>
+        <v>-8.6495802310078196E-2</v>
       </c>
       <c r="H90" s="6">
         <v>4.0587531840206102E-2</v>
       </c>
       <c r="I90" s="6">
-        <v>0.75467870669376802</v>
+        <v>0.75977706406657697</v>
       </c>
       <c r="J90" s="6">
         <v>4.1272062600250301</v>
@@ -6103,10 +6103,10 @@
         <v>30407</v>
       </c>
       <c r="B91" s="6">
-        <v>3.0612517167033899</v>
+        <v>3.1633113305296798</v>
       </c>
       <c r="C91" s="6">
-        <v>3.0530441521020202</v>
+        <v>2.9725611428882202</v>
       </c>
       <c r="D91" s="6">
         <v>3.0365419867912302</v>
@@ -6115,16 +6115,16 @@
         <v>3.4913295817835439</v>
       </c>
       <c r="F91" s="6">
-        <v>-9.9884255727376399</v>
+        <v>-8.1199857653762102</v>
       </c>
       <c r="G91" s="6">
-        <v>-6.47782548428016E-2</v>
+        <v>-8.2833062046233905E-2</v>
       </c>
       <c r="H91" s="6">
         <v>4.1639993751988999E-2</v>
       </c>
       <c r="I91" s="6">
-        <v>1.1088587971066</v>
+        <v>1.14015341388979</v>
       </c>
       <c r="J91" s="6">
         <v>3.1681433647446799</v>
@@ -6165,10 +6165,10 @@
         <v>30498</v>
       </c>
       <c r="B92" s="6">
-        <v>3.15300744943527</v>
+        <v>3.2615188459758202</v>
       </c>
       <c r="C92" s="6">
-        <v>3.0501876535726899</v>
+        <v>2.9653533142933002</v>
       </c>
       <c r="D92" s="6">
         <v>3.0299346830905498</v>
@@ -6177,16 +6177,16 @@
         <v>3.5261779965764002</v>
       </c>
       <c r="F92" s="6">
-        <v>-8.2959298596213706</v>
+        <v>-6.9782809989924299</v>
       </c>
       <c r="G92" s="6">
-        <v>-6.38501066879337E-2</v>
+        <v>-8.1816273124502903E-2</v>
       </c>
       <c r="H92" s="6">
         <v>4.1129396462225097E-2</v>
       </c>
       <c r="I92" s="6">
-        <v>1.3067970045095201</v>
+        <v>1.3415852170948399</v>
       </c>
       <c r="J92" s="6">
         <v>4.3789801979651601</v>
@@ -6227,10 +6227,10 @@
         <v>30590</v>
       </c>
       <c r="B93" s="6">
-        <v>3.24219465112022</v>
+        <v>3.2919578234236102</v>
       </c>
       <c r="C93" s="6">
-        <v>3.04283165774044</v>
+        <v>2.9553708833005898</v>
       </c>
       <c r="D93" s="6">
         <v>3.02098357257419</v>
@@ -6239,16 +6239,16 @@
         <v>3.5859619740238959</v>
       </c>
       <c r="F93" s="6">
-        <v>-8.1642836901895102</v>
+        <v>-6.5622630989497601</v>
       </c>
       <c r="G93" s="6">
-        <v>-6.1225744736795297E-2</v>
+        <v>-7.8965212810710603E-2</v>
       </c>
       <c r="H93" s="6">
         <v>4.1396299225506798E-2</v>
       </c>
       <c r="I93" s="6">
-        <v>1.3103485932974199</v>
+        <v>1.35995965239515</v>
       </c>
       <c r="J93" s="6">
         <v>3.3576818276627298</v>
@@ -6289,10 +6289,10 @@
         <v>30682</v>
       </c>
       <c r="B94" s="6">
-        <v>3.34291865029159</v>
+        <v>3.3585156389457498</v>
       </c>
       <c r="C94" s="6">
-        <v>3.0307213131061199</v>
+        <v>2.9426459214132201</v>
       </c>
       <c r="D94" s="6">
         <v>3.00967416378935</v>
@@ -6301,16 +6301,16 @@
         <v>3.645192554301504</v>
       </c>
       <c r="F94" s="6">
-        <v>-7.5167604738732097</v>
+        <v>-5.9034171639825699</v>
       </c>
       <c r="G94" s="6">
-        <v>-5.8069560930856801E-2</v>
+        <v>-7.5311209574479204E-2</v>
       </c>
       <c r="H94" s="6">
         <v>4.1338526296741201E-2</v>
       </c>
       <c r="I94" s="6">
-        <v>1.15895861599113</v>
+        <v>1.20293301078565</v>
       </c>
       <c r="J94" s="6">
         <v>3.0022462719748102</v>
@@ -6351,10 +6351,10 @@
         <v>30773</v>
       </c>
       <c r="B95" s="6">
-        <v>3.4289095272526802</v>
+        <v>3.4236117190972402</v>
       </c>
       <c r="C95" s="6">
-        <v>3.0137076821852502</v>
+        <v>2.92753996855184</v>
       </c>
       <c r="D95" s="6">
         <v>2.9963281058906799</v>
@@ -6363,16 +6363,16 @@
         <v>3.6932136496612999</v>
       </c>
       <c r="F95" s="6">
-        <v>-6.7305789696126199</v>
+        <v>-5.30738188851217</v>
       </c>
       <c r="G95" s="6">
-        <v>-5.5196014679776501E-2</v>
+        <v>-7.1841690649901396E-2</v>
       </c>
       <c r="H95" s="6">
         <v>4.1215129826901703E-2</v>
       </c>
       <c r="I95" s="6">
-        <v>1.0747875172482</v>
+        <v>1.1084832931178099</v>
       </c>
       <c r="J95" s="6">
         <v>3.5278225411684998</v>
@@ -6413,10 +6413,10 @@
         <v>30864</v>
       </c>
       <c r="B96" s="6">
-        <v>3.3489878429103599</v>
+        <v>3.3755165397055999</v>
       </c>
       <c r="C96" s="6">
-        <v>2.9992925680173301</v>
+        <v>2.91309143676891</v>
       </c>
       <c r="D96" s="6">
         <v>2.9834270655499102</v>
@@ -6425,16 +6425,16 @@
         <v>3.6635442113885319</v>
       </c>
       <c r="F96" s="6">
-        <v>-6.5571672140065997</v>
+        <v>-5.15112329131534</v>
       </c>
       <c r="G96" s="6">
-        <v>-5.8213153664410801E-2</v>
+        <v>-7.46649772512777E-2</v>
       </c>
       <c r="H96" s="6">
         <v>4.1308847692834903E-2</v>
       </c>
       <c r="I96" s="6">
-        <v>0.97825374980341095</v>
+        <v>1.01313271290569</v>
       </c>
       <c r="J96" s="6">
         <v>2.6986539973978898</v>
@@ -6475,10 +6475,10 @@
         <v>30956</v>
       </c>
       <c r="B97" s="6">
-        <v>3.3042700107012402</v>
+        <v>3.3422149564209098</v>
       </c>
       <c r="C97" s="6">
-        <v>2.98557461847953</v>
+        <v>2.8982165191934302</v>
       </c>
       <c r="D97" s="6">
         <v>2.9700559425754398</v>
@@ -6487,16 +6487,16 @@
         <v>3.6581221255006882</v>
       </c>
       <c r="F97" s="6">
-        <v>-6.9363139080496099</v>
+        <v>-5.3453702936415102</v>
       </c>
       <c r="G97" s="6">
-        <v>-6.01169180529567E-2</v>
+        <v>-7.5995914035260195E-2</v>
       </c>
       <c r="H97" s="6">
         <v>4.1443286748202801E-2</v>
       </c>
       <c r="I97" s="6">
-        <v>0.91453968059871904</v>
+        <v>0.95027648250598296</v>
       </c>
       <c r="J97" s="6">
         <v>1.8819175003708</v>
@@ -6537,10 +6537,10 @@
         <v>31048</v>
       </c>
       <c r="B98" s="6">
-        <v>3.4091973964717401</v>
+        <v>3.45140042962815</v>
       </c>
       <c r="C98" s="6">
-        <v>2.9674185803442898</v>
+        <v>2.8808841911099701</v>
       </c>
       <c r="D98" s="6">
         <v>2.9546878642874099</v>
@@ -6549,16 +6549,16 @@
         <v>3.6898111021048678</v>
       </c>
       <c r="F98" s="6">
-        <v>-5.9666939358721702</v>
+        <v>-4.9344351808638303</v>
       </c>
       <c r="G98" s="6">
-        <v>-5.6356399680957001E-2</v>
+        <v>-7.2078582223175605E-2</v>
       </c>
       <c r="H98" s="6">
         <v>4.0963939701170203E-2</v>
       </c>
       <c r="I98" s="6">
-        <v>1.26866859779644</v>
+        <v>1.2857557984125101</v>
       </c>
       <c r="J98" s="6">
         <v>3.04428960770734</v>
@@ -6599,10 +6599,10 @@
         <v>31138</v>
       </c>
       <c r="B99" s="6">
-        <v>3.37280312704898</v>
+        <v>3.4259687576736599</v>
       </c>
       <c r="C99" s="6">
-        <v>2.9497302132530101</v>
+        <v>2.8625452229972299</v>
       </c>
       <c r="D99" s="6">
         <v>2.93855542158418</v>
@@ -6611,16 +6611,16 @@
         <v>3.6866149814987721</v>
       </c>
       <c r="F99" s="6">
-        <v>-6.2592344701986899</v>
+        <v>-5.0862214981929101</v>
       </c>
       <c r="G99" s="6">
-        <v>-5.6803859168718003E-2</v>
+        <v>-7.2263712105614802E-2</v>
       </c>
       <c r="H99" s="6">
         <v>4.1079696243823099E-2</v>
       </c>
       <c r="I99" s="6">
-        <v>1.16190728106548</v>
+        <v>1.18953005743292</v>
       </c>
       <c r="J99" s="6">
         <v>2.36349542893092</v>
@@ -6661,10 +6661,10 @@
         <v>31229</v>
       </c>
       <c r="B100" s="6">
-        <v>3.5881013827819999</v>
+        <v>3.5412520891592498</v>
       </c>
       <c r="C100" s="6">
-        <v>2.9148457579322198</v>
+        <v>2.8384220476206301</v>
       </c>
       <c r="D100" s="6">
         <v>2.9181989961741102</v>
@@ -6673,16 +6673,16 @@
         <v>3.7787418041815362</v>
       </c>
       <c r="F100" s="6">
-        <v>-6.2177044811678002</v>
+        <v>-5.0042101952783504</v>
       </c>
       <c r="G100" s="6">
-        <v>-5.2622942305309901E-2</v>
+        <v>-6.8757134497129696E-2</v>
       </c>
       <c r="H100" s="6">
         <v>4.0998657634003899E-2</v>
       </c>
       <c r="I100" s="6">
-        <v>1.05331069682069</v>
+        <v>1.0784588908070101</v>
       </c>
       <c r="J100" s="6">
         <v>2.8533953406561801</v>
@@ -6723,10 +6723,10 @@
         <v>31321</v>
       </c>
       <c r="B101" s="6">
-        <v>3.4144240412987998</v>
+        <v>3.4377022474269698</v>
       </c>
       <c r="C101" s="6">
-        <v>2.8869495093167599</v>
+        <v>2.8167023683400201</v>
       </c>
       <c r="D101" s="6">
         <v>2.89955374372376</v>
@@ -6735,16 +6735,16 @@
         <v>3.707563374468636</v>
       </c>
       <c r="F101" s="6">
-        <v>-6.1370481790865501</v>
+        <v>-4.8558826661508201</v>
       </c>
       <c r="G101" s="6">
-        <v>-5.48678130447861E-2</v>
+        <v>-7.0854264627506103E-2</v>
       </c>
       <c r="H101" s="6">
         <v>4.11364631671342E-2</v>
       </c>
       <c r="I101" s="6">
-        <v>0.99014797339182803</v>
+        <v>1.0186494031390201</v>
       </c>
       <c r="J101" s="6">
         <v>1.9679236636442199</v>
@@ -6785,10 +6785,10 @@
         <v>31413</v>
       </c>
       <c r="B102" s="6">
-        <v>3.41434117288915</v>
+        <v>3.44573926093405</v>
       </c>
       <c r="C102" s="6">
-        <v>2.8575662440834799</v>
+        <v>2.7950336529194701</v>
       </c>
       <c r="D102" s="6">
         <v>2.8808656299967002</v>
@@ -6797,16 +6797,16 @@
         <v>3.6880338572693558</v>
       </c>
       <c r="F102" s="6">
-        <v>-5.7092331806731504</v>
+        <v>-4.5140732891369497</v>
       </c>
       <c r="G102" s="6">
-        <v>-5.5228634985801897E-2</v>
+        <v>-7.1467458721787003E-2</v>
       </c>
       <c r="H102" s="6">
         <v>4.0960421509822299E-2</v>
       </c>
       <c r="I102" s="6">
-        <v>0.96373608290638102</v>
+        <v>0.99207827994640096</v>
       </c>
       <c r="J102" s="6">
         <v>2.76069321322574</v>
@@ -6847,10 +6847,10 @@
         <v>31503</v>
       </c>
       <c r="B103" s="6">
-        <v>3.2070535141966801</v>
+        <v>3.3058739734954998</v>
       </c>
       <c r="C103" s="6">
-        <v>2.8383043854273202</v>
+        <v>2.7771957799328102</v>
       </c>
       <c r="D103" s="6">
         <v>2.8648731006235799</v>
@@ -6859,16 +6859,16 @@
         <v>3.593388582447044</v>
       </c>
       <c r="F103" s="6">
-        <v>-5.9831912335161004</v>
+        <v>-4.5674462224997097</v>
       </c>
       <c r="G103" s="6">
-        <v>-5.95347165397812E-2</v>
+        <v>-7.5623132483484304E-2</v>
       </c>
       <c r="H103" s="6">
         <v>4.11280920908575E-2</v>
       </c>
       <c r="I103" s="6">
-        <v>0.93727146599968703</v>
+        <v>0.97084600164317203</v>
       </c>
       <c r="J103" s="6">
         <v>1.8079848651416599</v>
@@ -6909,10 +6909,10 @@
         <v>31594</v>
       </c>
       <c r="B104" s="6">
-        <v>3.2230211588861302</v>
+        <v>3.30187874115075</v>
       </c>
       <c r="C104" s="6">
-        <v>2.8150774729327401</v>
+        <v>2.7584981556052801</v>
       </c>
       <c r="D104" s="6">
         <v>2.8482058843740998</v>
@@ -6921,16 +6921,16 @@
         <v>3.5958918111298241</v>
       </c>
       <c r="F104" s="6">
-        <v>-6.1069107644646001</v>
+        <v>-4.5643204998170903</v>
       </c>
       <c r="G104" s="6">
-        <v>-5.8839925440285601E-2</v>
+        <v>-7.5389348451822699E-2</v>
       </c>
       <c r="H104" s="6">
         <v>4.11643932858533E-2</v>
       </c>
       <c r="I104" s="6">
-        <v>0.85263100192385799</v>
+        <v>0.88424658141469203</v>
       </c>
       <c r="J104" s="6">
         <v>1.5955926161018299</v>
@@ -6971,10 +6971,10 @@
         <v>31686</v>
       </c>
       <c r="B105" s="6">
-        <v>3.09207045641547</v>
+        <v>3.2239807623271002</v>
       </c>
       <c r="C105" s="6">
-        <v>2.8003131502222698</v>
+        <v>2.7431234855154401</v>
       </c>
       <c r="D105" s="6">
         <v>2.8339482095564401</v>
@@ -6983,16 +6983,16 @@
         <v>3.51131279490756</v>
       </c>
       <c r="F105" s="6">
-        <v>-5.76785823429719</v>
+        <v>-4.3202250499135699</v>
       </c>
       <c r="G105" s="6">
-        <v>-5.9860708706948401E-2</v>
+        <v>-7.6182891825939597E-2</v>
       </c>
       <c r="H105" s="6">
         <v>4.1063805062390997E-2</v>
       </c>
       <c r="I105" s="6">
-        <v>0.79994358130445398</v>
+        <v>0.82849757987694606</v>
       </c>
       <c r="J105" s="6">
         <v>1.9883646759206901</v>
@@ -7033,10 +7033,10 @@
         <v>31778</v>
       </c>
       <c r="B106" s="6">
-        <v>3.01993075951059</v>
+        <v>3.1550295071398602</v>
       </c>
       <c r="C106" s="6">
-        <v>2.7883827399449701</v>
+        <v>2.7288521110962001</v>
       </c>
       <c r="D106" s="6">
         <v>2.82051244429426</v>
@@ -7045,16 +7045,16 @@
         <v>3.4720131495409601</v>
       </c>
       <c r="F106" s="6">
-        <v>-5.9695328126026697</v>
+        <v>-4.3458748698507197</v>
       </c>
       <c r="G106" s="6">
-        <v>-5.9912221013677103E-2</v>
+        <v>-7.6246950048722506E-2</v>
       </c>
       <c r="H106" s="6">
         <v>4.1186513283411198E-2</v>
       </c>
       <c r="I106" s="6">
-        <v>0.75754567525521999</v>
+        <v>0.78710371891552</v>
       </c>
       <c r="J106" s="6">
         <v>1.4458625449123099</v>
@@ -7095,10 +7095,10 @@
         <v>31868</v>
       </c>
       <c r="B107" s="6">
-        <v>3.1344468910458301</v>
+        <v>3.2353947531507798</v>
       </c>
       <c r="C107" s="6">
-        <v>2.7719721445122301</v>
+        <v>2.7130649242849398</v>
       </c>
       <c r="D107" s="6">
         <v>2.8060268900446599</v>
@@ -7107,16 +7107,16 @@
         <v>3.480587640445632</v>
       </c>
       <c r="F107" s="6">
-        <v>-5.1337954990104899</v>
+        <v>-3.8366396076462501</v>
       </c>
       <c r="G107" s="6">
-        <v>-5.9183376246416702E-2</v>
+        <v>-7.5930372537693802E-2</v>
       </c>
       <c r="H107" s="6">
         <v>4.0843552612969902E-2</v>
       </c>
       <c r="I107" s="6">
-        <v>0.88255854803595102</v>
+        <v>0.89881658663141595</v>
       </c>
       <c r="J107" s="6">
         <v>2.3476501462536299</v>
@@ -7157,10 +7157,10 @@
         <v>31959</v>
       </c>
       <c r="B108" s="6">
-        <v>3.09472801435136</v>
+        <v>3.2079127091518602</v>
       </c>
       <c r="C108" s="6">
-        <v>2.7596008580281901</v>
+        <v>2.6976378391957501</v>
       </c>
       <c r="D108" s="6">
         <v>2.7918680962709099</v>
@@ -7169,16 +7169,16 @@
         <v>3.4477689663593121</v>
       </c>
       <c r="F108" s="6">
-        <v>-4.8625845785882698</v>
+        <v>-3.6174987145258202</v>
       </c>
       <c r="G108" s="6">
-        <v>-5.9623725818729698E-2</v>
+        <v>-7.6483416294528705E-2</v>
       </c>
       <c r="H108" s="6">
         <v>4.0804283870319299E-2</v>
       </c>
       <c r="I108" s="6">
-        <v>0.81246874213972597</v>
+        <v>0.82747144090088198</v>
       </c>
       <c r="J108" s="6">
         <v>2.4053901645228501</v>
@@ -7219,10 +7219,10 @@
         <v>32051</v>
       </c>
       <c r="B109" s="6">
-        <v>3.4207780914353698</v>
+        <v>3.3938427413466798</v>
       </c>
       <c r="C109" s="6">
-        <v>2.7218136062098299</v>
+        <v>2.6744045089386699</v>
       </c>
       <c r="D109" s="6">
         <v>2.7722888868761202</v>
@@ -7231,16 +7231,16 @@
         <v>3.5690352449221558</v>
       </c>
       <c r="F109" s="6">
-        <v>-4.4558940629827397</v>
+        <v>-3.24934312810558</v>
       </c>
       <c r="G109" s="6">
-        <v>-5.5324250928910398E-2</v>
+        <v>-7.31474864004069E-2</v>
       </c>
       <c r="H109" s="6">
         <v>4.06453845852245E-2</v>
       </c>
       <c r="I109" s="6">
-        <v>0.80608208854280705</v>
+        <v>0.81550342822575395</v>
       </c>
       <c r="J109" s="6">
         <v>2.8162249488157598</v>
@@ -7281,10 +7281,10 @@
         <v>32143</v>
       </c>
       <c r="B110" s="6">
-        <v>3.2942635917403802</v>
+        <v>3.2993351100930401</v>
       </c>
       <c r="C110" s="6">
-        <v>2.6934558792394601</v>
+        <v>2.6549452639822801</v>
       </c>
       <c r="D110" s="6">
         <v>2.7554943863314798</v>
@@ -7293,16 +7293,16 @@
         <v>3.477425921068412</v>
       </c>
       <c r="F110" s="6">
-        <v>-4.1680169081850504</v>
+        <v>-2.9808716167998499</v>
       </c>
       <c r="G110" s="6">
-        <v>-5.6600619189203102E-2</v>
+        <v>-7.4848704789016202E-2</v>
       </c>
       <c r="H110" s="6">
         <v>4.0611563086197101E-2</v>
       </c>
       <c r="I110" s="6">
-        <v>0.748044383130966</v>
+        <v>0.75780181875429398</v>
       </c>
       <c r="J110" s="6">
         <v>2.66065004392344</v>
@@ -7343,10 +7343,10 @@
         <v>32234</v>
       </c>
       <c r="B111" s="6">
-        <v>3.4067585882841902</v>
+        <v>3.3975303081413699</v>
       </c>
       <c r="C111" s="6">
-        <v>2.6591862906496799</v>
+        <v>2.6328693449469101</v>
       </c>
       <c r="D111" s="6">
         <v>2.7367416609988502</v>
@@ -7355,16 +7355,16 @@
         <v>3.5133138535680359</v>
       </c>
       <c r="F111" s="6">
-        <v>-3.4231058799065299</v>
+        <v>-2.51047816479036</v>
       </c>
       <c r="G111" s="6">
-        <v>-5.6451235702836403E-2</v>
+        <v>-7.4619537293243901E-2</v>
       </c>
       <c r="H111" s="6">
         <v>4.0406645839472899E-2</v>
       </c>
       <c r="I111" s="6">
-        <v>0.80955906228429098</v>
+        <v>0.81570265834571898</v>
       </c>
       <c r="J111" s="6">
         <v>3.3887786584883099</v>
@@ -7405,10 +7405,10 @@
         <v>32325</v>
       </c>
       <c r="B112" s="6">
-        <v>3.3193446520883398</v>
+        <v>3.3305353676961902</v>
       </c>
       <c r="C112" s="6">
-        <v>2.63150790819213</v>
+        <v>2.6132710262751302</v>
       </c>
       <c r="D112" s="6">
         <v>2.7198851839486702</v>
@@ -7417,16 +7417,16 @@
         <v>3.4435106006121039</v>
       </c>
       <c r="F112" s="6">
-        <v>-3.2144667510132199</v>
+        <v>-2.3397397211307398</v>
       </c>
       <c r="G112" s="6">
-        <v>-5.61901282592389E-2</v>
+        <v>-7.4300591779158195E-2</v>
       </c>
       <c r="H112" s="6">
         <v>4.0376253722258303E-2</v>
       </c>
       <c r="I112" s="6">
-        <v>0.75229867081357304</v>
+        <v>0.75910422827704005</v>
       </c>
       <c r="J112" s="6">
         <v>3.3567776289296898</v>
@@ -7467,10 +7467,10 @@
         <v>32417</v>
       </c>
       <c r="B113" s="6">
-        <v>3.4136203141063</v>
+        <v>3.3957893491912601</v>
       </c>
       <c r="C113" s="6">
-        <v>2.59620084543227</v>
+        <v>2.5901136245489602</v>
       </c>
       <c r="D113" s="6">
         <v>2.7003756765874201</v>
@@ -7479,16 +7479,16 @@
         <v>3.495320298099152</v>
       </c>
       <c r="F113" s="6">
-        <v>-3.0280882565776301</v>
+        <v>-2.1517919170831901</v>
       </c>
       <c r="G113" s="6">
-        <v>-5.5268577223495499E-2</v>
+        <v>-7.3218282917170793E-2</v>
       </c>
       <c r="H113" s="6">
         <v>4.0355940147678501E-2</v>
       </c>
       <c r="I113" s="6">
-        <v>0.70040095231170896</v>
+        <v>0.70879998706408898</v>
       </c>
       <c r="J113" s="6">
         <v>3.3271245999172399</v>
@@ -7529,10 +7529,10 @@
         <v>32509</v>
       </c>
       <c r="B114" s="6">
-        <v>3.4095316296102798</v>
+        <v>3.39726436227784</v>
       </c>
       <c r="C114" s="6">
-        <v>2.5592660897753601</v>
+        <v>2.5658627559385399</v>
       </c>
       <c r="D114" s="6">
         <v>2.6800665455380801</v>
@@ -7541,16 +7541,16 @@
         <v>3.4966563300860121</v>
       </c>
       <c r="F114" s="6">
-        <v>-2.90173686242463</v>
+        <v>-2.02328268507961</v>
       </c>
       <c r="G114" s="6">
-        <v>-5.5254603178307403E-2</v>
+        <v>-7.3024340322826703E-2</v>
       </c>
       <c r="H114" s="6">
         <v>4.0354413514568303E-2</v>
       </c>
       <c r="I114" s="6">
-        <v>0.65495773810840496</v>
+        <v>0.665278789056859</v>
       </c>
       <c r="J114" s="6">
         <v>3.2014094004074098</v>
@@ -7591,10 +7591,10 @@
         <v>32599</v>
       </c>
       <c r="B115" s="6">
-        <v>3.3217670575932399</v>
+        <v>3.3259137061653798</v>
       </c>
       <c r="C115" s="6">
-        <v>2.52328645961274</v>
+        <v>2.5415341240937499</v>
       </c>
       <c r="D115" s="6">
         <v>2.6596963620310898</v>
@@ -7603,16 +7603,16 @@
         <v>3.4780078698066919</v>
       </c>
       <c r="F115" s="6">
-        <v>-3.3855388961510999</v>
+        <v>-2.2549948353106402</v>
       </c>
       <c r="G115" s="6">
-        <v>-5.6800099795130399E-2</v>
+        <v>-7.4492362074056406E-2</v>
       </c>
       <c r="H115" s="6">
         <v>4.0479506875384597E-2</v>
       </c>
       <c r="I115" s="6">
-        <v>0.67005131581080002</v>
+        <v>0.68379301990652996</v>
       </c>
       <c r="J115" s="6">
         <v>2.4863867796839099</v>
@@ -7653,10 +7653,10 @@
         <v>32690</v>
       </c>
       <c r="B116" s="6">
-        <v>3.2561981218532798</v>
+        <v>3.2703320082624701</v>
       </c>
       <c r="C116" s="6">
-        <v>2.4848977058261701</v>
+        <v>2.5160395797462298</v>
       </c>
       <c r="D116" s="6">
         <v>2.6384648055116902</v>
@@ -7665,16 +7665,16 @@
         <v>3.4800254732292921</v>
       </c>
       <c r="F116" s="6">
-        <v>-4.0418868168017603</v>
+        <v>-2.6426034482413998</v>
       </c>
       <c r="G116" s="6">
-        <v>-5.7607444623486902E-2</v>
+        <v>-7.4504634869901998E-2</v>
       </c>
       <c r="H116" s="6">
         <v>4.0645441557925099E-2</v>
       </c>
       <c r="I116" s="6">
-        <v>0.71005183079044298</v>
+        <v>0.72435749497414403</v>
       </c>
       <c r="J116" s="6">
         <v>1.86137089373297</v>
@@ -7715,10 +7715,10 @@
         <v>32782</v>
       </c>
       <c r="B117" s="6">
-        <v>3.0750417354531598</v>
+        <v>3.1852717730660101</v>
       </c>
       <c r="C117" s="6">
-        <v>2.4578082869795299</v>
+        <v>2.4933965875264099</v>
       </c>
       <c r="D117" s="6">
         <v>2.6193173963166601</v>
@@ -7727,16 +7727,16 @@
         <v>3.3924721239645681</v>
       </c>
       <c r="F117" s="6">
-        <v>-4.0579953066887198</v>
+        <v>-2.7822787200065</v>
       </c>
       <c r="G117" s="6">
-        <v>-7.1401503259465204E-2</v>
+        <v>-8.6170972213171201E-2</v>
       </c>
       <c r="H117" s="6">
         <v>4.0578665658630997E-2</v>
       </c>
       <c r="I117" s="6">
-        <v>0.67254926767024503</v>
+        <v>0.68880003097633402</v>
       </c>
       <c r="J117" s="6">
         <v>2.3111615680964501</v>
@@ -7777,10 +7777,10 @@
         <v>32874</v>
       </c>
       <c r="B118" s="6">
-        <v>3.3132973000249102</v>
+        <v>3.3686409899555998</v>
       </c>
       <c r="C118" s="6">
-        <v>2.4150084811841399</v>
+        <v>2.46440399918911</v>
       </c>
       <c r="D118" s="6">
         <v>2.59575496567266</v>
@@ -7789,16 +7789,16 @@
         <v>3.47968261976464</v>
       </c>
       <c r="F118" s="6">
-        <v>-3.6825925092182401</v>
+        <v>-2.7217944561451799</v>
       </c>
       <c r="G118" s="6">
-        <v>-5.8052291875787497E-2</v>
+        <v>-7.3516868285025905E-2</v>
       </c>
       <c r="H118" s="6">
         <v>4.0338233655084398E-2</v>
       </c>
       <c r="I118" s="6">
-        <v>0.75092774050716704</v>
+        <v>0.760158013177477</v>
       </c>
       <c r="J118" s="6">
         <v>3.0996803600785099</v>
@@ -7839,10 +7839,10 @@
         <v>32964</v>
       </c>
       <c r="B119" s="6">
-        <v>3.2221932407310598</v>
+        <v>3.32366155063256</v>
       </c>
       <c r="C119" s="6">
-        <v>2.37642737239528</v>
+        <v>2.4375343851159998</v>
       </c>
       <c r="D119" s="6">
         <v>2.5737553357891398</v>
@@ -7851,16 +7851,16 @@
         <v>3.4224835097009878</v>
       </c>
       <c r="F119" s="6">
-        <v>-3.6669596410432099</v>
+        <v>-2.7993306957323498</v>
       </c>
       <c r="G119" s="6">
-        <v>-6.3236427753721403E-2</v>
+        <v>-7.8197331188854802E-2</v>
       </c>
       <c r="H119" s="6">
         <v>4.0265335786575797E-2</v>
       </c>
       <c r="I119" s="6">
-        <v>0.71719045577048002</v>
+        <v>0.724405856650985</v>
       </c>
       <c r="J119" s="6">
         <v>3.1760715507544899</v>
@@ -7901,10 +7901,10 @@
         <v>33055</v>
       </c>
       <c r="B120" s="6">
-        <v>3.0680867933662399</v>
+        <v>3.2141629783329599</v>
       </c>
       <c r="C120" s="6">
-        <v>2.3448827405214501</v>
+        <v>2.4150890109987602</v>
       </c>
       <c r="D120" s="6">
         <v>2.5549323398055099</v>
@@ -7913,16 +7913,16 @@
         <v>3.3338260100272241</v>
       </c>
       <c r="F120" s="6">
-        <v>-4.0000968429627601</v>
+        <v>-3.0970578647184102</v>
       </c>
       <c r="G120" s="6">
-        <v>-7.0887712544437195E-2</v>
+        <v>-8.5859710944096002E-2</v>
       </c>
       <c r="H120" s="6">
         <v>4.02736823726128E-2</v>
       </c>
       <c r="I120" s="6">
-        <v>0.66882893856025005</v>
+        <v>0.67843006560693597</v>
       </c>
       <c r="J120" s="6">
         <v>2.81326429022391</v>
@@ -7963,10 +7963,10 @@
         <v>33147</v>
       </c>
       <c r="B121" s="6">
-        <v>2.6853298774374998</v>
+        <v>2.9229399541721701</v>
       </c>
       <c r="C121" s="6">
-        <v>2.3350332288221298</v>
+        <v>2.4027142349864401</v>
       </c>
       <c r="D121" s="6">
         <v>2.5434943312786098</v>
@@ -7975,16 +7975,16 @@
         <v>3.1353677889135758</v>
       </c>
       <c r="F121" s="6">
-        <v>-5.0021170191425304</v>
+        <v>-3.8486808541077799</v>
       </c>
       <c r="G121" s="6">
-        <v>-9.4167617379458196E-2</v>
+        <v>-0.107412068279022</v>
       </c>
       <c r="H121" s="6">
         <v>4.0420238658137098E-2</v>
       </c>
       <c r="I121" s="6">
-        <v>0.66430020394521905</v>
+        <v>0.67537300420883095</v>
       </c>
       <c r="J121" s="6">
         <v>2.1199790127521498</v>
@@ -8025,10 +8025,10 @@
         <v>33239</v>
       </c>
       <c r="B122" s="6">
-        <v>2.6398569064074202</v>
+        <v>2.8670444132853601</v>
       </c>
       <c r="C122" s="6">
-        <v>2.3276562250506201</v>
+        <v>2.3918772251660201</v>
       </c>
       <c r="D122" s="6">
         <v>2.5333347765777501</v>
@@ -8037,16 +8037,16 @@
         <v>3.0966701404094081</v>
       </c>
       <c r="F122" s="6">
-        <v>-5.9750609107181303</v>
+        <v>-4.5991203591942202</v>
       </c>
       <c r="G122" s="6">
-        <v>-9.7545533364159207E-2</v>
+        <v>-0.11192202541754601</v>
       </c>
       <c r="H122" s="6">
         <v>4.0433079819836397E-2</v>
       </c>
       <c r="I122" s="6">
-        <v>0.62498559728722203</v>
+        <v>0.63733586780845797</v>
       </c>
       <c r="J122" s="6">
         <v>2.2762853096112901</v>
@@ -8087,10 +8087,10 @@
         <v>33329</v>
       </c>
       <c r="B123" s="6">
-        <v>2.66928051040263</v>
+        <v>2.87216364880936</v>
       </c>
       <c r="C123" s="6">
-        <v>2.3175480323351998</v>
+        <v>2.38000441093337</v>
       </c>
       <c r="D123" s="6">
         <v>2.5223428538989698</v>
@@ -8099,16 +8099,16 @@
         <v>3.1226037889993998</v>
       </c>
       <c r="F123" s="6">
-        <v>-6.41705417181731</v>
+        <v>-4.9218242958725096</v>
       </c>
       <c r="G123" s="6">
-        <v>-9.5181674629256904E-2</v>
+        <v>-0.11043606009517801</v>
       </c>
       <c r="H123" s="6">
         <v>4.0611964827663397E-2</v>
       </c>
       <c r="I123" s="6">
-        <v>0.60791566847874801</v>
+        <v>0.62264986565078195</v>
       </c>
       <c r="J123" s="6">
         <v>1.97887781023559</v>
@@ -8149,10 +8149,10 @@
         <v>33420</v>
       </c>
       <c r="B124" s="6">
-        <v>2.6601450352884801</v>
+        <v>2.86551243002955</v>
       </c>
       <c r="C124" s="6">
-        <v>2.30884286046106</v>
+        <v>2.3693404883742</v>
       </c>
       <c r="D124" s="6">
         <v>2.5124560923743</v>
@@ -8161,16 +8161,16 @@
         <v>3.0851804561159319</v>
       </c>
       <c r="F124" s="6">
-        <v>-6.1788995828418898</v>
+        <v>-4.8310842234828897</v>
       </c>
       <c r="G124" s="6">
-        <v>-9.5051745634667395E-2</v>
+        <v>-0.10989884254403801</v>
       </c>
       <c r="H124" s="6">
         <v>4.0381449236786097E-2</v>
       </c>
       <c r="I124" s="6">
-        <v>0.603254055373039</v>
+        <v>0.61727096946530502</v>
       </c>
       <c r="J124" s="6">
         <v>2.3194982344867898</v>
@@ -8211,10 +8211,10 @@
         <v>33512</v>
       </c>
       <c r="B125" s="6">
-        <v>2.5649218375450902</v>
+        <v>2.7690429098067701</v>
       </c>
       <c r="C125" s="6">
-        <v>2.3042472709708699</v>
+        <v>2.3609388981934001</v>
       </c>
       <c r="D125" s="6">
         <v>2.5046249035178398</v>
@@ -8223,16 +8223,16 @@
         <v>3.0176040704367679</v>
       </c>
       <c r="F125" s="6">
-        <v>-6.3802032912541904</v>
+        <v>-4.9663428258512603</v>
       </c>
       <c r="G125" s="6">
-        <v>-9.4351548755675294E-2</v>
+        <v>-0.10823780748834901</v>
       </c>
       <c r="H125" s="6">
         <v>4.0432283757956898E-2</v>
       </c>
       <c r="I125" s="6">
-        <v>0.57374893781731995</v>
+        <v>0.58920290642645501</v>
       </c>
       <c r="J125" s="6">
         <v>2.00861616375999</v>
@@ -8273,10 +8273,10 @@
         <v>33604</v>
       </c>
       <c r="B126" s="6">
-        <v>2.6548101957905499</v>
+        <v>2.8084822727901702</v>
       </c>
       <c r="C126" s="6">
-        <v>2.2950051605597399</v>
+        <v>2.35123128752842</v>
       </c>
       <c r="D126" s="6">
         <v>2.4957698494338398</v>
@@ -8285,16 +8285,16 @@
         <v>3.0429359648755478</v>
       </c>
       <c r="F126" s="6">
-        <v>-6.0836895197996901</v>
+        <v>-4.6596003318584298</v>
       </c>
       <c r="G126" s="6">
-        <v>-9.5687566115515599E-2</v>
+        <v>-0.109469626609578</v>
       </c>
       <c r="H126" s="6">
         <v>4.0420556095911803E-2</v>
       </c>
       <c r="I126" s="6">
-        <v>0.54828582968471795</v>
+        <v>0.56405909797770104</v>
       </c>
       <c r="J126" s="6">
         <v>1.98658890166921</v>
@@ -8335,10 +8335,10 @@
         <v>33695</v>
       </c>
       <c r="B127" s="6">
-        <v>2.6287340503946202</v>
+        <v>2.7660390043627499</v>
       </c>
       <c r="C127" s="6">
-        <v>2.2860980916601998</v>
+        <v>2.3426565414418499</v>
       </c>
       <c r="D127" s="6">
         <v>2.48778916691478</v>
@@ -8347,16 +8347,16 @@
         <v>3.0188338402146</v>
       </c>
       <c r="F127" s="6">
-        <v>-5.7545064157567403</v>
+        <v>-4.2779626562693203</v>
       </c>
       <c r="G127" s="6">
-        <v>-9.35607126882982E-2</v>
+        <v>-0.106054419644418</v>
       </c>
       <c r="H127" s="6">
         <v>4.0475403858868497E-2</v>
       </c>
       <c r="I127" s="6">
-        <v>0.52734687952913795</v>
+        <v>0.54408547787469597</v>
       </c>
       <c r="J127" s="6">
         <v>1.7714582869257101</v>
@@ -8397,10 +8397,10 @@
         <v>33786</v>
       </c>
       <c r="B128" s="6">
-        <v>2.5215196596185501</v>
+        <v>2.6499179142104801</v>
       </c>
       <c r="C128" s="6">
-        <v>2.2804196240768801</v>
+        <v>2.3368595107013901</v>
       </c>
       <c r="D128" s="6">
         <v>2.48184395214715</v>
@@ -8409,16 +8409,16 @@
         <v>2.9691788779117161</v>
       </c>
       <c r="F128" s="6">
-        <v>-5.6404166156556199</v>
+        <v>-4.0218796614840402</v>
       </c>
       <c r="G128" s="6">
-        <v>-8.6637038643971598E-2</v>
+        <v>-9.7514666228182806E-2</v>
       </c>
       <c r="H128" s="6">
         <v>4.0691206324752399E-2</v>
       </c>
       <c r="I128" s="6">
-        <v>0.53079185265850104</v>
+        <v>0.54964624429484299</v>
       </c>
       <c r="J128" s="6">
         <v>1.30872226634884</v>
@@ -8459,10 +8459,10 @@
         <v>33878</v>
       </c>
       <c r="B129" s="6">
-        <v>2.5037386919086901</v>
+        <v>2.6346270183531302</v>
       </c>
       <c r="C129" s="6">
-        <v>2.2764660119907698</v>
+        <v>2.3339343017948999</v>
       </c>
       <c r="D129" s="6">
         <v>2.4778468134868401</v>
@@ -8471,16 +8471,16 @@
         <v>2.9182872742606438</v>
       </c>
       <c r="F129" s="6">
-        <v>-4.7141740247281501</v>
+        <v>-3.21279801635592</v>
       </c>
       <c r="G129" s="6">
-        <v>-8.1776302664683304E-2</v>
+        <v>-9.0784152097513296E-2</v>
       </c>
       <c r="H129" s="6">
         <v>4.0479476085913499E-2</v>
       </c>
       <c r="I129" s="6">
-        <v>0.54243371288859399</v>
+        <v>0.55843594398936203</v>
       </c>
       <c r="J129" s="6">
         <v>1.77118756161597</v>
@@ -8521,10 +8521,10 @@
         <v>33970</v>
       </c>
       <c r="B130" s="6">
-        <v>2.140237586195</v>
+        <v>2.4160784234094801</v>
       </c>
       <c r="C130" s="6">
-        <v>2.2950922873014701</v>
+        <v>2.3400851143130401</v>
       </c>
       <c r="D130" s="6">
         <v>2.48051709905734</v>
@@ -8533,16 +8533,16 @@
         <v>2.7427197204432838</v>
       </c>
       <c r="F130" s="6">
-        <v>-4.2142658744290902</v>
+        <v>-2.76298800526058</v>
       </c>
       <c r="G130" s="6">
-        <v>-5.79650447089744E-2</v>
+        <v>-6.9061203035020294E-2</v>
       </c>
       <c r="H130" s="6">
         <v>4.0466433681525603E-2</v>
       </c>
       <c r="I130" s="6">
-        <v>0.52167207731757204</v>
+        <v>0.53769026531279196</v>
       </c>
       <c r="J130" s="6">
         <v>1.6527245961222199</v>
@@ -8583,10 +8583,10 @@
         <v>34060</v>
       </c>
       <c r="B131" s="6">
-        <v>2.1459525731180298</v>
+        <v>2.42155546648483</v>
       </c>
       <c r="C131" s="6">
-        <v>2.31580409632666</v>
+        <v>2.3480091185066501</v>
       </c>
       <c r="D131" s="6">
         <v>2.48438309684028</v>
@@ -8595,16 +8595,16 @@
         <v>2.705330666714032</v>
       </c>
       <c r="F131" s="6">
-        <v>-3.69038571875245</v>
+        <v>-2.2943257152005598</v>
       </c>
       <c r="G131" s="6">
-        <v>-5.68368155302253E-2</v>
+        <v>-6.6480037739525294E-2</v>
       </c>
       <c r="H131" s="6">
         <v>4.0337007356705402E-2</v>
       </c>
       <c r="I131" s="6">
-        <v>0.52848166318342504</v>
+        <v>0.54059713910228402</v>
       </c>
       <c r="J131" s="6">
         <v>1.9007028709457201</v>
@@ -8645,10 +8645,10 @@
         <v>34151</v>
       </c>
       <c r="B132" s="6">
-        <v>2.054610517505</v>
+        <v>2.3279532578837001</v>
       </c>
       <c r="C132" s="6">
-        <v>2.3420101690825699</v>
+        <v>2.3583556074324701</v>
       </c>
       <c r="D132" s="6">
         <v>2.4901500712079501</v>
@@ -8657,16 +8657,16 @@
         <v>2.6659290100311681</v>
       </c>
       <c r="F132" s="6">
-        <v>-3.9120682467871601</v>
+        <v>-2.3969690227895599</v>
       </c>
       <c r="G132" s="6">
-        <v>-5.4459426043941203E-2</v>
+        <v>-6.3164586443335294E-2</v>
       </c>
       <c r="H132" s="6">
         <v>4.0488730088522197E-2</v>
       </c>
       <c r="I132" s="6">
-        <v>0.54322338547163096</v>
+        <v>0.56270035523835404</v>
       </c>
       <c r="J132" s="6">
         <v>1.13368655981231</v>
@@ -8707,10 +8707,10 @@
         <v>34243</v>
       </c>
       <c r="B133" s="6">
-        <v>2.1382560918147999</v>
+        <v>2.3384487669488401</v>
       </c>
       <c r="C133" s="6">
-        <v>2.3617928229967502</v>
+        <v>2.3668954679952501</v>
       </c>
       <c r="D133" s="6">
         <v>2.4945344436766699</v>
@@ -8719,16 +8719,16 @@
         <v>2.7098579003741361</v>
       </c>
       <c r="F133" s="6">
-        <v>-3.79288724331394</v>
+        <v>-2.1804945104144098</v>
       </c>
       <c r="G133" s="6">
-        <v>-5.86231028065596E-2</v>
+        <v>-6.6084138670784401E-2</v>
       </c>
       <c r="H133" s="6">
         <v>4.0568718769069603E-2</v>
       </c>
       <c r="I133" s="6">
-        <v>0.53241665283761797</v>
+        <v>0.55341823835881898</v>
       </c>
       <c r="J133" s="6">
         <v>1.08599451236628</v>
@@ -8769,10 +8769,10 @@
         <v>34335</v>
       </c>
       <c r="B134" s="6">
-        <v>2.0966268877218801</v>
+        <v>2.2916090161531302</v>
       </c>
       <c r="C134" s="6">
-        <v>2.3843159826511902</v>
+        <v>2.3765537920608102</v>
       </c>
       <c r="D134" s="6">
         <v>2.4998638558128201</v>
@@ -8781,16 +8781,16 @@
         <v>2.6937676500061398</v>
       </c>
       <c r="F134" s="6">
-        <v>-3.6223380183202498</v>
+        <v>-1.9485613723389901</v>
       </c>
       <c r="G134" s="6">
-        <v>-5.7755518500450298E-2</v>
+        <v>-6.4989426944763201E-2</v>
       </c>
       <c r="H134" s="6">
         <v>4.0656314020364903E-2</v>
       </c>
       <c r="I134" s="6">
-        <v>0.52768164094077497</v>
+        <v>0.55050848613189896</v>
       </c>
       <c r="J134" s="6">
         <v>0.83033200876999902</v>
@@ -8831,10 +8831,10 @@
         <v>34425</v>
       </c>
       <c r="B135" s="6">
-        <v>2.2356368333516201</v>
+        <v>2.3862733997983598</v>
       </c>
       <c r="C135" s="6">
-        <v>2.40101844560485</v>
+        <v>2.38469507352844</v>
       </c>
       <c r="D135" s="6">
         <v>2.5040140371097301</v>
@@ -8843,16 +8843,16 @@
         <v>2.7196251722884162</v>
       </c>
       <c r="F135" s="6">
-        <v>-2.5997979620066798</v>
+        <v>-1.1592573050345401</v>
       </c>
       <c r="G135" s="6">
-        <v>-6.0965270150728702E-2</v>
+        <v>-6.7350732794275905E-2</v>
       </c>
       <c r="H135" s="6">
         <v>4.0498313176113E-2</v>
       </c>
       <c r="I135" s="6">
-        <v>0.57753403274797499</v>
+        <v>0.59177472624558702</v>
       </c>
       <c r="J135" s="6">
         <v>1.60401186680566</v>
@@ -8893,10 +8893,10 @@
         <v>34516</v>
       </c>
       <c r="B136" s="6">
-        <v>2.1128859153339201</v>
+        <v>2.3095121203676299</v>
       </c>
       <c r="C136" s="6">
-        <v>2.4276037630848899</v>
+        <v>2.3966813123896702</v>
       </c>
       <c r="D136" s="6">
         <v>2.5111059231255899</v>
@@ -8905,16 +8905,16 @@
         <v>2.6499574454458159</v>
       </c>
       <c r="F136" s="6">
-        <v>-2.2742753484295699</v>
+        <v>-0.87242031546782095</v>
       </c>
       <c r="G136" s="6">
-        <v>-5.8427388589276798E-2</v>
+        <v>-6.4897707934294793E-2</v>
       </c>
       <c r="H136" s="6">
         <v>4.0509917781658897E-2</v>
       </c>
       <c r="I136" s="6">
-        <v>0.55204767859231996</v>
+        <v>0.56873821312106698</v>
       </c>
       <c r="J136" s="6">
         <v>1.1466172867929001</v>
@@ -8955,10 +8955,10 @@
         <v>34608</v>
       </c>
       <c r="B137" s="6">
-        <v>2.2136946697971198</v>
+        <v>2.34564314785599</v>
       </c>
       <c r="C137" s="6">
-        <v>2.4475814413344099</v>
+        <v>2.4069975705629498</v>
       </c>
       <c r="D137" s="6">
         <v>2.5168794567114801</v>
@@ -8967,16 +8967,16 @@
         <v>2.69355020224324</v>
       </c>
       <c r="F137" s="6">
-        <v>-2.1538205357678102</v>
+        <v>-0.745236357934004</v>
       </c>
       <c r="G137" s="6">
-        <v>-5.8165164782009601E-2</v>
+        <v>-6.5105896230873303E-2</v>
       </c>
       <c r="H137" s="6">
         <v>4.0518015669222397E-2</v>
       </c>
       <c r="I137" s="6">
-        <v>0.53013096948442595</v>
+        <v>0.54832996618468299</v>
       </c>
       <c r="J137" s="6">
         <v>1.08961067660834</v>
@@ -9017,10 +9017,10 @@
         <v>34700</v>
       </c>
       <c r="B138" s="6">
-        <v>2.0917960705763599</v>
+        <v>2.2782021159717001</v>
       </c>
       <c r="C138" s="6">
-        <v>2.4777452177727599</v>
+        <v>2.4214275308096802</v>
       </c>
       <c r="D138" s="6">
         <v>2.5256543051870701</v>
@@ -9029,16 +9029,16 @@
         <v>2.6230637810891362</v>
       </c>
       <c r="F138" s="6">
-        <v>-1.9734279036001099</v>
+        <v>-0.60457712759443905</v>
       </c>
       <c r="G138" s="6">
-        <v>-6.0147679857150201E-2</v>
+        <v>-6.6379437483512896E-2</v>
       </c>
       <c r="H138" s="6">
         <v>4.0509596715445302E-2</v>
       </c>
       <c r="I138" s="6">
-        <v>0.51079655106719501</v>
+        <v>0.52877890167337305</v>
       </c>
       <c r="J138" s="6">
         <v>1.0771879257100401</v>
@@ -9079,10 +9079,10 @@
         <v>34790</v>
       </c>
       <c r="B139" s="6">
-        <v>2.0454304073318701</v>
+        <v>2.2550012501674002</v>
       </c>
       <c r="C139" s="6">
-        <v>2.5152843567901901</v>
+        <v>2.4385924017499701</v>
       </c>
       <c r="D139" s="6">
         <v>2.5363641596674</v>
@@ -9091,16 +9091,16 @@
         <v>2.5787658998353522</v>
       </c>
       <c r="F139" s="6">
-        <v>-1.88834449724459</v>
+        <v>-0.58245077444803395</v>
       </c>
       <c r="G139" s="6">
-        <v>-6.2446771893108599E-2</v>
+        <v>-6.8320431634091905E-2</v>
       </c>
       <c r="H139" s="6">
         <v>4.0487473643912399E-2</v>
       </c>
       <c r="I139" s="6">
-        <v>0.50128712916277796</v>
+        <v>0.517182785636223</v>
       </c>
       <c r="J139" s="6">
         <v>1.33785121838494</v>
@@ -9141,10 +9141,10 @@
         <v>34881</v>
       </c>
       <c r="B140" s="6">
-        <v>2.1580254380298101</v>
+        <v>2.2941499506437601</v>
       </c>
       <c r="C140" s="6">
-        <v>2.5467764935466599</v>
+        <v>2.4533653002895699</v>
       </c>
       <c r="D140" s="6">
         <v>2.54534653400647</v>
@@ -9153,16 +9153,16 @@
         <v>2.6402740468711361</v>
       </c>
       <c r="F140" s="6">
-        <v>-2.3247762314772999</v>
+        <v>-0.92103233787179295</v>
       </c>
       <c r="G140" s="6">
-        <v>-5.5127973708312301E-2</v>
+        <v>-6.3504652533256295E-2</v>
       </c>
       <c r="H140" s="6">
         <v>4.0517119847981002E-2</v>
       </c>
       <c r="I140" s="6">
-        <v>0.49624955439337498</v>
+        <v>0.51666557964778803</v>
       </c>
       <c r="J140" s="6">
         <v>0.86081246924668697</v>
@@ -9203,10 +9203,10 @@
         <v>34973</v>
       </c>
       <c r="B141" s="6">
-        <v>2.18975238036401</v>
+        <v>2.3201601551302802</v>
       </c>
       <c r="C141" s="6">
-        <v>2.5795510562659798</v>
+        <v>2.4677921723245801</v>
       </c>
       <c r="D141" s="6">
         <v>2.5540844765472901</v>
@@ -9215,16 +9215,16 @@
         <v>2.655195947914756</v>
       </c>
       <c r="F141" s="6">
-        <v>-2.3242476899089302</v>
+        <v>-0.989180422961908</v>
       </c>
       <c r="G141" s="6">
-        <v>-5.3744829458170197E-2</v>
+        <v>-6.2036228014035397E-2</v>
       </c>
       <c r="H141" s="6">
         <v>4.0501943562167297E-2</v>
       </c>
       <c r="I141" s="6">
-        <v>0.482174763870096</v>
+        <v>0.50166343903203503</v>
       </c>
       <c r="J141" s="6">
         <v>1.00805267408086</v>
@@ -9265,10 +9265,10 @@
         <v>35065</v>
       </c>
       <c r="B142" s="6">
-        <v>2.2067432896079802</v>
+        <v>2.3127702086575099</v>
       </c>
       <c r="C142" s="6">
-        <v>2.61430662487893</v>
+        <v>2.4813552427893799</v>
       </c>
       <c r="D142" s="6">
         <v>2.5622061318549099</v>
@@ -9277,16 +9277,16 @@
         <v>2.6877408226659161</v>
       </c>
       <c r="F142" s="6">
-        <v>-2.7361716459987</v>
+        <v>-1.29884219342227</v>
       </c>
       <c r="G142" s="6">
-        <v>-5.1545919622604103E-2</v>
+        <v>-6.0072450127450598E-2</v>
       </c>
       <c r="H142" s="6">
         <v>4.0567723047911203E-2</v>
       </c>
       <c r="I142" s="6">
-        <v>0.490248710696365</v>
+        <v>0.51329699772875303</v>
       </c>
       <c r="J142" s="6">
         <v>0.54957859454258995</v>
@@ -9327,10 +9327,10 @@
         <v>35156</v>
       </c>
       <c r="B143" s="6">
-        <v>2.5605909173020298</v>
+        <v>2.5136956808472699</v>
       </c>
       <c r="C143" s="6">
-        <v>2.62489405099898</v>
+        <v>2.4859679193375102</v>
       </c>
       <c r="D143" s="6">
         <v>2.5639032202248502</v>
@@ -9339,16 +9339,16 @@
         <v>2.8546737636657</v>
       </c>
       <c r="F143" s="6">
-        <v>-2.63662474473773</v>
+        <v>-1.2392807795835099</v>
       </c>
       <c r="G143" s="6">
-        <v>-4.1504846959239498E-2</v>
+        <v>-5.1590611674487599E-2</v>
       </c>
       <c r="H143" s="6">
         <v>4.0516747870774202E-2</v>
       </c>
       <c r="I143" s="6">
-        <v>0.48270461074035798</v>
+        <v>0.50313495682092202</v>
       </c>
       <c r="J143" s="6">
         <v>1.00055551407332</v>
@@ -9389,10 +9389,10 @@
         <v>35247</v>
       </c>
       <c r="B144" s="6">
-        <v>2.5536332547565701</v>
+        <v>2.5140143704816098</v>
       </c>
       <c r="C144" s="6">
-        <v>2.6364902164931898</v>
+        <v>2.4905583132677198</v>
       </c>
       <c r="D144" s="6">
         <v>2.5655542499123101</v>
@@ -9401,16 +9401,16 @@
         <v>2.854648832174588</v>
       </c>
       <c r="F144" s="6">
-        <v>-2.36863576812129</v>
+        <v>-1.0683845713711</v>
       </c>
       <c r="G144" s="6">
-        <v>-4.1823036690882401E-2</v>
+        <v>-5.1641997876709901E-2</v>
       </c>
       <c r="H144" s="6">
         <v>4.05109594930263E-2</v>
       </c>
       <c r="I144" s="6">
-        <v>0.46962630688496598</v>
+        <v>0.48951851119618001</v>
       </c>
       <c r="J144" s="6">
         <v>0.87788986765919197</v>
@@ -9451,10 +9451,10 @@
         <v>35339</v>
       </c>
       <c r="B145" s="6">
-        <v>2.62029691493498</v>
+        <v>2.5834338535362802</v>
       </c>
       <c r="C145" s="6">
-        <v>2.6459985078274602</v>
+        <v>2.4938139843247602</v>
       </c>
       <c r="D145" s="6">
         <v>2.5660925125366898</v>
@@ -9463,16 +9463,16 @@
         <v>2.8725447337795158</v>
       </c>
       <c r="F145" s="6">
-        <v>-1.78335854859813</v>
+        <v>-0.67516305773483498</v>
       </c>
       <c r="G145" s="6">
-        <v>-4.1461591410423201E-2</v>
+        <v>-5.0926621156848498E-2</v>
       </c>
       <c r="H145" s="6">
         <v>4.0426910989507403E-2</v>
       </c>
       <c r="I145" s="6">
-        <v>0.50079634497480496</v>
+        <v>0.51402686831310895</v>
       </c>
       <c r="J145" s="6">
         <v>1.3456478660228199</v>
@@ -9513,10 +9513,10 @@
         <v>35431</v>
       </c>
       <c r="B146" s="6">
-        <v>2.5621669701412699</v>
+        <v>2.5306105688538398</v>
       </c>
       <c r="C146" s="6">
-        <v>2.6602694362363799</v>
+        <v>2.4980371432685802</v>
       </c>
       <c r="D146" s="6">
         <v>2.5673803119952501</v>
@@ -9525,16 +9525,16 @@
         <v>2.8633065782686038</v>
       </c>
       <c r="F146" s="6">
-        <v>-2.0216773537375201</v>
+        <v>-0.855267210189254</v>
       </c>
       <c r="G146" s="6">
-        <v>-4.2058463614248497E-2</v>
+        <v>-5.1456150499536599E-2</v>
       </c>
       <c r="H146" s="6">
         <v>4.0468134657409699E-2</v>
       </c>
       <c r="I146" s="6">
-        <v>0.50886966055351102</v>
+        <v>0.52818150521297302</v>
       </c>
       <c r="J146" s="6">
         <v>0.50501401517661004</v>
@@ -9575,10 +9575,10 @@
         <v>35521</v>
       </c>
       <c r="B147" s="6">
-        <v>2.7788612159556698</v>
+        <v>2.6823491131371702</v>
       </c>
       <c r="C147" s="6">
-        <v>2.6603246797607198</v>
+        <v>2.4956837547886299</v>
       </c>
       <c r="D147" s="6">
         <v>2.5633521806660502</v>
@@ -9587,16 +9587,16 @@
         <v>2.9907484266067521</v>
       </c>
       <c r="F147" s="6">
-        <v>-1.63607427295824</v>
+        <v>-0.553574078975544</v>
       </c>
       <c r="G147" s="6">
-        <v>-3.8953460709602199E-2</v>
+        <v>-4.7775657935458002E-2</v>
       </c>
       <c r="H147" s="6">
         <v>4.04100526973536E-2</v>
       </c>
       <c r="I147" s="6">
-        <v>0.51341666972438704</v>
+        <v>0.53006924589990501</v>
       </c>
       <c r="J147" s="6">
         <v>1.1726520289945801</v>
@@ -9637,10 +9637,10 @@
         <v>35612</v>
       </c>
       <c r="B148" s="6">
-        <v>2.7540533038739299</v>
+        <v>2.63620555868849</v>
       </c>
       <c r="C148" s="6">
-        <v>2.6581058361334402</v>
+        <v>2.4916980700445501</v>
       </c>
       <c r="D148" s="6">
         <v>2.5579797670629798</v>
@@ -9649,16 +9649,16 @@
         <v>3.0385756890070561</v>
       </c>
       <c r="F148" s="6">
-        <v>-2.1040108726047602</v>
+        <v>-0.77200325940452796</v>
       </c>
       <c r="G148" s="6">
-        <v>-3.8657030145503098E-2</v>
+        <v>-4.7038685880597897E-2</v>
       </c>
       <c r="H148" s="6">
         <v>4.05142950431003E-2</v>
       </c>
       <c r="I148" s="6">
-        <v>0.64116455029365305</v>
+        <v>0.66691324462874302</v>
       </c>
       <c r="J148" s="6">
         <v>0.20234143553005901</v>
@@ -9699,10 +9699,10 @@
         <v>35704</v>
       </c>
       <c r="B149" s="6">
-        <v>2.7345736279206498</v>
+        <v>2.6308261848318399</v>
       </c>
       <c r="C149" s="6">
-        <v>2.6576621378832299</v>
+        <v>2.4877558485857798</v>
       </c>
       <c r="D149" s="6">
         <v>2.5525306056498702</v>
@@ -9711,16 +9711,16 @@
         <v>3.0378992511759919</v>
       </c>
       <c r="F149" s="6">
-        <v>-1.9925467591666599</v>
+        <v>-0.661512050605779</v>
       </c>
       <c r="G149" s="6">
-        <v>-3.9003134359195599E-2</v>
+        <v>-4.7204921749958301E-2</v>
       </c>
       <c r="H149" s="6">
         <v>4.0517780985909302E-2</v>
       </c>
       <c r="I149" s="6">
-        <v>0.60498118717585103</v>
+        <v>0.62978059832032895</v>
       </c>
       <c r="J149" s="6">
         <v>0.28385431419523</v>
@@ -9761,10 +9761,10 @@
         <v>35796</v>
       </c>
       <c r="B150" s="6">
-        <v>2.7659236496486601</v>
+        <v>2.6501329269821299</v>
       </c>
       <c r="C150" s="6">
-        <v>2.6552372743901298</v>
+        <v>2.48235616323106</v>
       </c>
       <c r="D150" s="6">
         <v>2.5457073006246098</v>
@@ -9773,16 +9773,16 @@
         <v>3.0689371222892801</v>
       </c>
       <c r="F150" s="6">
-        <v>-2.0265127356186698</v>
+        <v>-0.65204227583558405</v>
       </c>
       <c r="G150" s="6">
-        <v>-3.8338669069685402E-2</v>
+        <v>-4.6209291212013399E-2</v>
       </c>
       <c r="H150" s="6">
         <v>4.0530414429008003E-2</v>
       </c>
       <c r="I150" s="6">
-        <v>0.57623775999119597</v>
+        <v>0.60090694037425396</v>
       </c>
       <c r="J150" s="6">
         <v>0.23409550561686801</v>
@@ -9823,10 +9823,10 @@
         <v>35886</v>
       </c>
       <c r="B151" s="6">
-        <v>2.7877469259666601</v>
+        <v>2.6697582015489498</v>
       </c>
       <c r="C151" s="6">
-        <v>2.6533060287793702</v>
+        <v>2.4758213009108498</v>
       </c>
       <c r="D151" s="6">
         <v>2.5380712633251701</v>
@@ -9835,16 +9835,16 @@
         <v>3.0915894378389921</v>
       </c>
       <c r="F151" s="6">
-        <v>-1.9836593321229501</v>
+        <v>-0.640046838545686</v>
       </c>
       <c r="G151" s="6">
-        <v>-3.7895733415391701E-2</v>
+        <v>-4.5398232517500997E-2</v>
       </c>
       <c r="H151" s="6">
         <v>4.0530439021751102E-2</v>
       </c>
       <c r="I151" s="6">
-        <v>0.549822146474919</v>
+        <v>0.57368385308896597</v>
       </c>
       <c r="J151" s="6">
         <v>0.25386340231396998</v>
@@ -9885,10 +9885,10 @@
         <v>35977</v>
       </c>
       <c r="B152" s="6">
-        <v>2.9265124732725498</v>
+        <v>2.7612611122738402</v>
       </c>
       <c r="C152" s="6">
-        <v>2.6437951016168402</v>
+        <v>2.4654597822888</v>
       </c>
       <c r="D152" s="6">
         <v>2.5272220574642801</v>
@@ -9897,16 +9897,16 @@
         <v>3.1637391101691641</v>
       </c>
       <c r="F152" s="6">
-        <v>-1.8328808928934599</v>
+        <v>-0.53320321882449695</v>
       </c>
       <c r="G152" s="6">
-        <v>-3.52617998067562E-2</v>
+        <v>-4.2352939829598597E-2</v>
       </c>
       <c r="H152" s="6">
         <v>4.0499578227503601E-2</v>
       </c>
       <c r="I152" s="6">
-        <v>0.53770962758316398</v>
+        <v>0.55817390162051805</v>
       </c>
       <c r="J152" s="6">
         <v>0.50140811953685105</v>
@@ -9947,10 +9947,10 @@
         <v>36069</v>
       </c>
       <c r="B153" s="6">
-        <v>3.1118643172857201</v>
+        <v>2.8637011170285001</v>
       </c>
       <c r="C153" s="6">
-        <v>2.61963926453494</v>
+        <v>2.4492199426399099</v>
       </c>
       <c r="D153" s="6">
         <v>2.5117626712580101</v>
@@ -9959,16 +9959,16 @@
         <v>3.2743073370118081</v>
       </c>
       <c r="F153" s="6">
-        <v>-1.7945771785317099</v>
+        <v>-0.44705710933908499</v>
       </c>
       <c r="G153" s="6">
-        <v>-3.2121357049454798E-2</v>
+        <v>-3.8664936691583697E-2</v>
       </c>
       <c r="H153" s="6">
         <v>4.0499602133718102E-2</v>
       </c>
       <c r="I153" s="6">
-        <v>0.516876282131702</v>
+        <v>0.53710477917889998</v>
       </c>
       <c r="J153" s="6">
         <v>0.36927147662430099</v>
@@ -10009,10 +10009,10 @@
         <v>36161</v>
       </c>
       <c r="B154" s="6">
-        <v>3.0713951850807399</v>
+        <v>2.84389235780248</v>
       </c>
       <c r="C154" s="6">
-        <v>2.5970219125002898</v>
+        <v>2.4329962132235599</v>
       </c>
       <c r="D154" s="6">
         <v>2.4960403995406701</v>
@@ -10021,16 +10021,16 @@
         <v>3.2754331793812601</v>
       </c>
       <c r="F154" s="6">
-        <v>-1.73377646380635</v>
+        <v>-0.400811854596554</v>
       </c>
       <c r="G154" s="6">
-        <v>-3.2482142140232297E-2</v>
+        <v>-3.8819151155022401E-2</v>
       </c>
       <c r="H154" s="6">
         <v>4.05168834881523E-2</v>
       </c>
       <c r="I154" s="6">
-        <v>0.50509287093208599</v>
+        <v>0.526723886925895</v>
       </c>
       <c r="J154" s="6">
         <v>3.0535282321502599E-2</v>
@@ -10071,10 +10071,10 @@
         <v>36251</v>
       </c>
       <c r="B155" s="6">
-        <v>3.05738409385147</v>
+        <v>2.8548364917059201</v>
       </c>
       <c r="C155" s="6">
-        <v>2.5778335820959599</v>
+        <v>2.4165737477802902</v>
       </c>
       <c r="D155" s="6">
         <v>2.4803566852548</v>
@@ -10083,16 +10083,16 @@
         <v>3.2655322100229278</v>
       </c>
       <c r="F155" s="6">
-        <v>-1.4595831467450999</v>
+        <v>-0.230456882391991</v>
       </c>
       <c r="G155" s="6">
-        <v>-3.2677333258080303E-2</v>
+        <v>-3.8951462129744201E-2</v>
       </c>
       <c r="H155" s="6">
         <v>4.0490189271041498E-2</v>
       </c>
       <c r="I155" s="6">
-        <v>0.50020107821342397</v>
+        <v>0.51969163698966003</v>
       </c>
       <c r="J155" s="6">
         <v>0.45552959030826701</v>
@@ -10133,10 +10133,10 @@
         <v>36342</v>
       </c>
       <c r="B156" s="6">
-        <v>3.1858859185697601</v>
+        <v>2.9331217217006298</v>
       </c>
       <c r="C156" s="6">
-        <v>2.54971456801468</v>
+        <v>2.3967456736397099</v>
       </c>
       <c r="D156" s="6">
         <v>2.4615652521747502</v>
@@ -10145,16 +10145,16 @@
         <v>3.3333270190374442</v>
       </c>
       <c r="F156" s="6">
-        <v>-1.2920954528767099</v>
+        <v>-7.9843621292411598E-2</v>
       </c>
       <c r="G156" s="6">
-        <v>-3.1949926309715798E-2</v>
+        <v>-3.7989567811645197E-2</v>
       </c>
       <c r="H156" s="6">
         <v>4.0473364121900397E-2</v>
       </c>
       <c r="I156" s="6">
-        <v>0.48919606249865999</v>
+        <v>0.506822344277856</v>
       </c>
       <c r="J156" s="6">
         <v>0.49789196034572802</v>
@@ -10195,10 +10195,10 @@
         <v>36434</v>
       </c>
       <c r="B157" s="6">
-        <v>3.3800546327260199</v>
+        <v>3.05499233635144</v>
       </c>
       <c r="C157" s="6">
-        <v>2.5057512183593902</v>
+        <v>2.3712159546262201</v>
       </c>
       <c r="D157" s="6">
         <v>2.4383004718064099</v>
@@ -10207,16 +10207,16 @@
         <v>3.4214609203956798</v>
       </c>
       <c r="F157" s="6">
-        <v>-0.78137463035460497</v>
+        <v>0.34542501765417899</v>
       </c>
       <c r="G157" s="6">
-        <v>-3.0959443502467002E-2</v>
+        <v>-3.6581513841707498E-2</v>
       </c>
       <c r="H157" s="6">
         <v>4.0435863273217097E-2</v>
       </c>
       <c r="I157" s="6">
-        <v>0.52032763097222201</v>
+        <v>0.53048825377431696</v>
       </c>
       <c r="J157" s="6">
         <v>1.0206991261212099</v>
@@ -10257,10 +10257,10 @@
         <v>36526</v>
       </c>
       <c r="B158" s="6">
-        <v>3.2405308698267401</v>
+        <v>3.0037327217201399</v>
       </c>
       <c r="C158" s="6">
-        <v>2.47283830147693</v>
+        <v>2.34948312936565</v>
       </c>
       <c r="D158" s="6">
         <v>2.4173929091364101</v>
@@ -10269,16 +10269,16 @@
         <v>3.3434837160281079</v>
       </c>
       <c r="F158" s="6">
-        <v>-0.392279596859964</v>
+        <v>0.54155582664031998</v>
       </c>
       <c r="G158" s="6">
-        <v>-3.1858851165872303E-2</v>
+        <v>-3.7789918156352603E-2</v>
       </c>
       <c r="H158" s="6">
         <v>4.0456003309074499E-2</v>
       </c>
       <c r="I158" s="6">
-        <v>0.52919542541076403</v>
+        <v>0.53542437098553697</v>
       </c>
       <c r="J158" s="6">
         <v>1.08452647593056</v>
@@ -10319,10 +10319,10 @@
         <v>36617</v>
       </c>
       <c r="B159" s="6">
-        <v>3.39208314708186</v>
+        <v>3.0928484802718201</v>
       </c>
       <c r="C159" s="6">
-        <v>2.4258644754304401</v>
+        <v>2.32120331295227</v>
       </c>
       <c r="D159" s="6">
         <v>2.3913706001046702</v>
@@ -10331,16 +10331,16 @@
         <v>3.4684685246631122</v>
       </c>
       <c r="F159" s="6">
-        <v>-0.50402045089191505</v>
+        <v>0.51027188683929103</v>
       </c>
       <c r="G159" s="6">
-        <v>-3.0328428094297699E-2</v>
+        <v>-3.5446695982766202E-2</v>
       </c>
       <c r="H159" s="6">
         <v>4.0440218285864402E-2</v>
       </c>
       <c r="I159" s="6">
-        <v>0.53676739188014</v>
+        <v>0.55035325907664601</v>
       </c>
       <c r="J159" s="6">
         <v>0.44299562428269301</v>
@@ -10381,10 +10381,10 @@
         <v>36708</v>
       </c>
       <c r="B160" s="6">
-        <v>3.3162757132596998</v>
+        <v>3.0674529459191899</v>
       </c>
       <c r="C160" s="6">
-        <v>2.3835948516560101</v>
+        <v>2.2949779912328698</v>
       </c>
       <c r="D160" s="6">
         <v>2.3673695410073599</v>
@@ -10393,16 +10393,16 @@
         <v>3.3976918041325761</v>
       </c>
       <c r="F160" s="6">
-        <v>-0.53644721741841295</v>
+        <v>0.14155658700565299</v>
       </c>
       <c r="G160" s="6">
-        <v>-3.1122758262118199E-2</v>
+        <v>-3.6359318156604301E-2</v>
       </c>
       <c r="H160" s="6">
         <v>4.0460255316372401E-2</v>
       </c>
       <c r="I160" s="6">
-        <v>0.53034688392386298</v>
+        <v>0.54341277859994697</v>
       </c>
       <c r="J160" s="6">
         <v>0.89985697953170496</v>
@@ -10443,10 +10443,10 @@
         <v>36800</v>
       </c>
       <c r="B161" s="6">
-        <v>3.2963405627331999</v>
+        <v>3.07957827128388</v>
       </c>
       <c r="C161" s="6">
-        <v>2.34162425387597</v>
+        <v>2.2672590349065702</v>
       </c>
       <c r="D161" s="6">
         <v>2.3428232562011799</v>
@@ -10455,16 +10455,16 @@
         <v>3.3938926736391961</v>
       </c>
       <c r="F161" s="6">
-        <v>-0.73850033493812395</v>
+        <v>-0.13132152755770199</v>
       </c>
       <c r="G161" s="6">
-        <v>-3.1485983715354902E-2</v>
+        <v>-3.6125730255950797E-2</v>
       </c>
       <c r="H161" s="6">
         <v>4.0461615652767499E-2</v>
       </c>
       <c r="I161" s="6">
-        <v>0.51205998037711498</v>
+        <v>0.52581787846126904</v>
       </c>
       <c r="J161" s="6">
         <v>1.04057056678721</v>
@@ -10505,10 +10505,10 @@
         <v>36892</v>
       </c>
       <c r="B162" s="6">
-        <v>3.1341512700295899</v>
+        <v>3.013017566467</v>
       </c>
       <c r="C162" s="6">
-        <v>2.3080878225123498</v>
+        <v>2.2435346838655601</v>
       </c>
       <c r="D162" s="6">
         <v>2.32129422179037</v>
@@ -10517,16 +10517,16 @@
         <v>3.2819891690345999</v>
       </c>
       <c r="F162" s="6">
-        <v>-0.83110284168992599</v>
+        <v>-0.32248445111292801</v>
       </c>
       <c r="G162" s="6">
-        <v>-3.3634312921807498E-2</v>
+        <v>-3.91015042691523E-2</v>
       </c>
       <c r="H162" s="6">
         <v>4.0485108726504397E-2</v>
       </c>
       <c r="I162" s="6">
-        <v>0.55437922462002398</v>
+        <v>0.56962205774305497</v>
       </c>
       <c r="J162" s="6">
         <v>1.6098237016806001</v>
@@ -10567,10 +10567,10 @@
         <v>36982</v>
       </c>
       <c r="B163" s="6">
-        <v>3.1325897499005801</v>
+        <v>3.00896526519811</v>
       </c>
       <c r="C163" s="6">
-        <v>2.2701705509186398</v>
+        <v>2.2182072973963902</v>
       </c>
       <c r="D163" s="6">
         <v>2.2987580596625099</v>
@@ -10579,16 +10579,16 @@
         <v>3.3107844227250922</v>
       </c>
       <c r="F163" s="6">
-        <v>-1.5213747062455201</v>
+        <v>-0.97607142103117905</v>
       </c>
       <c r="G163" s="6">
-        <v>-3.35413019498381E-2</v>
+        <v>-3.8735756372465603E-2</v>
       </c>
       <c r="H163" s="6">
         <v>4.0499952309068797E-2</v>
       </c>
       <c r="I163" s="6">
-        <v>0.59433207425446</v>
+        <v>0.61248725494876</v>
       </c>
       <c r="J163" s="6">
         <v>0.58076533151778698</v>
@@ -10629,10 +10629,10 @@
         <v>37073</v>
       </c>
       <c r="B164" s="6">
-        <v>2.9655379937594599</v>
+        <v>2.8492972666648799</v>
       </c>
       <c r="C164" s="6">
-        <v>2.24194240520205</v>
+        <v>2.1974261497288401</v>
       </c>
       <c r="D164" s="6">
         <v>2.27949057496479</v>
@@ -10641,16 +10641,16 @@
         <v>3.2051742474970681</v>
       </c>
       <c r="F164" s="6">
-        <v>-2.32640381891082</v>
+        <v>-1.5506349869420999</v>
       </c>
       <c r="G164" s="6">
-        <v>-3.3504785281778797E-2</v>
+        <v>-3.9098463931042E-2</v>
       </c>
       <c r="H164" s="6">
         <v>4.05483799940018E-2</v>
       </c>
       <c r="I164" s="6">
-        <v>0.62220148257193197</v>
+        <v>0.63507820372269697</v>
       </c>
       <c r="J164" s="6">
         <v>-0.11002157291987</v>
@@ -10691,10 +10691,10 @@
         <v>37165</v>
       </c>
       <c r="B165" s="6">
-        <v>2.9404312646378399</v>
+        <v>2.83469929570676</v>
       </c>
       <c r="C165" s="6">
-        <v>2.21484680656584</v>
+        <v>2.1771703099564701</v>
       </c>
       <c r="D165" s="6">
         <v>2.26074463887148</v>
@@ -10703,16 +10703,16 @@
         <v>3.1837790523166918</v>
       </c>
       <c r="F165" s="6">
-        <v>-2.4551076019590101</v>
+        <v>-1.68699370796401</v>
       </c>
       <c r="G165" s="6">
-        <v>-3.3362974109407903E-2</v>
+        <v>-3.8854004742499698E-2</v>
       </c>
       <c r="H165" s="6">
         <v>4.04543062969435E-2</v>
       </c>
       <c r="I165" s="6">
-        <v>0.61517306591771204</v>
+        <v>0.63321999741787005</v>
       </c>
       <c r="J165" s="6">
         <v>0.74998931807893598</v>
@@ -10753,10 +10753,10 @@
         <v>37257</v>
       </c>
       <c r="B166" s="6">
-        <v>2.9468207839145402</v>
+        <v>2.8364791607027402</v>
       </c>
       <c r="C166" s="6">
-        <v>2.1854306635091598</v>
+        <v>2.15564506217838</v>
       </c>
       <c r="D166" s="6">
         <v>2.2409961490700798</v>
@@ -10765,16 +10765,16 @@
         <v>3.20730890026296</v>
       </c>
       <c r="F166" s="6">
-        <v>-2.7636417712855099</v>
+        <v>-1.92436045096395</v>
       </c>
       <c r="G166" s="6">
-        <v>-3.3605450092989E-2</v>
+        <v>-3.92131263664613E-2</v>
       </c>
       <c r="H166" s="6">
         <v>4.05701878018506E-2</v>
       </c>
       <c r="I166" s="6">
-        <v>0.61255885847915303</v>
+        <v>0.63014294226208301</v>
       </c>
       <c r="J166" s="6">
         <v>0.15831885484721001</v>
@@ -10815,10 +10815,10 @@
         <v>37347</v>
       </c>
       <c r="B167" s="6">
-        <v>2.8923623537305998</v>
+        <v>2.8092981812373199</v>
       </c>
       <c r="C167" s="6">
-        <v>2.1570739800437799</v>
+        <v>2.13471177531442</v>
       </c>
       <c r="D167" s="6">
         <v>2.2217262109276499</v>
@@ -10827,16 +10827,16 @@
         <v>3.147924823797676</v>
       </c>
       <c r="F167" s="6">
-        <v>-2.1595343641747</v>
+        <v>-1.5121776828463001</v>
       </c>
       <c r="G167" s="6">
-        <v>-3.22123616345312E-2</v>
+        <v>-3.7474590424422097E-2</v>
       </c>
       <c r="H167" s="6">
         <v>4.0343975368168E-2</v>
       </c>
       <c r="I167" s="6">
-        <v>0.67873334973659605</v>
+        <v>0.69908105151347499</v>
       </c>
       <c r="J167" s="6">
         <v>1.0319435860416899</v>
@@ -10877,10 +10877,10 @@
         <v>37438</v>
       </c>
       <c r="B168" s="6">
-        <v>2.7786506553742099</v>
+        <v>2.7302164582413599</v>
       </c>
       <c r="C168" s="6">
-        <v>2.1322068877739899</v>
+        <v>2.1156798385125799</v>
       </c>
       <c r="D168" s="6">
         <v>2.2041401443386501</v>
@@ -10889,16 +10889,16 @@
         <v>3.0679396777213359</v>
       </c>
       <c r="F168" s="6">
-        <v>-1.87725611346622</v>
+        <v>-1.31866933230901</v>
       </c>
       <c r="G168" s="6">
-        <v>-2.9859978558525499E-2</v>
+        <v>-3.4584186961713802E-2</v>
       </c>
       <c r="H168" s="6">
         <v>4.0304000059875097E-2</v>
       </c>
       <c r="I168" s="6">
-        <v>0.64592835901304901</v>
+        <v>0.66523200004813998</v>
       </c>
       <c r="J168" s="6">
         <v>1.02778518880474</v>
@@ -10939,10 +10939,10 @@
         <v>37530</v>
       </c>
       <c r="B169" s="6">
-        <v>2.6082804788659701</v>
+        <v>2.60633502684448</v>
       </c>
       <c r="C169" s="6">
-        <v>2.1156872156334101</v>
+        <v>2.1003152709701198</v>
       </c>
       <c r="D169" s="6">
         <v>2.1894893152332902</v>
@@ -10951,16 +10951,16 @@
         <v>2.9728379911825442</v>
       </c>
       <c r="F169" s="6">
-        <v>-2.0140937946997601</v>
+        <v>-1.3973894059144001</v>
       </c>
       <c r="G169" s="6">
-        <v>-2.68107722018468E-2</v>
+        <v>-3.1016587360811001E-2</v>
       </c>
       <c r="H169" s="6">
         <v>4.0372420894020503E-2</v>
       </c>
       <c r="I169" s="6">
-        <v>0.63453272005483097</v>
+        <v>0.65390873294105101</v>
       </c>
       <c r="J169" s="6">
         <v>0.2813830977506</v>
@@ -11001,10 +11001,10 @@
         <v>37622</v>
       </c>
       <c r="B170" s="6">
-        <v>2.5717927315005999</v>
+        <v>2.5695194373566901</v>
       </c>
       <c r="C170" s="6">
-        <v>2.1015584838610599</v>
+        <v>2.0859610797252901</v>
       </c>
       <c r="D170" s="6">
         <v>2.1756923953870899</v>
@@ -11013,16 +11013,16 @@
         <v>2.9474600752828479</v>
       </c>
       <c r="F170" s="6">
-        <v>-2.1617183961608899</v>
+        <v>-1.48025389973179</v>
       </c>
       <c r="G170" s="6">
-        <v>-2.63015203504878E-2</v>
+        <v>-3.0163416453888599E-2</v>
       </c>
       <c r="H170" s="6">
         <v>4.0423201018770602E-2</v>
       </c>
       <c r="I170" s="6">
-        <v>0.60917014395949398</v>
+        <v>0.62755508326265397</v>
       </c>
       <c r="J170" s="6">
         <v>0.21621471921317101</v>
@@ -11063,10 +11063,10 @@
         <v>37712</v>
       </c>
       <c r="B171" s="6">
-        <v>2.5978556092411198</v>
+        <v>2.57757321729818</v>
       </c>
       <c r="C171" s="6">
-        <v>2.0876118621031701</v>
+        <v>2.0714387370593799</v>
       </c>
       <c r="D171" s="6">
         <v>2.16176647621245</v>
@@ -11075,16 +11075,16 @@
         <v>2.947608597644308</v>
       </c>
       <c r="F171" s="6">
-        <v>-2.0343955179856201</v>
+        <v>-1.35154134339564</v>
       </c>
       <c r="G171" s="6">
-        <v>-2.6764844329429601E-2</v>
+        <v>-3.0375603482165899E-2</v>
       </c>
       <c r="H171" s="6">
         <v>4.0405287899560299E-2</v>
       </c>
       <c r="I171" s="6">
-        <v>0.57821687632313401</v>
+        <v>0.59704889888194201</v>
       </c>
       <c r="J171" s="6">
         <v>0.56108214162200598</v>
@@ -11125,10 +11125,10 @@
         <v>37803</v>
       </c>
       <c r="B172" s="6">
-        <v>2.82051913178221</v>
+        <v>2.6982293663118599</v>
       </c>
       <c r="C172" s="6">
-        <v>2.0587999882678201</v>
+        <v>2.0515822986688201</v>
       </c>
       <c r="D172" s="6">
         <v>2.1439868478327799</v>
@@ -11137,16 +11137,16 @@
         <v>3.0363910524228359</v>
       </c>
       <c r="F172" s="6">
-        <v>-1.7273117758860499</v>
+        <v>-1.0163936567937499</v>
       </c>
       <c r="G172" s="6">
-        <v>-3.1034632906023499E-2</v>
+        <v>-3.4051409122708903E-2</v>
       </c>
       <c r="H172" s="6">
         <v>4.0322561456389197E-2</v>
       </c>
       <c r="I172" s="6">
-        <v>0.56577817760740201</v>
+        <v>0.58380723969021298</v>
       </c>
       <c r="J172" s="6">
         <v>0.92538048523535199</v>
@@ -11187,10 +11187,10 @@
         <v>37895</v>
       </c>
       <c r="B173" s="6">
-        <v>2.8157464982548901</v>
+        <v>2.6988139860671598</v>
       </c>
       <c r="C173" s="6">
-        <v>2.0276845180774199</v>
+        <v>2.0308714151708398</v>
       </c>
       <c r="D173" s="6">
         <v>2.1256514789039</v>
@@ -11199,16 +11199,16 @@
         <v>3.026774181594408</v>
       </c>
       <c r="F173" s="6">
-        <v>-1.12114211095053</v>
+        <v>-0.53005050040189905</v>
       </c>
       <c r="G173" s="6">
-        <v>-3.0890766982724801E-2</v>
+        <v>-3.3912590354121898E-2</v>
       </c>
       <c r="H173" s="6">
         <v>4.02929938162341E-2</v>
       </c>
       <c r="I173" s="6">
-        <v>0.54595205215190701</v>
+        <v>0.56307657373939901</v>
       </c>
       <c r="J173" s="6">
         <v>0.87846537459601703</v>
@@ -11249,10 +11249,10 @@
         <v>37987</v>
       </c>
       <c r="B174" s="6">
-        <v>2.6778808568630001</v>
+        <v>2.6208480990671501</v>
       </c>
       <c r="C174" s="6">
-        <v>2.0031458953375698</v>
+        <v>2.01289183411608</v>
       </c>
       <c r="D174" s="6">
         <v>2.1094747587242102</v>
@@ -11261,16 +11261,16 @@
         <v>2.9344585152236879</v>
       </c>
       <c r="F174" s="6">
-        <v>-0.469707154373737</v>
+        <v>1.7123668068165902E-2</v>
       </c>
       <c r="G174" s="6">
-        <v>-2.7349598137220401E-2</v>
+        <v>-3.0496626690217198E-2</v>
       </c>
       <c r="H174" s="6">
         <v>4.02680309740212E-2</v>
       </c>
       <c r="I174" s="6">
-        <v>0.55872592089913897</v>
+        <v>0.57382855944314703</v>
       </c>
       <c r="J174" s="6">
         <v>1.2527798474276099</v>
@@ -11311,10 +11311,10 @@
         <v>38078</v>
       </c>
       <c r="B175" s="6">
-        <v>2.65793157170951</v>
+        <v>2.6061830660016798</v>
       </c>
       <c r="C175" s="6">
-        <v>1.97926192478956</v>
+        <v>1.9952903456126301</v>
       </c>
       <c r="D175" s="6">
         <v>2.0936435967867801</v>
@@ -11323,16 +11323,16 @@
         <v>2.9068927561593401</v>
       </c>
       <c r="F175" s="6">
-        <v>-0.14236351571162201</v>
+        <v>0.292483744673177</v>
       </c>
       <c r="G175" s="6">
-        <v>-2.6886434301924202E-2</v>
+        <v>-2.97930961722702E-2</v>
       </c>
       <c r="H175" s="6">
         <v>4.0271857551171998E-2</v>
       </c>
       <c r="I175" s="6">
-        <v>0.54475143909194901</v>
+        <v>0.55894668154225502</v>
       </c>
       <c r="J175" s="6">
         <v>1.2935876677495499</v>
@@ -11373,10 +11373,10 @@
         <v>38169</v>
       </c>
       <c r="B176" s="6">
-        <v>2.67107790891651</v>
+        <v>2.5943129610521498</v>
       </c>
       <c r="C176" s="6">
-        <v>1.95329216523875</v>
+        <v>1.9769118200587501</v>
       </c>
       <c r="D176" s="6">
         <v>2.0772953236786198</v>
@@ -11385,16 +11385,16 @@
         <v>2.9259186910016481</v>
       </c>
       <c r="F176" s="6">
-        <v>-0.344630520988915</v>
+        <v>0.18410537212275799</v>
       </c>
       <c r="G176" s="6">
-        <v>-2.7326725879323398E-2</v>
+        <v>-3.00232532951746E-2</v>
       </c>
       <c r="H176" s="6">
         <v>4.0223663790814899E-2</v>
       </c>
       <c r="I176" s="6">
-        <v>0.58601308912072503</v>
+        <v>0.60384242185442505</v>
       </c>
       <c r="J176" s="6">
         <v>0.40990518928082098</v>
@@ -11435,10 +11435,10 @@
         <v>38261</v>
       </c>
       <c r="B177" s="6">
-        <v>2.7081587482310199</v>
+        <v>2.6202461429628801</v>
       </c>
       <c r="C177" s="6">
-        <v>1.92372285487868</v>
+        <v>1.95719375833903</v>
       </c>
       <c r="D177" s="6">
         <v>2.0600264412101401</v>
@@ -11447,16 +11447,16 @@
         <v>2.927472300214772</v>
       </c>
       <c r="F177" s="6">
-        <v>4.1849386295723399E-2</v>
+        <v>0.53247033130764998</v>
       </c>
       <c r="G177" s="6">
-        <v>-2.80481818351099E-2</v>
+        <v>-3.05489144282294E-2</v>
       </c>
       <c r="H177" s="6">
         <v>4.0243613948369797E-2</v>
       </c>
       <c r="I177" s="6">
-        <v>0.58203020783665205</v>
+        <v>0.60077013241514698</v>
       </c>
       <c r="J177" s="6">
         <v>1.26033681650473</v>
@@ -11497,10 +11497,10 @@
         <v>38353</v>
       </c>
       <c r="B178" s="6">
-        <v>2.7835610073604702</v>
+        <v>2.6710462034910298</v>
       </c>
       <c r="C178" s="6">
-        <v>1.88536668485551</v>
+        <v>1.9347396300405599</v>
       </c>
       <c r="D178" s="6">
         <v>2.0408753081665201</v>
@@ -11509,16 +11509,16 @@
         <v>2.9410605973106039</v>
       </c>
       <c r="F178" s="6">
-        <v>0.55738607399604201</v>
+        <v>0.95032278676387705</v>
       </c>
       <c r="G178" s="6">
-        <v>-2.94575227671015E-2</v>
+        <v>-3.1604137457401697E-2</v>
       </c>
       <c r="H178" s="6">
         <v>4.0314553642649999E-2</v>
       </c>
       <c r="I178" s="6">
-        <v>0.62007264714124499</v>
+        <v>0.63444451410679603</v>
       </c>
       <c r="J178" s="6">
         <v>1.9431368992261799</v>
@@ -11559,10 +11559,10 @@
         <v>38443</v>
       </c>
       <c r="B179" s="6">
-        <v>2.58967795284283</v>
+        <v>2.56415313103403</v>
       </c>
       <c r="C179" s="6">
-        <v>1.8566173435611</v>
+        <v>1.9152978936355201</v>
       </c>
       <c r="D179" s="6">
         <v>2.02388331080365</v>
@@ -11571,16 +11571,16 @@
         <v>2.8720391035245481</v>
       </c>
       <c r="F179" s="6">
-        <v>0.67890887406571199</v>
+        <v>1.0413493434697301</v>
       </c>
       <c r="G179" s="6">
-        <v>-2.5782468974109199E-2</v>
+        <v>-2.9026406816413199E-2</v>
       </c>
       <c r="H179" s="6">
         <v>4.0204336972128503E-2</v>
       </c>
       <c r="I179" s="6">
-        <v>0.61757727310544697</v>
+        <v>0.63646963241155796</v>
       </c>
       <c r="J179" s="6">
         <v>0.96448903557186905</v>
@@ -11621,10 +11621,10 @@
         <v>38534</v>
       </c>
       <c r="B180" s="6">
-        <v>2.59532608726964</v>
+        <v>2.5570677025282502</v>
       </c>
       <c r="C180" s="6">
-        <v>1.8248880663592899</v>
+        <v>1.8949089032729101</v>
       </c>
       <c r="D180" s="6">
         <v>2.0062500390333402</v>
@@ -11633,16 +11633,16 @@
         <v>2.882014678944016</v>
       </c>
       <c r="F180" s="6">
-        <v>0.52558719193922299</v>
+        <v>0.934062979873715</v>
       </c>
       <c r="G180" s="6">
-        <v>-2.5944807991655001E-2</v>
+        <v>-2.9094982652474798E-2</v>
       </c>
       <c r="H180" s="6">
         <v>4.0113485829036601E-2</v>
       </c>
       <c r="I180" s="6">
-        <v>0.61583746250229798</v>
+        <v>0.63469843517574398</v>
       </c>
       <c r="J180" s="6">
         <v>0.52287224285681</v>
@@ -11683,10 +11683,10 @@
         <v>38626</v>
       </c>
       <c r="B181" s="6">
-        <v>2.5382020125459102</v>
+        <v>2.5343947419194399</v>
       </c>
       <c r="C181" s="6">
-        <v>1.7988889028570301</v>
+        <v>1.8759451883738001</v>
       </c>
       <c r="D181" s="6">
         <v>1.9895466676828799</v>
@@ -11695,16 +11695,16 @@
         <v>2.8378895459497961</v>
       </c>
       <c r="F181" s="6">
-        <v>0.85456392286357596</v>
+        <v>1.17876450976212</v>
       </c>
       <c r="G181" s="6">
-        <v>-2.52569455788859E-2</v>
+        <v>-2.8542428398856901E-2</v>
       </c>
       <c r="H181" s="6">
         <v>4.0243880898409599E-2</v>
       </c>
       <c r="I181" s="6">
-        <v>0.64452687823696198</v>
+        <v>0.66566726191335901</v>
       </c>
       <c r="J181" s="6">
         <v>1.5049325675259799</v>
@@ -11745,10 +11745,10 @@
         <v>38718</v>
       </c>
       <c r="B182" s="6">
-        <v>2.78262492276916</v>
+        <v>2.6660148446962499</v>
       </c>
       <c r="C182" s="6">
-        <v>1.7494122101238301</v>
+        <v>1.8494837357079901</v>
       </c>
       <c r="D182" s="6">
         <v>1.96764015240421</v>
@@ -11757,16 +11757,16 @@
         <v>2.950594410044324</v>
       </c>
       <c r="F182" s="6">
-        <v>0.63337094803119998</v>
+        <v>1.04719138956136</v>
       </c>
       <c r="G182" s="6">
-        <v>-2.6834813135091899E-2</v>
+        <v>-2.9795143468866199E-2</v>
       </c>
       <c r="H182" s="6">
         <v>4.0221306585537103E-2</v>
       </c>
       <c r="I182" s="6">
-        <v>0.60961507200582099</v>
+        <v>0.63158001807983899</v>
       </c>
       <c r="J182" s="6">
         <v>1.38118206028224</v>
@@ -11807,10 +11807,10 @@
         <v>38808</v>
       </c>
       <c r="B183" s="6">
-        <v>2.65527280294955</v>
+        <v>2.5938534953932599</v>
       </c>
       <c r="C183" s="6">
-        <v>1.7074831177985601</v>
+        <v>1.8259553359809899</v>
       </c>
       <c r="D183" s="6">
         <v>1.9478269686284599</v>
@@ -11819,16 +11819,16 @@
         <v>2.863413026868848</v>
       </c>
       <c r="F183" s="6">
-        <v>1.06811016576484</v>
+        <v>1.36144853378028</v>
       </c>
       <c r="G183" s="6">
-        <v>-2.61205284573954E-2</v>
+        <v>-2.92731329798851E-2</v>
       </c>
       <c r="H183" s="6">
         <v>4.0409013462085801E-2</v>
       </c>
       <c r="I183" s="6">
-        <v>0.67129750593570603</v>
+        <v>0.68745713918670504</v>
       </c>
       <c r="J183" s="6">
         <v>2.16893361193635</v>
@@ -11869,10 +11869,10 @@
         <v>38899</v>
       </c>
       <c r="B184" s="6">
-        <v>2.55598168799404</v>
+        <v>2.5142225034723702</v>
       </c>
       <c r="C184" s="6">
-        <v>1.67134587309331</v>
+        <v>1.80485394202641</v>
       </c>
       <c r="D184" s="6">
         <v>1.9297818869961101</v>
@@ -11881,16 +11881,16 @@
         <v>2.816608052398728</v>
       </c>
       <c r="F184" s="6">
-        <v>0.68592121077011803</v>
+        <v>1.06998513400742</v>
       </c>
       <c r="G184" s="6">
-        <v>-2.61022618897362E-2</v>
+        <v>-2.9280248221217098E-2</v>
       </c>
       <c r="H184" s="6">
         <v>4.0257050124659501E-2</v>
       </c>
       <c r="I184" s="6">
-        <v>0.67380651048553497</v>
+        <v>0.695449731329982</v>
       </c>
       <c r="J184" s="6">
         <v>1.12994806982464</v>
@@ -11931,10 +11931,10 @@
         <v>38991</v>
       </c>
       <c r="B185" s="6">
-        <v>2.6181745582907601</v>
+        <v>2.5543963392951299</v>
       </c>
       <c r="C185" s="6">
-        <v>1.6278111161981399</v>
+        <v>1.7807830086281999</v>
       </c>
       <c r="D185" s="6">
         <v>1.90948658495802</v>
@@ -11943,16 +11943,16 @@
         <v>2.869549981376196</v>
       </c>
       <c r="F185" s="6">
-        <v>0.35069050790804102</v>
+        <v>0.76813024339014702</v>
       </c>
       <c r="G185" s="6">
-        <v>-2.60067301885448E-2</v>
+        <v>-2.9129337834616E-2</v>
       </c>
       <c r="H185" s="6">
         <v>4.0162547513185202E-2</v>
       </c>
       <c r="I185" s="6">
-        <v>0.67952889944513695</v>
+        <v>0.69882242900785196</v>
       </c>
       <c r="J185" s="6">
         <v>0.70034510378848402</v>
@@ -11993,10 +11993,10 @@
         <v>39083</v>
       </c>
       <c r="B186" s="6">
-        <v>2.5412026863812698</v>
+        <v>2.51314154724533</v>
       </c>
       <c r="C186" s="6">
-        <v>1.5888064352445199</v>
+        <v>1.75834745565454</v>
       </c>
       <c r="D186" s="6">
         <v>1.89037748184682</v>
@@ -12005,16 +12005,16 @@
         <v>2.8179446499801841</v>
       </c>
       <c r="F186" s="6">
-        <v>0.42877255169975098</v>
+        <v>0.78042833872439099</v>
       </c>
       <c r="G186" s="6">
-        <v>-2.6258530179767502E-2</v>
+        <v>-2.9388841160591501E-2</v>
       </c>
       <c r="H186" s="6">
         <v>4.0244926581978098E-2</v>
       </c>
       <c r="I186" s="6">
-        <v>0.67557543335491499</v>
+        <v>0.69697767995176896</v>
       </c>
       <c r="J186" s="6">
         <v>1.59843454243135</v>
@@ -12055,10 +12055,10 @@
         <v>39173</v>
       </c>
       <c r="B187" s="6">
-        <v>2.5427967293081002</v>
+        <v>2.5079438086861399</v>
       </c>
       <c r="C187" s="6">
-        <v>1.54695582713344</v>
+        <v>1.7347357288838301</v>
       </c>
       <c r="D187" s="6">
         <v>1.87036608772901</v>
@@ -12067,16 +12067,16 @@
         <v>2.838910008482816</v>
       </c>
       <c r="F187" s="6">
-        <v>4.1651160758533496E-3</v>
+        <v>0.43266060580549498</v>
       </c>
       <c r="G187" s="6">
-        <v>-2.6228523781402401E-2</v>
+        <v>-2.9320063995050799E-2</v>
       </c>
       <c r="H187" s="6">
         <v>4.0130823867760401E-2</v>
       </c>
       <c r="I187" s="6">
-        <v>0.72155526092150302</v>
+        <v>0.74503800103282503</v>
       </c>
       <c r="J187" s="6">
         <v>0.685308572634031</v>
@@ -12117,10 +12117,10 @@
         <v>39264</v>
       </c>
       <c r="B188" s="6">
-        <v>2.5304046554585198</v>
+        <v>2.5048956949887198</v>
       </c>
       <c r="C188" s="6">
-        <v>1.5025448674555799</v>
+        <v>1.7101299743559999</v>
       </c>
       <c r="D188" s="6">
         <v>1.8496246578898301</v>
@@ -12129,16 +12129,16 @@
         <v>2.835635095075304</v>
       </c>
       <c r="F188" s="6">
-        <v>-7.6344533472024495E-2</v>
+        <v>0.32658955578233401</v>
       </c>
       <c r="G188" s="6">
-        <v>-2.6287207264566698E-2</v>
+        <v>-2.9342289705560801E-2</v>
       </c>
       <c r="H188" s="6">
         <v>4.0141042513094E-2</v>
       </c>
       <c r="I188" s="6">
-        <v>0.67223659906286604</v>
+        <v>0.69544401738200101</v>
       </c>
       <c r="J188" s="6">
         <v>0.94455410558146602</v>
@@ -12179,10 +12179,10 @@
         <v>39356</v>
       </c>
       <c r="B189" s="6">
-        <v>2.5441262230283801</v>
+        <v>2.5230961360483302</v>
       </c>
       <c r="C189" s="6">
-        <v>1.4493905931067901</v>
+        <v>1.6830282724314201</v>
       </c>
       <c r="D189" s="6">
         <v>1.82718032703078</v>
@@ -12191,16 +12191,16 @@
         <v>2.831646585111756</v>
       </c>
       <c r="F189" s="6">
-        <v>3.9523256466566202E-2</v>
+        <v>0.371983661073159</v>
       </c>
       <c r="G189" s="6">
-        <v>-2.6231053169037798E-2</v>
+        <v>-2.9270030429794799E-2</v>
       </c>
       <c r="H189" s="6">
         <v>4.0183022034079398E-2</v>
       </c>
       <c r="I189" s="6">
-        <v>0.68887954788651595</v>
+        <v>0.71000257614781903</v>
       </c>
       <c r="J189" s="6">
         <v>1.71125078438911</v>
@@ -12241,10 +12241,10 @@
         <v>39448</v>
       </c>
       <c r="B190" s="6">
-        <v>2.1406822767419502</v>
+        <v>2.2920758138104098</v>
       </c>
       <c r="C190" s="6">
-        <v>1.42049615049498</v>
+        <v>1.6641315327681201</v>
       </c>
       <c r="D190" s="6">
         <v>1.81067378304101</v>
@@ -12253,16 +12253,16 @@
         <v>2.6552698165156641</v>
       </c>
       <c r="F190" s="6">
-        <v>5.8134063386489701E-2</v>
+        <v>0.25010622357399398</v>
       </c>
       <c r="G190" s="6">
-        <v>-2.7360357380916901E-2</v>
+        <v>-3.0200946690345499E-2</v>
       </c>
       <c r="H190" s="6">
         <v>4.0136813092777897E-2</v>
       </c>
       <c r="I190" s="6">
-        <v>0.66138839707965902</v>
+        <v>0.68315670336402901</v>
       </c>
       <c r="J190" s="6">
         <v>0.91450610928327303</v>
@@ -12303,10 +12303,10 @@
         <v>39539</v>
       </c>
       <c r="B191" s="6">
-        <v>2.1605639689292402</v>
+        <v>2.30452783135348</v>
       </c>
       <c r="C191" s="6">
-        <v>1.3871901667373301</v>
+        <v>1.6433840457133899</v>
       </c>
       <c r="D191" s="6">
         <v>1.7928226084299399</v>
@@ -12315,16 +12315,16 @@
         <v>2.6763208451206721</v>
       </c>
       <c r="F191" s="6">
-        <v>-0.27942318661502002</v>
+        <v>-8.3377161202065495E-2</v>
       </c>
       <c r="G191" s="6">
-        <v>-2.75437747329992E-2</v>
+        <v>-3.0380090973483698E-2</v>
       </c>
       <c r="H191" s="6">
         <v>4.0120942049019802E-2</v>
       </c>
       <c r="I191" s="6">
-        <v>0.64270942527500996</v>
+        <v>0.66332907667128604</v>
       </c>
       <c r="J191" s="6">
         <v>0.65598519734078797</v>
@@ -12365,10 +12365,10 @@
         <v>39630</v>
       </c>
       <c r="B192" s="6">
-        <v>2.0188170512482801</v>
+        <v>2.1705487819062399</v>
       </c>
       <c r="C192" s="6">
-        <v>1.3595319354439099</v>
+        <v>1.62654343972286</v>
       </c>
       <c r="D192" s="6">
         <v>1.7782874346397799</v>
@@ -12377,16 +12377,16 @@
         <v>2.5562140546595682</v>
       </c>
       <c r="F192" s="6">
-        <v>-0.67391576386387397</v>
+        <v>-0.385360055121168</v>
       </c>
       <c r="G192" s="6">
-        <v>-2.56678530113786E-2</v>
+        <v>-2.7550220722445399E-2</v>
       </c>
       <c r="H192" s="6">
         <v>4.0127754145021802E-2</v>
       </c>
       <c r="I192" s="6">
-        <v>0.60688315855295305</v>
+        <v>0.62793635881668697</v>
       </c>
       <c r="J192" s="6">
         <v>0.92454977627079304</v>
@@ -12427,10 +12427,10 @@
         <v>39722</v>
       </c>
       <c r="B193" s="6">
-        <v>1.7309321412071501</v>
+        <v>1.9088454815426801</v>
       </c>
       <c r="C193" s="6">
-        <v>1.3485837518000701</v>
+        <v>1.6184815522664899</v>
       </c>
       <c r="D193" s="6">
         <v>1.7707155960174501</v>
@@ -12439,16 +12439,16 @@
         <v>2.4016500853187002</v>
       </c>
       <c r="F193" s="6">
-        <v>-2.8313574426537098</v>
+        <v>-1.9252589576400401</v>
       </c>
       <c r="G193" s="6">
-        <v>-2.1485005254542101E-2</v>
+        <v>-2.2513849435683998E-2</v>
       </c>
       <c r="H193" s="6">
         <v>4.0110809079312901E-2</v>
       </c>
       <c r="I193" s="6">
-        <v>1.6488639917363299</v>
+        <v>1.61353945044398</v>
       </c>
       <c r="J193" s="6">
         <v>-0.38066085371665098</v>
@@ -12489,10 +12489,10 @@
         <v>39814</v>
       </c>
       <c r="B194" s="6">
-        <v>1.72278296675313</v>
+        <v>1.89726303059393</v>
       </c>
       <c r="C194" s="6">
-        <v>1.33907500705047</v>
+        <v>1.61118953134695</v>
       </c>
       <c r="D194" s="6">
         <v>1.7636591348555399</v>
@@ -12501,16 +12501,16 @@
         <v>2.3902407192020401</v>
       </c>
       <c r="F194" s="6">
-        <v>-4.1699731214750404</v>
+        <v>-3.1441312821507399</v>
       </c>
       <c r="G194" s="6">
-        <v>-2.15100902433474E-2</v>
+        <v>-2.2368726324945E-2</v>
       </c>
       <c r="H194" s="6">
         <v>4.0146840946407497E-2</v>
       </c>
       <c r="I194" s="6">
-        <v>1.41908684228872</v>
+        <v>1.3977782420296101</v>
       </c>
       <c r="J194" s="6">
         <v>-1.00025102367323</v>
@@ -12551,10 +12551,10 @@
         <v>39904</v>
       </c>
       <c r="B195" s="6">
-        <v>1.7216452461096099</v>
+        <v>1.89688873250128</v>
       </c>
       <c r="C195" s="6">
-        <v>1.3301790548938299</v>
+        <v>1.60440061715205</v>
       </c>
       <c r="D195" s="6">
         <v>1.7571658726777699</v>
@@ -12563,16 +12563,16 @@
         <v>2.3747402224829322</v>
       </c>
       <c r="F195" s="6">
-        <v>-4.6380070132098599</v>
+        <v>-3.6973290017165299</v>
       </c>
       <c r="G195" s="6">
-        <v>-2.1598817673450101E-2</v>
+        <v>-2.2347046352427E-2</v>
       </c>
       <c r="H195" s="6">
         <v>4.0038525251966502E-2</v>
       </c>
       <c r="I195" s="6">
-        <v>1.30044854380584</v>
+        <v>1.2928688490907201</v>
       </c>
       <c r="J195" s="6">
         <v>2.9699471385612498E-3</v>
@@ -12613,10 +12613,10 @@
         <v>39995</v>
       </c>
       <c r="B196" s="6">
-        <v>1.7209657458913901</v>
+        <v>1.89540598024815</v>
       </c>
       <c r="C196" s="6">
-        <v>1.3222806452820099</v>
+        <v>1.5981561613572</v>
       </c>
       <c r="D196" s="6">
         <v>1.7511991894343999</v>
@@ -12625,16 +12625,16 @@
         <v>2.3663868449578001</v>
       </c>
       <c r="F196" s="6">
-        <v>-4.6923414074696002</v>
+        <v>-3.8542228058008701</v>
       </c>
       <c r="G196" s="6">
-        <v>-2.16946789814472E-2</v>
+        <v>-2.23551142026212E-2</v>
       </c>
       <c r="H196" s="6">
         <v>4.0005818409089199E-2</v>
       </c>
       <c r="I196" s="6">
-        <v>1.1495116675697299</v>
+        <v>1.1469975738137099</v>
       </c>
       <c r="J196" s="6">
         <v>0.27169442679558697</v>
@@ -12675,10 +12675,10 @@
         <v>40087</v>
       </c>
       <c r="B197" s="6">
-        <v>1.7498307402561899</v>
+        <v>1.9224457652567699</v>
       </c>
       <c r="C197" s="6">
-        <v>1.31255726388066</v>
+        <v>1.59112471744866</v>
       </c>
       <c r="D197" s="6">
         <v>1.7444314341161999</v>
@@ -12687,16 +12687,16 @@
         <v>2.381121360008688</v>
       </c>
       <c r="F197" s="6">
-        <v>-3.92949464510485</v>
+        <v>-3.2831938610393099</v>
       </c>
       <c r="G197" s="6">
-        <v>-2.2106988698663801E-2</v>
+        <v>-2.2773430532068002E-2</v>
       </c>
       <c r="H197" s="6">
         <v>3.9742157458295402E-2</v>
       </c>
       <c r="I197" s="6">
-        <v>1.1864181169542301</v>
+        <v>1.17913735429573</v>
       </c>
       <c r="J197" s="6">
         <v>1.0829142871296999</v>
@@ -12737,10 +12737,10 @@
         <v>40179</v>
       </c>
       <c r="B198" s="6">
-        <v>1.7110286428328401</v>
+        <v>1.8888604550246599</v>
       </c>
       <c r="C198" s="6">
-        <v>1.3054031145817799</v>
+        <v>1.5854070257246999</v>
       </c>
       <c r="D198" s="6">
         <v>1.7388774527066</v>
@@ -12749,16 +12749,16 @@
         <v>2.347989937884932</v>
       </c>
       <c r="F198" s="6">
-        <v>-3.7235297994844201</v>
+        <v>-3.1460892121370998</v>
       </c>
       <c r="G198" s="6">
-        <v>-2.1723645736328099E-2</v>
+        <v>-2.21884055042402E-2</v>
       </c>
       <c r="H198" s="6">
         <v>3.98051518839743E-2</v>
       </c>
       <c r="I198" s="6">
-        <v>1.05417268595424</v>
+        <v>1.0567650685885801</v>
       </c>
       <c r="J198" s="6">
         <v>0.28181672390228102</v>
@@ -12799,10 +12799,10 @@
         <v>40269</v>
       </c>
       <c r="B199" s="6">
-        <v>1.7421900282395499</v>
+        <v>1.8995614972524</v>
       </c>
       <c r="C199" s="6">
-        <v>1.2963641038893701</v>
+        <v>1.57903169956616</v>
       </c>
       <c r="D199" s="6">
         <v>1.73272347522779</v>
@@ -12811,16 +12811,16 @@
         <v>2.362876960202192</v>
       </c>
       <c r="F199" s="6">
-        <v>-3.5016070822577499</v>
+        <v>-2.9459216431553199</v>
       </c>
       <c r="G199" s="6">
-        <v>-2.2157254431515502E-2</v>
+        <v>-2.2456558173783801E-2</v>
       </c>
       <c r="H199" s="6">
         <v>3.98668209956662E-2</v>
       </c>
       <c r="I199" s="6">
-        <v>0.94983335557681703</v>
+        <v>0.95748715599868695</v>
       </c>
       <c r="J199" s="6">
         <v>0.15419225209596599</v>
@@ -12861,10 +12861,10 @@
         <v>40360</v>
       </c>
       <c r="B200" s="6">
-        <v>1.72533296156098</v>
+        <v>1.8767902886707799</v>
       </c>
       <c r="C200" s="6">
-        <v>1.2868523829053</v>
+        <v>1.5727158960879</v>
       </c>
       <c r="D200" s="6">
         <v>1.7266780931530299</v>
@@ -12873,16 +12873,16 @@
         <v>2.3488978320252478</v>
       </c>
       <c r="F200" s="6">
-        <v>-3.3236291254984902</v>
+        <v>-2.7315992746098301</v>
       </c>
       <c r="G200" s="6">
-        <v>-2.1907911614041799E-2</v>
+        <v>-2.2012673109674301E-2</v>
       </c>
       <c r="H200" s="6">
         <v>3.9976004182503203E-2</v>
       </c>
       <c r="I200" s="6">
-        <v>0.88304445552353406</v>
+        <v>0.89465618483132403</v>
       </c>
       <c r="J200" s="6">
         <v>-0.48011812283191402</v>
@@ -12923,10 +12923,10 @@
         <v>40452</v>
       </c>
       <c r="B201" s="6">
-        <v>1.6495311858769099</v>
+        <v>1.8250928912242299</v>
       </c>
       <c r="C201" s="6">
-        <v>1.2779065255694499</v>
+        <v>1.5671602923485499</v>
       </c>
       <c r="D201" s="6">
         <v>1.72138922764837</v>
@@ -12935,16 +12935,16 @@
         <v>2.2960278708771882</v>
       </c>
       <c r="F201" s="6">
-        <v>-2.7125932134263699</v>
+        <v>-2.2137755975934401</v>
       </c>
       <c r="G201" s="6">
-        <v>-2.1035044595897699E-2</v>
+        <v>-2.09961555966591E-2</v>
       </c>
       <c r="H201" s="6">
         <v>3.9920039314419203E-2</v>
       </c>
       <c r="I201" s="6">
-        <v>0.81487517934786202</v>
+        <v>0.828505862472111</v>
       </c>
       <c r="J201" s="6">
         <v>0.1102120709062</v>
@@ -12985,10 +12985,10 @@
         <v>40544</v>
       </c>
       <c r="B202" s="6">
-        <v>1.39288634039611</v>
+        <v>1.6780936277366201</v>
       </c>
       <c r="C202" s="6">
-        <v>1.2822678208742999</v>
+        <v>1.5669870335782601</v>
       </c>
       <c r="D202" s="6">
         <v>1.7204542591919301</v>
@@ -12997,16 +12997,16 @@
         <v>2.152073766483944</v>
       </c>
       <c r="F202" s="6">
-        <v>-1.86688094838934</v>
+        <v>-1.4776135087298601</v>
       </c>
       <c r="G202" s="6">
-        <v>-1.8561580862938399E-2</v>
+        <v>-1.8621307300053999E-2</v>
       </c>
       <c r="H202" s="6">
         <v>3.9849419812588598E-2</v>
       </c>
       <c r="I202" s="6">
-        <v>0.78696474606676903</v>
+        <v>0.79800123244915699</v>
       </c>
       <c r="J202" s="6">
         <v>0.54206174815216202</v>
@@ -13047,10 +13047,10 @@
         <v>40634</v>
       </c>
       <c r="B203" s="6">
-        <v>1.4336283485614401</v>
+        <v>1.7007074823074799</v>
       </c>
       <c r="C203" s="6">
-        <v>1.2830704443143199</v>
+        <v>1.5657845151796299</v>
       </c>
       <c r="D203" s="6">
         <v>1.71871396913796</v>
@@ -13059,16 +13059,16 @@
         <v>2.1534878801365802</v>
       </c>
       <c r="F203" s="6">
-        <v>-1.45018310295933</v>
+        <v>-1.1945420418419399</v>
       </c>
       <c r="G203" s="6">
-        <v>-1.89568741948999E-2</v>
+        <v>-1.8867198571171799E-2</v>
       </c>
       <c r="H203" s="6">
         <v>3.9729621673674602E-2</v>
       </c>
       <c r="I203" s="6">
-        <v>0.81184144840629802</v>
+        <v>0.81531772340522302</v>
       </c>
       <c r="J203" s="6">
         <v>1.16083105799426</v>
@@ -13109,10 +13109,10 @@
         <v>40725</v>
       </c>
       <c r="B204" s="6">
-        <v>1.3109895556978199</v>
+        <v>1.6219609446277401</v>
       </c>
       <c r="C204" s="6">
-        <v>1.2924304413177199</v>
+        <v>1.56806485558679</v>
       </c>
       <c r="D204" s="6">
         <v>1.71967837389293</v>
@@ -13121,16 +13121,16 @@
         <v>2.0821824653849119</v>
       </c>
       <c r="F204" s="6">
-        <v>-1.23086725203268</v>
+        <v>-1.01685110906453</v>
       </c>
       <c r="G204" s="6">
-        <v>-1.7926316342121301E-2</v>
+        <v>-1.77768728047181E-2</v>
       </c>
       <c r="H204" s="6">
         <v>3.9731908293277302E-2</v>
       </c>
       <c r="I204" s="6">
-        <v>0.74751614045508696</v>
+        <v>0.75425108931239604</v>
       </c>
       <c r="J204" s="6">
         <v>0.62977441248172195</v>
@@ -13171,10 +13171,10 @@
         <v>40817</v>
       </c>
       <c r="B205" s="6">
-        <v>1.4508512805504801</v>
+        <v>1.6896468320822899</v>
       </c>
       <c r="C205" s="6">
-        <v>1.29437553646696</v>
+        <v>1.5675840304670701</v>
       </c>
       <c r="D205" s="6">
         <v>1.7186999155510601</v>
@@ -13183,16 +13183,16 @@
         <v>2.1463654853880358</v>
       </c>
       <c r="F205" s="6">
-        <v>-1.44279250169808</v>
+        <v>-1.1720532730031401</v>
       </c>
       <c r="G205" s="6">
-        <v>-1.9124662050234099E-2</v>
+        <v>-1.8781636452287701E-2</v>
       </c>
       <c r="H205" s="6">
         <v>3.9768474087676503E-2</v>
       </c>
       <c r="I205" s="6">
-        <v>0.70122165437545303</v>
+        <v>0.71181850205194797</v>
       </c>
       <c r="J205" s="6">
         <v>0.44463418666501098</v>
@@ -13233,10 +13233,10 @@
         <v>40909</v>
       </c>
       <c r="B206" s="6">
-        <v>1.4664241642074101</v>
+        <v>1.70544084183749</v>
       </c>
       <c r="C206" s="6">
-        <v>1.29398587444797</v>
+        <v>1.5662562624716401</v>
       </c>
       <c r="D206" s="6">
         <v>1.71708964624843</v>
@@ -13245,16 +13245,16 @@
         <v>2.1407864938206882</v>
       </c>
       <c r="F206" s="6">
-        <v>-0.69712863585977003</v>
+        <v>-0.59797704565062304</v>
       </c>
       <c r="G206" s="6">
-        <v>-1.9404260924483101E-2</v>
+        <v>-1.8963911993907401E-2</v>
       </c>
       <c r="H206" s="6">
         <v>3.9662718197324101E-2</v>
       </c>
       <c r="I206" s="6">
-        <v>0.73831100119807302</v>
+        <v>0.74976258673850404</v>
       </c>
       <c r="J206" s="6">
         <v>1.2178814166302501</v>
@@ -13295,10 +13295,10 @@
         <v>41000</v>
       </c>
       <c r="B207" s="6">
-        <v>1.40337995019442</v>
+        <v>1.6557330370160399</v>
       </c>
       <c r="C207" s="6">
-        <v>1.29561177011701</v>
+        <v>1.5660287433794899</v>
       </c>
       <c r="D207" s="6">
         <v>1.7164068279932101</v>
@@ -13307,16 +13307,16 @@
         <v>2.1069991469726039</v>
       </c>
       <c r="F207" s="6">
-        <v>-0.59307796581020999</v>
+        <v>-0.50041795953256996</v>
       </c>
       <c r="G207" s="6">
-        <v>-1.86688542889312E-2</v>
+        <v>-1.8173084270651899E-2</v>
       </c>
       <c r="H207" s="6">
         <v>3.9671645681036899E-2</v>
       </c>
       <c r="I207" s="6">
-        <v>0.712549020344588</v>
+        <v>0.72943389912385903</v>
       </c>
       <c r="J207" s="6">
         <v>0.54938881767648795</v>
@@ -13357,10 +13357,10 @@
         <v>41091</v>
       </c>
       <c r="B208" s="6">
-        <v>1.2824876746398599</v>
+        <v>1.5725183140994901</v>
       </c>
       <c r="C208" s="6">
-        <v>1.30369622527688</v>
+        <v>1.5686002431493999</v>
       </c>
       <c r="D208" s="6">
         <v>1.7178940104495399</v>
@@ -13369,16 +13369,16 @@
         <v>2.0441170626227319</v>
       </c>
       <c r="F208" s="6">
-        <v>-0.55020931985330901</v>
+        <v>-0.458745079206551</v>
       </c>
       <c r="G208" s="6">
-        <v>-1.7412991205836999E-2</v>
+        <v>-1.6946950885141199E-2</v>
       </c>
       <c r="H208" s="6">
         <v>3.9666568419565798E-2</v>
       </c>
       <c r="I208" s="6">
-        <v>0.69612237175151004</v>
+        <v>0.714291548997665</v>
       </c>
       <c r="J208" s="6">
         <v>5.2639480377397199E-2</v>
@@ -13419,10 +13419,10 @@
         <v>41183</v>
       </c>
       <c r="B209" s="6">
-        <v>1.19296000185822</v>
+        <v>1.5149632159369999</v>
       </c>
       <c r="C209" s="6">
-        <v>1.3194610415219099</v>
+        <v>1.5740835882836499</v>
       </c>
       <c r="D209" s="6">
         <v>1.7215597204633299</v>
@@ -13431,16 +13431,16 @@
         <v>1.9852320946191919</v>
       </c>
       <c r="F209" s="6">
-        <v>-0.30141789480558101</v>
+        <v>-0.253770100363226</v>
       </c>
       <c r="G209" s="6">
-        <v>-1.66963155434116E-2</v>
+        <v>-1.6190883369262499E-2</v>
       </c>
       <c r="H209" s="6">
         <v>3.96635671425545E-2</v>
       </c>
       <c r="I209" s="6">
-        <v>0.66197933392419905</v>
+        <v>0.68070582956187997</v>
       </c>
       <c r="J209" s="6">
         <v>0.56647538245474904</v>
@@ -13481,10 +13481,10 @@
         <v>41275</v>
       </c>
       <c r="B210" s="6">
-        <v>1.36083708949886</v>
+        <v>1.59102974199632</v>
       </c>
       <c r="C210" s="6">
-        <v>1.32506951994061</v>
+        <v>1.57629543533255</v>
       </c>
       <c r="D210" s="6">
         <v>1.7228603347895399</v>
@@ -13493,16 +13493,16 @@
         <v>2.0526718726698241</v>
       </c>
       <c r="F210" s="6">
-        <v>-0.54777955110745302</v>
+        <v>-0.40407824238218398</v>
       </c>
       <c r="G210" s="6">
-        <v>-1.8023925962720001E-2</v>
+        <v>-1.71260477207438E-2</v>
       </c>
       <c r="H210" s="6">
         <v>3.9668062150389899E-2</v>
       </c>
       <c r="I210" s="6">
-        <v>0.62521938982129299</v>
+        <v>0.64489007107724805</v>
       </c>
       <c r="J210" s="6">
         <v>0.47297322317773999</v>
@@ -13543,10 +13543,10 @@
         <v>41365</v>
       </c>
       <c r="B211" s="6">
-        <v>1.2625901163495501</v>
+        <v>1.52613442157375</v>
       </c>
       <c r="C211" s="6">
-        <v>1.33812528035157</v>
+        <v>1.5812963175019801</v>
       </c>
       <c r="D211" s="6">
         <v>1.7262468347679301</v>
@@ -13555,16 +13555,16 @@
         <v>2.0052629611086319</v>
       </c>
       <c r="F211" s="6">
-        <v>-0.45258364388985201</v>
+        <v>-0.32515204593562402</v>
       </c>
       <c r="G211" s="6">
-        <v>-1.7125725267625298E-2</v>
+        <v>-1.6339901604088498E-2</v>
       </c>
       <c r="H211" s="6">
         <v>3.9661711622805997E-2</v>
       </c>
       <c r="I211" s="6">
-        <v>0.60695044355018501</v>
+        <v>0.62813530142225005</v>
       </c>
       <c r="J211" s="6">
         <v>2.0851464010232901E-2</v>
@@ -13605,10 +13605,10 @@
         <v>41456</v>
       </c>
       <c r="B212" s="6">
-        <v>1.35571689754859</v>
+        <v>1.5747186613720201</v>
       </c>
       <c r="C212" s="6">
-        <v>1.34601745148063</v>
+        <v>1.58448964531096</v>
       </c>
       <c r="D212" s="6">
         <v>1.72832237036962</v>
@@ -13617,16 +13617,16 @@
         <v>2.0373403567013439</v>
       </c>
       <c r="F212" s="6">
-        <v>-0.27453224553147498</v>
+        <v>-0.17394605702145299</v>
       </c>
       <c r="G212" s="6">
-        <v>-1.78901641503285E-2</v>
+        <v>-1.6870909482714101E-2</v>
       </c>
       <c r="H212" s="6">
         <v>3.9643109280154201E-2</v>
       </c>
       <c r="I212" s="6">
-        <v>0.587629863159979</v>
+        <v>0.60740892749749897</v>
       </c>
       <c r="J212" s="6">
         <v>0.45712204427105102</v>
@@ -13667,10 +13667,10 @@
         <v>41548</v>
       </c>
       <c r="B213" s="6">
-        <v>1.4236550737377101</v>
+        <v>1.6121670943077999</v>
       </c>
       <c r="C213" s="6">
-        <v>1.3464083310997601</v>
+        <v>1.5853109703011901</v>
       </c>
       <c r="D213" s="6">
         <v>1.728731877128</v>
@@ -13679,16 +13679,16 @@
         <v>2.0627851946312918</v>
       </c>
       <c r="F213" s="6">
-        <v>2.32769954794776E-3</v>
+        <v>3.7935988265530803E-2</v>
       </c>
       <c r="G213" s="6">
-        <v>-1.85361007159974E-2</v>
+        <v>-1.7324929622980101E-2</v>
       </c>
       <c r="H213" s="6">
         <v>3.9635010864136899E-2</v>
       </c>
       <c r="I213" s="6">
-        <v>0.56542895581424002</v>
+        <v>0.58381751512174096</v>
       </c>
       <c r="J213" s="6">
         <v>0.62292560914572603</v>
@@ -13729,10 +13729,10 @@
         <v>41640</v>
       </c>
       <c r="B214" s="6">
-        <v>1.1072125672069999</v>
+        <v>1.4214784178819699</v>
       </c>
       <c r="C214" s="6">
-        <v>1.36894780308162</v>
+        <v>1.5944319762917001</v>
       </c>
       <c r="D214" s="6">
         <v>1.73522646815165</v>
@@ -13741,16 +13741,16 @@
         <v>1.9111633436864559</v>
       </c>
       <c r="F214" s="6">
-        <v>0.25756627741111499</v>
+        <v>0.22782552815374399</v>
       </c>
       <c r="G214" s="6">
-        <v>-1.55367148542341E-2</v>
+        <v>-1.4976181703599401E-2</v>
       </c>
       <c r="H214" s="6">
         <v>3.9564171873053798E-2</v>
       </c>
       <c r="I214" s="6">
-        <v>0.55410480131296502</v>
+        <v>0.57398179020203</v>
       </c>
       <c r="J214" s="6">
         <v>0.13023735191119201</v>
@@ -13791,10 +13791,10 @@
         <v>41730</v>
       </c>
       <c r="B215" s="6">
-        <v>1.24080287357754</v>
+        <v>1.5169063591674801</v>
       </c>
       <c r="C215" s="6">
-        <v>1.3841819522274701</v>
+        <v>1.6002665226014401</v>
       </c>
       <c r="D215" s="6">
         <v>1.7393287857580599</v>
@@ -13803,16 +13803,16 @@
         <v>1.9793525562905721</v>
       </c>
       <c r="F215" s="6">
-        <v>0.51241331157035597</v>
+        <v>0.34447394186042901</v>
       </c>
       <c r="G215" s="6">
-        <v>-1.6367181202023101E-2</v>
+        <v>-1.5844499149463401E-2</v>
       </c>
       <c r="H215" s="6">
         <v>3.9575328683980698E-2</v>
       </c>
       <c r="I215" s="6">
-        <v>0.549738156301946</v>
+        <v>0.56838780527454902</v>
       </c>
       <c r="J215" s="6">
         <v>0.68289638920518902</v>
@@ -13853,10 +13853,10 @@
         <v>41821</v>
       </c>
       <c r="B216" s="6">
-        <v>1.3003078794612499</v>
+        <v>1.56599065962321</v>
       </c>
       <c r="C216" s="6">
-        <v>1.3954262263525901</v>
+        <v>1.6041402806823599</v>
       </c>
       <c r="D216" s="6">
         <v>1.7418848544416701</v>
@@ -13865,16 +13865,16 @@
         <v>2.024663234456908</v>
       </c>
       <c r="F216" s="6">
-        <v>0.80920291228017105</v>
+        <v>0.52904709275344397</v>
       </c>
       <c r="G216" s="6">
-        <v>-1.6863128581057402E-2</v>
+        <v>-1.6417514043466801E-2</v>
       </c>
       <c r="H216" s="6">
         <v>3.9544343194512402E-2</v>
       </c>
       <c r="I216" s="6">
-        <v>0.53020218877523295</v>
+        <v>0.54919443945441504</v>
       </c>
       <c r="J216" s="6">
         <v>0.49698621153494199</v>
@@ -13915,10 +13915,10 @@
         <v>41913</v>
       </c>
       <c r="B217" s="6">
-        <v>1.2701772947898999</v>
+        <v>1.5371065097571599</v>
       </c>
       <c r="C217" s="6">
-        <v>1.4092864920085699</v>
+        <v>1.60916625937111</v>
       </c>
       <c r="D217" s="6">
         <v>1.74547592228785</v>
@@ -13927,16 +13927,16 @@
         <v>2.0100755984767682</v>
       </c>
       <c r="F217" s="6">
-        <v>0.78250646315461803</v>
+        <v>0.54267234447183899</v>
       </c>
       <c r="G217" s="6">
-        <v>-1.6645380556435802E-2</v>
+        <v>-1.6142388917283802E-2</v>
       </c>
       <c r="H217" s="6">
         <v>3.9426282904250903E-2</v>
       </c>
       <c r="I217" s="6">
-        <v>0.53766516394991504</v>
+        <v>0.55583854113102404</v>
       </c>
       <c r="J217" s="6">
         <v>5.2129136238447997E-2</v>
@@ -13977,10 +13977,10 @@
         <v>42005</v>
       </c>
       <c r="B218" s="6">
-        <v>1.33383559761415</v>
+        <v>1.5690912666480199</v>
       </c>
       <c r="C218" s="6">
-        <v>1.41975061339501</v>
+        <v>1.6127959660204001</v>
       </c>
       <c r="D218" s="6">
         <v>1.74797240325291</v>
@@ -13989,16 +13989,16 @@
         <v>2.0552159899348119</v>
       </c>
       <c r="F218" s="6">
-        <v>0.64045688584718596</v>
+        <v>0.470788621222823</v>
       </c>
       <c r="G218" s="6">
-        <v>-1.71304817574028E-2</v>
+        <v>-1.65549062857763E-2</v>
       </c>
       <c r="H218" s="6">
         <v>3.9301907953157897E-2</v>
       </c>
       <c r="I218" s="6">
-        <v>0.562870039279596</v>
+        <v>0.57921519837035296</v>
       </c>
       <c r="J218" s="6">
         <v>-0.288371189233942</v>
@@ -14039,10 +14039,10 @@
         <v>42095</v>
       </c>
       <c r="B219" s="6">
-        <v>1.3264739837469799</v>
+        <v>1.56723428197367</v>
       </c>
       <c r="C219" s="6">
-        <v>1.42963269031371</v>
+        <v>1.6163444646280201</v>
       </c>
       <c r="D219" s="6">
         <v>1.7504682291935101</v>
@@ -14051,16 +14051,16 @@
         <v>2.031290523473992</v>
       </c>
       <c r="F219" s="6">
-        <v>1.1584878334236901</v>
+        <v>0.91491566796639801</v>
       </c>
       <c r="G219" s="6">
-        <v>-1.71607057783595E-2</v>
+        <v>-1.6503257497468601E-2</v>
       </c>
       <c r="H219" s="6">
         <v>3.94580235208234E-2</v>
       </c>
       <c r="I219" s="6">
-        <v>0.60799707031109096</v>
+        <v>0.62765436409845599</v>
       </c>
       <c r="J219" s="6">
         <v>0.66082201281890796</v>
@@ -14101,10 +14101,10 @@
         <v>42186</v>
       </c>
       <c r="B220" s="6">
-        <v>1.28916826159725</v>
+        <v>1.5334794309745401</v>
       </c>
       <c r="C220" s="6">
-        <v>1.4411277278065</v>
+        <v>1.62079688487873</v>
       </c>
       <c r="D220" s="6">
         <v>1.75367327424036</v>
@@ -14113,16 +14113,16 @@
         <v>2.0076443599326121</v>
       </c>
       <c r="F220" s="6">
-        <v>1.1479009185023299</v>
+        <v>0.92771275514792295</v>
       </c>
       <c r="G220" s="6">
-        <v>-1.6887873263007301E-2</v>
+        <v>-1.6155563001262599E-2</v>
       </c>
       <c r="H220" s="6">
         <v>3.9379083648224698E-2</v>
       </c>
       <c r="I220" s="6">
-        <v>0.58335467690137799</v>
+        <v>0.60409101450938196</v>
       </c>
       <c r="J220" s="6">
         <v>0.26016267364765899</v>
@@ -14163,10 +14163,10 @@
         <v>42278</v>
       </c>
       <c r="B221" s="6">
-        <v>1.2055252304214401</v>
+        <v>1.47164623036886</v>
       </c>
       <c r="C221" s="6">
-        <v>1.4589466874657799</v>
+        <v>1.62774992606826</v>
       </c>
       <c r="D221" s="6">
         <v>1.7587950660956899</v>
@@ -14175,16 +14175,16 @@
         <v>1.9614663687209479</v>
       </c>
       <c r="F221" s="6">
-        <v>1.09625691571824</v>
+        <v>0.87746957471938503</v>
       </c>
       <c r="G221" s="6">
-        <v>-1.62991696588386E-2</v>
+        <v>-1.5549349015349699E-2</v>
       </c>
       <c r="H221" s="6">
         <v>3.92866172482935E-2</v>
       </c>
       <c r="I221" s="6">
-        <v>0.56498649162991199</v>
+        <v>0.58547964689339405</v>
       </c>
       <c r="J221" s="6">
         <v>-4.4761789219742E-3</v>
@@ -14225,10 +14225,10 @@
         <v>42370</v>
       </c>
       <c r="B222" s="6">
-        <v>1.2729673923817799</v>
+        <v>1.50410644818218</v>
       </c>
       <c r="C222" s="6">
-        <v>1.47311689333256</v>
+        <v>1.6336068692479799</v>
       </c>
       <c r="D222" s="6">
         <v>1.7631169133614999</v>
@@ -14237,16 +14237,16 @@
         <v>1.972992904344568</v>
       </c>
       <c r="F222" s="6">
-        <v>1.2353910472718299</v>
+        <v>0.99342406631694802</v>
       </c>
       <c r="G222" s="6">
-        <v>-1.67655187672456E-2</v>
+        <v>-1.5835023135914901E-2</v>
       </c>
       <c r="H222" s="6">
         <v>3.9424781934948798E-2</v>
       </c>
       <c r="I222" s="6">
-        <v>0.57324764916799298</v>
+        <v>0.59353159986483905</v>
       </c>
       <c r="J222" s="6">
         <v>0.67712448208049203</v>
@@ -14287,10 +14287,10 @@
         <v>42461</v>
       </c>
       <c r="B223" s="6">
-        <v>1.2246407536497499</v>
+        <v>1.4738400131298599</v>
       </c>
       <c r="C223" s="6">
-        <v>1.49268551856396</v>
+        <v>1.64126445145122</v>
       </c>
       <c r="D223" s="6">
         <v>1.7687447589641101</v>
@@ -14299,16 +14299,16 @@
         <v>1.932689391141116</v>
       </c>
       <c r="F223" s="6">
-        <v>1.5222412376302299</v>
+        <v>1.21179092213811</v>
       </c>
       <c r="G223" s="6">
-        <v>-1.6453145850984299E-2</v>
+        <v>-1.55223653002783E-2</v>
       </c>
       <c r="H223" s="6">
         <v>3.9611330563128197E-2</v>
       </c>
       <c r="I223" s="6">
-        <v>0.58851508306739198</v>
+        <v>0.60714264135819196</v>
       </c>
       <c r="J223" s="6">
         <v>1.1216511725913401</v>
@@ -14349,10 +14349,10 @@
         <v>42552</v>
       </c>
       <c r="B224" s="6">
-        <v>1.3463006374107001</v>
+        <v>1.53071663481733</v>
       </c>
       <c r="C224" s="6">
-        <v>1.5063645984514999</v>
+        <v>1.6470043608896301</v>
       </c>
       <c r="D224" s="6">
         <v>1.77298880003314</v>
@@ -14361,16 +14361,16 @@
         <v>1.980508326966876</v>
       </c>
       <c r="F224" s="6">
-        <v>1.3438395779988399</v>
+        <v>1.0899187480214301</v>
       </c>
       <c r="G224" s="6">
-        <v>-1.73395453851946E-2</v>
+        <v>-1.6091466858331301E-2</v>
       </c>
       <c r="H224" s="6">
         <v>3.9552694429925497E-2</v>
       </c>
       <c r="I224" s="6">
-        <v>0.56268066196999</v>
+        <v>0.58215702438571304</v>
       </c>
       <c r="J224" s="6">
         <v>0.72930593961898804</v>
@@ -14411,10 +14411,10 @@
         <v>42644</v>
       </c>
       <c r="B225" s="6">
-        <v>1.35997777656984</v>
+        <v>1.53292728286276</v>
       </c>
       <c r="C225" s="6">
-        <v>1.5203632825272599</v>
+        <v>1.6528295388905201</v>
       </c>
       <c r="D225" s="6">
         <v>1.77729570078202</v>
@@ -14423,16 +14423,16 @@
         <v>1.98974935673862</v>
       </c>
       <c r="F225" s="6">
-        <v>1.2583525099633399</v>
+        <v>1.0300854910241199</v>
       </c>
       <c r="G225" s="6">
-        <v>-1.7446299861351201E-2</v>
+        <v>-1.6129256997704799E-2</v>
       </c>
       <c r="H225" s="6">
         <v>3.94326899818042E-2</v>
       </c>
       <c r="I225" s="6">
-        <v>0.552632599443316</v>
+        <v>0.57159006317750105</v>
       </c>
       <c r="J225" s="6">
         <v>0.42276592030314403</v>
@@ -14473,10 +14473,10 @@
         <v>42736</v>
       </c>
       <c r="B226" s="6">
-        <v>1.35488178089422</v>
+        <v>1.5252161086560001</v>
       </c>
       <c r="C226" s="6">
-        <v>1.53731253295268</v>
+        <v>1.6596132666791501</v>
       </c>
       <c r="D226" s="6">
         <v>1.7822313553414899</v>
@@ -14485,16 +14485,16 @@
         <v>1.9770538473422039</v>
       </c>
       <c r="F226" s="6">
-        <v>1.4007945741047401</v>
+        <v>1.14861908427406</v>
       </c>
       <c r="G226" s="6">
-        <v>-1.73713911510965E-2</v>
+        <v>-1.6016995414534101E-2</v>
       </c>
       <c r="H226" s="6">
         <v>3.95037932332679E-2</v>
       </c>
       <c r="I226" s="6">
-        <v>0.53420195230316603</v>
+        <v>0.55409628107563202</v>
       </c>
       <c r="J226" s="6">
         <v>0.86453917340754305</v>
@@ -14535,10 +14535,10 @@
         <v>42826</v>
       </c>
       <c r="B227" s="6">
-        <v>1.3858929615168101</v>
+        <v>1.5338945958469801</v>
       </c>
       <c r="C227" s="6">
-        <v>1.5566323991857001</v>
+        <v>1.6670315630113599</v>
       </c>
       <c r="D227" s="6">
         <v>1.7875149000885</v>
@@ -14547,16 +14547,16 @@
         <v>1.996616127552076</v>
       </c>
       <c r="F227" s="6">
-        <v>1.1699051528726201</v>
+        <v>0.99818289244376501</v>
       </c>
       <c r="G227" s="6">
-        <v>-1.7671733905280401E-2</v>
+        <v>-1.6146393099568501E-2</v>
       </c>
       <c r="H227" s="6">
         <v>3.9311237085224902E-2</v>
       </c>
       <c r="I227" s="6">
-        <v>0.54761959042290098</v>
+        <v>0.56635654274701597</v>
       </c>
       <c r="J227" s="6">
         <v>0.373393065634327</v>
@@ -14597,10 +14597,10 @@
         <v>42917</v>
       </c>
       <c r="B228" s="6">
-        <v>1.51192761148522</v>
+        <v>1.59661274026464</v>
       </c>
       <c r="C228" s="6">
-        <v>1.57219760773853</v>
+        <v>1.6730860941362999</v>
       </c>
       <c r="D228" s="6">
         <v>1.7918196182372701</v>
@@ -14609,16 +14609,16 @@
         <v>2.0514281491531761</v>
       </c>
       <c r="F228" s="6">
-        <v>0.96730065409650501</v>
+        <v>0.89222277285034601</v>
       </c>
       <c r="G228" s="6">
-        <v>-1.8898272107960499E-2</v>
+        <v>-1.6841825809640901E-2</v>
       </c>
       <c r="H228" s="6">
         <v>3.92260964719452E-2</v>
       </c>
       <c r="I228" s="6">
-        <v>0.53660303829482103</v>
+        <v>0.554616365258638</v>
       </c>
       <c r="J228" s="6">
         <v>0.29135234630198498</v>
@@ -14659,10 +14659,10 @@
         <v>43009</v>
       </c>
       <c r="B229" s="6">
-        <v>1.7486767876434599</v>
+        <v>1.72954822417577</v>
       </c>
       <c r="C229" s="6">
-        <v>1.5718921118792499</v>
+        <v>1.6740843348661101</v>
       </c>
       <c r="D229" s="6">
         <v>1.7925798947101901</v>
@@ -14671,16 +14671,16 @@
         <v>2.141756345421904</v>
       </c>
       <c r="F229" s="6">
-        <v>1.0621816623124101</v>
+        <v>1.0030380333140601</v>
       </c>
       <c r="G229" s="6">
-        <v>-2.14021229628533E-2</v>
+        <v>-1.8237738800807798E-2</v>
       </c>
       <c r="H229" s="6">
         <v>3.9324158649941397E-2</v>
       </c>
       <c r="I229" s="6">
-        <v>0.53756252817901795</v>
+        <v>0.55559262888639305</v>
       </c>
       <c r="J229" s="6">
         <v>0.901673821233129</v>
@@ -14721,10 +14721,10 @@
         <v>43101</v>
       </c>
       <c r="B230" s="6">
-        <v>1.7899579372098</v>
+        <v>1.76170660653502</v>
       </c>
       <c r="C230" s="6">
-        <v>1.56866795780168</v>
+        <v>1.6739085722368201</v>
       </c>
       <c r="D230" s="6">
         <v>1.7924381814354799</v>
@@ -14733,16 +14733,16 @@
         <v>2.1473611410601441</v>
       </c>
       <c r="F230" s="6">
-        <v>1.601791187858</v>
+        <v>1.3880458013491099</v>
       </c>
       <c r="G230" s="6">
-        <v>-2.1787682122501401E-2</v>
+        <v>-1.8539151146712202E-2</v>
       </c>
       <c r="H230" s="6">
         <v>3.9594849023863801E-2</v>
       </c>
       <c r="I230" s="6">
-        <v>0.61062401953254097</v>
+        <v>0.623932181209081</v>
       </c>
       <c r="J230" s="6">
         <v>1.62813725506434</v>
@@ -14783,10 +14783,10 @@
         <v>43191</v>
       </c>
       <c r="B231" s="6">
-        <v>1.74545615675751</v>
+        <v>1.7378433110193301</v>
       </c>
       <c r="C231" s="6">
-        <v>1.5680839243717299</v>
+        <v>1.67453773857801</v>
       </c>
       <c r="D231" s="6">
         <v>1.79273788939954</v>
@@ -14795,16 +14795,16 @@
         <v>2.132301287513112</v>
       </c>
       <c r="F231" s="6">
-        <v>1.73036628571322</v>
+        <v>1.4908318601502499</v>
       </c>
       <c r="G231" s="6">
-        <v>-2.1125000631461499E-2</v>
+        <v>-1.8228261606333701E-2</v>
       </c>
       <c r="H231" s="6">
         <v>3.9582964027063801E-2</v>
       </c>
       <c r="I231" s="6">
-        <v>0.57883772410785705</v>
+        <v>0.59327182682752699</v>
       </c>
       <c r="J231" s="6">
         <v>1.1402378487146101</v>
@@ -14845,10 +14845,10 @@
         <v>43282</v>
       </c>
       <c r="B232" s="6">
-        <v>1.7565930676244901</v>
+        <v>1.7458559400237701</v>
       </c>
       <c r="C232" s="6">
-        <v>1.5634671358526</v>
+        <v>1.6741010981369699</v>
       </c>
       <c r="D232" s="6">
         <v>1.7923141855263001</v>
@@ -14857,16 +14857,16 @@
         <v>2.1587818867784199</v>
       </c>
       <c r="F232" s="6">
-        <v>1.47315817442166</v>
+        <v>1.3172755339922999</v>
       </c>
       <c r="G232" s="6">
-        <v>-2.1374177866343401E-2</v>
+        <v>-1.8392713842644199E-2</v>
       </c>
       <c r="H232" s="6">
         <v>3.9256670134426297E-2</v>
       </c>
       <c r="I232" s="6">
-        <v>0.63152654202196501</v>
+        <v>0.64710274109212595</v>
       </c>
       <c r="J232" s="6">
         <v>0.273717196683541</v>
@@ -14907,10 +14907,10 @@
         <v>43374</v>
       </c>
       <c r="B233" s="6">
-        <v>1.58752795849072</v>
+        <v>1.65153969891333</v>
       </c>
       <c r="C233" s="6">
-        <v>1.5736276524758901</v>
+        <v>1.6781876223285199</v>
       </c>
       <c r="D233" s="6">
         <v>1.79487794924774</v>
@@ -14919,16 +14919,16 @@
         <v>2.08573258940562</v>
       </c>
       <c r="F233" s="6">
-        <v>1.5809482468584399</v>
+        <v>1.3866965457101501</v>
       </c>
       <c r="G233" s="6">
-        <v>-1.93385407549845E-2</v>
+        <v>-1.73297950511924E-2</v>
       </c>
       <c r="H233" s="6">
         <v>3.9324213008088103E-2</v>
       </c>
       <c r="I233" s="6">
-        <v>0.59869069507500094</v>
+        <v>0.61617981297378199</v>
       </c>
       <c r="J233" s="6">
         <v>0.94380277129398904</v>
@@ -14969,10 +14969,10 @@
         <v>43466</v>
       </c>
       <c r="B234" s="6">
-        <v>1.6565320085241899</v>
+        <v>1.6931908109418801</v>
       </c>
       <c r="C234" s="6">
-        <v>1.5807896485206401</v>
+        <v>1.6811668909330699</v>
       </c>
       <c r="D234" s="6">
         <v>1.79651776075034</v>
@@ -14981,16 +14981,16 @@
         <v>2.1262275877499199</v>
       </c>
       <c r="F234" s="6">
-        <v>1.3438979521055801</v>
+        <v>1.1977891608087201</v>
       </c>
       <c r="G234" s="6">
-        <v>-1.9966279684680802E-2</v>
+        <v>-1.77175573593162E-2</v>
       </c>
       <c r="H234" s="6">
         <v>3.9213542877347102E-2</v>
       </c>
       <c r="I234" s="6">
-        <v>0.58437102619645698</v>
+        <v>0.60140166766770398</v>
       </c>
       <c r="J234" s="6">
         <v>0.67753537061639302</v>
@@ -15031,10 +15031,10 @@
         <v>43556</v>
       </c>
       <c r="B235" s="6">
-        <v>1.7686385992157501</v>
+        <v>1.7663957045685501</v>
       </c>
       <c r="C235" s="6">
-        <v>1.5816815462985101</v>
+        <v>1.68159756564549</v>
       </c>
       <c r="D235" s="6">
         <v>1.7962639918412899</v>
@@ -15043,16 +15043,16 @@
         <v>2.1842598167485199</v>
       </c>
       <c r="F235" s="6">
-        <v>1.2846182533439201</v>
+        <v>1.1484748547221699</v>
       </c>
       <c r="G235" s="6">
-        <v>-2.07899270434862E-2</v>
+        <v>-1.8255875044098799E-2</v>
       </c>
       <c r="H235" s="6">
         <v>3.9209964599998502E-2</v>
       </c>
       <c r="I235" s="6">
-        <v>0.55662759633261405</v>
+        <v>0.57404498541155702</v>
       </c>
       <c r="J235" s="6">
         <v>0.76317824012694402</v>
@@ -15093,10 +15093,10 @@
         <v>43647</v>
       </c>
       <c r="B236" s="6">
-        <v>1.9525248184148201</v>
+        <v>1.8873927161558</v>
       </c>
       <c r="C236" s="6">
-        <v>1.5649589119812899</v>
+        <v>1.67578843995086</v>
       </c>
       <c r="D236" s="6">
         <v>1.7915910883445101</v>
@@ -15105,16 +15105,16 @@
         <v>2.284288006606376</v>
       </c>
       <c r="F236" s="6">
-        <v>1.2325922192523</v>
+        <v>1.12529305931878</v>
       </c>
       <c r="G236" s="6">
-        <v>-2.2135893125001999E-2</v>
+        <v>-1.90897004502147E-2</v>
       </c>
       <c r="H236" s="6">
         <v>3.9156461241587101E-2</v>
       </c>
       <c r="I236" s="6">
-        <v>0.53759881208717697</v>
+        <v>0.55538590191162396</v>
       </c>
       <c r="J236" s="6">
         <v>0.64067199353429605</v>
@@ -15155,10 +15155,10 @@
         <v>43739</v>
       </c>
       <c r="B237" s="6">
-        <v>1.93038803978999</v>
+        <v>1.8813112537363901</v>
       </c>
       <c r="C237" s="6">
-        <v>1.53995864911653</v>
+        <v>1.6677760903419501</v>
       </c>
       <c r="D237" s="6">
         <v>1.7853707525984199</v>
@@ -15167,16 +15167,16 @@
         <v>2.2871213921804401</v>
       </c>
       <c r="F237" s="6">
-        <v>1.2844251434476099</v>
+        <v>1.2027008560686501</v>
       </c>
       <c r="G237" s="6">
-        <v>-2.1965298694405298E-2</v>
+        <v>-1.90560798179258E-2</v>
       </c>
       <c r="H237" s="6">
         <v>3.9086537387403301E-2</v>
       </c>
       <c r="I237" s="6">
-        <v>0.52283026697491597</v>
+        <v>0.54012443208814798</v>
       </c>
       <c r="J237" s="6">
         <v>0.58220534399771695</v>
@@ -15217,10 +15217,10 @@
         <v>43831</v>
       </c>
       <c r="B238" s="6">
-        <v>1.35182209418787</v>
+        <v>1.5086980516725601</v>
       </c>
       <c r="C238" s="6">
-        <v>1.5580038752726599</v>
+        <v>1.67492827829048</v>
       </c>
       <c r="D238" s="6">
         <v>1.7903908321520401</v>
@@ -15229,16 +15229,16 @@
         <v>1.981653863339</v>
       </c>
       <c r="F238" s="6">
-        <v>1.2682558209824</v>
+        <v>1.1252723063932999</v>
       </c>
       <c r="G238" s="6">
-        <v>-1.61741037839086E-2</v>
+        <v>-1.54552815584919E-2</v>
       </c>
       <c r="H238" s="6">
         <v>3.9157141122953397E-2</v>
       </c>
       <c r="I238" s="6">
-        <v>0.50897721121695605</v>
+        <v>0.52745276077945302</v>
       </c>
       <c r="J238" s="6">
         <v>0.775973293085368</v>
@@ -15279,10 +15279,10 @@
         <v>43922</v>
       </c>
       <c r="B239" s="6">
-        <v>1.2734817042009901</v>
+        <v>1.4668704544470099</v>
       </c>
       <c r="C239" s="6">
-        <v>1.5778867238675001</v>
+        <v>1.6825864366393299</v>
       </c>
       <c r="D239" s="6">
         <v>1.79582771381115</v>
@@ -15291,16 +15291,16 @@
         <v>2.0223673803636562</v>
       </c>
       <c r="F239" s="6">
-        <v>-4.6911984042360997</v>
+        <v>-8.0188341148833597</v>
       </c>
       <c r="G239" s="6">
-        <v>-1.57484396752356E-2</v>
+        <v>-1.5330918809595501E-2</v>
       </c>
       <c r="H239" s="6">
         <v>3.8360562714448702E-2</v>
       </c>
       <c r="I239" s="6">
-        <v>2.41816333556728</v>
+        <v>2.3025249047618801</v>
       </c>
       <c r="J239" s="6">
         <v>-1.05658291249103</v>
@@ -15341,10 +15341,10 @@
         <v>44013</v>
       </c>
       <c r="B240" s="6">
-        <v>1.2816911962647499</v>
+        <v>1.47229219648501</v>
       </c>
       <c r="C240" s="6">
-        <v>1.5959729952058599</v>
+        <v>1.6894140497169501</v>
       </c>
       <c r="D240" s="6">
         <v>1.80047230250753</v>
@@ -15353,16 +15353,16 @@
         <v>2.0242649011096598</v>
       </c>
       <c r="F240" s="6">
-        <v>0.41687715026699801</v>
+        <v>-0.98372715102118502</v>
       </c>
       <c r="G240" s="6">
-        <v>-1.57953997331352E-2</v>
+        <v>-1.5397901664751201E-2</v>
       </c>
       <c r="H240" s="6">
         <v>3.80248151289687E-2</v>
       </c>
       <c r="I240" s="6">
-        <v>2.19573713926447</v>
+        <v>2.17425590107473</v>
       </c>
       <c r="J240" s="6">
         <v>0.77257194299320098</v>
@@ -15403,10 +15403,10 @@
         <v>44105</v>
       </c>
       <c r="B241" s="6">
-        <v>1.27203203265486</v>
+        <v>1.4641027558970301</v>
       </c>
       <c r="C241" s="6">
-        <v>1.6142535928991899</v>
+        <v>1.69660725531029</v>
       </c>
       <c r="D241" s="6">
         <v>1.80561264692558</v>
@@ -15415,16 +15415,16 @@
         <v>2.0170472335578959</v>
       </c>
       <c r="F241" s="6">
-        <v>1.02975112118656</v>
+        <v>-0.30979828557997302</v>
       </c>
       <c r="G241" s="6">
-        <v>-1.57132737915162E-2</v>
+        <v>-1.5257134473682901E-2</v>
       </c>
       <c r="H241" s="6">
         <v>3.8045576314815102E-2</v>
       </c>
       <c r="I241" s="6">
-        <v>1.82329603191477</v>
+        <v>1.8160741646499401</v>
       </c>
       <c r="J241" s="6">
         <v>0.96187455169548997</v>
@@ -15465,10 +15465,10 @@
         <v>44197</v>
       </c>
       <c r="B242" s="6">
-        <v>1.27863844026552</v>
+        <v>1.47081128770039</v>
       </c>
       <c r="C242" s="6">
-        <v>1.6316973167372599</v>
+        <v>1.70384779656727</v>
       </c>
       <c r="D242" s="6">
         <v>1.8104294359608399</v>
@@ -15477,16 +15477,16 @@
         <v>2.0281609685122439</v>
       </c>
       <c r="F242" s="6">
-        <v>2.05363739060817</v>
+        <v>0.59612773574679101</v>
       </c>
       <c r="G242" s="6">
-        <v>-1.5860671258637798E-2</v>
+        <v>-1.5400334675069899E-2</v>
       </c>
       <c r="H242" s="6">
         <v>3.8036969356628897E-2</v>
       </c>
       <c r="I242" s="6">
-        <v>1.63474563197802</v>
+        <v>1.6533510349087199</v>
       </c>
       <c r="J242" s="6">
         <v>1.9644170066062301</v>
@@ -15527,10 +15527,10 @@
         <v>44287</v>
       </c>
       <c r="B243" s="6">
-        <v>1.30672831181459</v>
+        <v>1.5097745626365</v>
       </c>
       <c r="C243" s="6">
-        <v>1.6465505399741001</v>
+        <v>1.7087967256489101</v>
       </c>
       <c r="D243" s="6">
         <v>1.81325797315422</v>
@@ -15539,16 +15539,16 @@
         <v>2.0655682156523678</v>
       </c>
       <c r="F243" s="6">
-        <v>3.6335763029144901</v>
+        <v>1.6134416365461</v>
       </c>
       <c r="G243" s="6">
-        <v>-1.6229656646526699E-2</v>
+        <v>-1.6178849130688799E-2</v>
       </c>
       <c r="H243" s="6">
         <v>3.80365209615404E-2</v>
       </c>
       <c r="I243" s="6">
-        <v>1.7473727966700801</v>
+        <v>1.78980166707485</v>
       </c>
       <c r="J243" s="6">
         <v>2.93975572738875</v>
@@ -15589,10 +15589,10 @@
         <v>44378</v>
       </c>
       <c r="B244" s="6">
-        <v>1.3079524684927699</v>
+        <v>1.4892649746681801</v>
       </c>
       <c r="C244" s="6">
-        <v>1.6616677415397301</v>
+        <v>1.7150915400916</v>
       </c>
       <c r="D244" s="6">
         <v>1.8170187314833499</v>
@@ -15601,16 +15601,16 @@
         <v>2.0531238817681201</v>
       </c>
       <c r="F244" s="6">
-        <v>4.0416343020697196</v>
+        <v>2.0865075829248099</v>
       </c>
       <c r="G244" s="6">
-        <v>-1.63196988360968E-2</v>
+        <v>-1.5760338037359E-2</v>
       </c>
       <c r="H244" s="6">
         <v>3.8055607110235597E-2</v>
       </c>
       <c r="I244" s="6">
-        <v>1.4845604455374699</v>
+        <v>1.5249475452368799</v>
       </c>
       <c r="J244" s="6">
         <v>3.5548727232597601</v>
@@ -15651,10 +15651,10 @@
         <v>44470</v>
       </c>
       <c r="B245" s="6">
-        <v>1.4099932156894099</v>
+        <v>1.6026032484681001</v>
       </c>
       <c r="C245" s="6">
-        <v>1.66946419612453</v>
+        <v>1.7162336945552701</v>
       </c>
       <c r="D245" s="6">
         <v>1.81622192097601</v>
@@ -15663,16 +15663,16 @@
         <v>2.1727382074428481</v>
       </c>
       <c r="F245" s="6">
-        <v>4.6536767236741499</v>
+        <v>2.5684931775987301</v>
       </c>
       <c r="G245" s="6">
-        <v>-1.8007903609450399E-2</v>
+        <v>-1.8678914959610798E-2</v>
       </c>
       <c r="H245" s="6">
         <v>3.81000467017042E-2</v>
       </c>
       <c r="I245" s="6">
-        <v>1.30347564068346</v>
+        <v>1.34768802954058</v>
       </c>
       <c r="J245" s="6">
         <v>4.0016421419763599</v>
@@ -15713,10 +15713,10 @@
         <v>44562</v>
       </c>
       <c r="B246" s="6">
-        <v>1.3042613510687899</v>
+        <v>1.4678011306264001</v>
       </c>
       <c r="C246" s="6">
-        <v>1.6823233947989999</v>
+        <v>1.7214817380288501</v>
       </c>
       <c r="D246" s="6">
         <v>1.8185025520871501</v>
@@ -15725,16 +15725,16 @@
         <v>2.0574934874734438</v>
       </c>
       <c r="F246" s="6">
-        <v>5.2465483029313296</v>
+        <v>2.8567560928140701</v>
       </c>
       <c r="G246" s="6">
-        <v>-1.5924989734464299E-2</v>
+        <v>-1.46681296976165E-2</v>
       </c>
       <c r="H246" s="6">
         <v>3.8197592262906803E-2</v>
       </c>
       <c r="I246" s="6">
-        <v>1.16743882909438</v>
+        <v>1.21720317031377</v>
       </c>
       <c r="J246" s="6">
         <v>4.4553202808012697</v>
@@ -15775,10 +15775,10 @@
         <v>44652</v>
       </c>
       <c r="B247" s="6">
-        <v>1.2994251682986599</v>
+        <v>1.4528034342424001</v>
       </c>
       <c r="C247" s="6">
-        <v>1.6962800384205801</v>
+        <v>1.7275207631329199</v>
       </c>
       <c r="D247" s="6">
         <v>1.82153771914158</v>
@@ -15787,16 +15787,16 @@
         <v>2.043985008530572</v>
       </c>
       <c r="F247" s="6">
-        <v>4.6105222759630902</v>
+        <v>2.5869351686267201</v>
       </c>
       <c r="G247" s="6">
-        <v>-1.5780702453023598E-2</v>
+        <v>-1.4267238940572601E-2</v>
       </c>
       <c r="H247" s="6">
         <v>3.8064062853987397E-2</v>
       </c>
       <c r="I247" s="6">
-        <v>1.1045666264957601</v>
+        <v>1.1331669594876199</v>
       </c>
       <c r="J247" s="6">
         <v>3.0601189783148901</v>
@@ -15837,10 +15837,10 @@
         <v>44743</v>
       </c>
       <c r="B248" s="6">
-        <v>1.36088678684534</v>
+        <v>1.48992503116449</v>
       </c>
       <c r="C248" s="6">
-        <v>1.7077096544030901</v>
+        <v>1.73245313330321</v>
       </c>
       <c r="D248" s="6">
         <v>1.8238613434548101</v>
@@ -15849,16 +15849,16 @@
         <v>2.0690366325810521</v>
       </c>
       <c r="F248" s="6">
-        <v>4.2896341774069198</v>
+        <v>2.5284421212501198</v>
       </c>
       <c r="G248" s="6">
-        <v>-1.6893149363503099E-2</v>
+        <v>-1.5045421170425399E-2</v>
       </c>
       <c r="H248" s="6">
         <v>3.8076485290018398E-2</v>
       </c>
       <c r="I248" s="6">
-        <v>0.98729245292733603</v>
+        <v>1.01264465252022</v>
       </c>
       <c r="J248" s="6">
         <v>3.6911739418420302</v>
@@ -15899,10 +15899,10 @@
         <v>44835</v>
       </c>
       <c r="B249" s="6">
-        <v>1.40711762922925</v>
+        <v>1.5158841067365401</v>
       </c>
       <c r="C249" s="6">
-        <v>1.71808424355764</v>
+        <v>1.7369276561398399</v>
       </c>
       <c r="D249" s="6">
         <v>1.8252996504937899</v>
@@ -15911,16 +15911,16 @@
         <v>2.109067381749564</v>
       </c>
       <c r="F249" s="6">
-        <v>3.8708758343359499</v>
+        <v>2.46385642758537</v>
       </c>
       <c r="G249" s="6">
-        <v>-1.75982401458449E-2</v>
+        <v>-1.5463521369803199E-2</v>
       </c>
       <c r="H249" s="6">
         <v>3.79921982522003E-2</v>
       </c>
       <c r="I249" s="6">
-        <v>0.92316290727444705</v>
+        <v>0.93711546715322502</v>
       </c>
       <c r="J249" s="6">
         <v>3.3901181290375901</v>
@@ -15961,10 +15961,10 @@
         <v>44927</v>
       </c>
       <c r="B250" s="6">
-        <v>1.4629022174866499</v>
+        <v>1.54711469145693</v>
       </c>
       <c r="C250" s="6">
-        <v>1.72727415053551</v>
+        <v>1.7409098333598501</v>
       </c>
       <c r="D250" s="6">
         <v>1.82662665674691</v>
@@ -15973,16 +15973,16 @@
         <v>2.1232877944619561</v>
       </c>
       <c r="F250" s="6">
-        <v>3.5150301774824002</v>
+        <v>2.41794328747608</v>
       </c>
       <c r="G250" s="6">
-        <v>-1.8283167352769601E-2</v>
+        <v>-1.5859724927916999E-2</v>
       </c>
       <c r="H250" s="6">
         <v>3.79416335219648E-2</v>
       </c>
       <c r="I250" s="6">
-        <v>0.85426432674916297</v>
+        <v>0.86271437943612495</v>
       </c>
       <c r="J250" s="6">
         <v>3.3889185724509701</v>
@@ -16023,10 +16023,10 @@
         <v>45017</v>
       </c>
       <c r="B251" s="6">
-        <v>1.50297179211398</v>
+        <v>1.56952356652886</v>
       </c>
       <c r="C251" s="6">
-        <v>1.7380096318461</v>
+        <v>1.74543503936217</v>
       </c>
       <c r="D251" s="6">
         <v>1.82842128227597</v>
@@ -16035,16 +16035,16 @@
         <v>2.1443801236802602</v>
       </c>
       <c r="F251" s="6">
-        <v>2.8940583666087001</v>
+        <v>2.2297959401427101</v>
       </c>
       <c r="G251" s="6">
-        <v>-1.8569240893387198E-2</v>
+        <v>-1.5993732121894699E-2</v>
       </c>
       <c r="H251" s="6">
         <v>3.7740510054703101E-2</v>
       </c>
       <c r="I251" s="6">
-        <v>0.85476867911364995</v>
+        <v>0.85244142946675105</v>
       </c>
       <c r="J251" s="6">
         <v>2.61636145232761</v>
@@ -16085,10 +16085,10 @@
         <v>45108</v>
       </c>
       <c r="B252" s="6">
-        <v>1.7022552562892601</v>
+        <v>1.70228609274517</v>
       </c>
       <c r="C252" s="6">
-        <v>1.7396225746841401</v>
+        <v>1.74638115730932</v>
       </c>
       <c r="D252" s="6">
         <v>1.82797713327655</v>
@@ -16097,16 +16097,16 @@
         <v>2.2565085879441482</v>
       </c>
       <c r="F252" s="6">
-        <v>1.3693072394304999</v>
+        <v>1.64176560563783</v>
       </c>
       <c r="G252" s="6">
-        <v>-1.9571068048729202E-2</v>
+        <v>-1.6647277641905E-2</v>
       </c>
       <c r="H252" s="6">
         <v>3.7451684484177197E-2</v>
       </c>
       <c r="I252" s="6">
-        <v>1.15343078683553</v>
+        <v>1.1314094164716</v>
       </c>
       <c r="J252" s="6">
         <v>1.52214273055714</v>
@@ -16147,10 +16147,10 @@
         <v>45200</v>
       </c>
       <c r="B253" s="6">
-        <v>1.74233981560697</v>
+        <v>1.73371946175838</v>
       </c>
       <c r="C253" s="6">
-        <v>1.7381878743489301</v>
+        <v>1.7461382156619301</v>
       </c>
       <c r="D253" s="6">
         <v>1.8269449317037401</v>
@@ -16159,16 +16159,16 @@
         <v>2.2836765408837598</v>
       </c>
       <c r="F253" s="6">
-        <v>1.1831229657646001</v>
+        <v>1.59937616728632</v>
       </c>
       <c r="G253" s="6">
-        <v>-1.9678862568133199E-2</v>
+        <v>-1.67199850765202E-2</v>
       </c>
       <c r="H253" s="6">
         <v>3.7364680324472703E-2</v>
       </c>
       <c r="I253" s="6">
-        <v>1.0982194792611799</v>
+        <v>1.07572031809521</v>
       </c>
       <c r="J253" s="6">
         <v>1.1043265103429001</v>
@@ -16209,10 +16209,10 @@
         <v>45292</v>
       </c>
       <c r="B254" s="6">
-        <v>1.6286875999022401</v>
+        <v>1.65647627451234</v>
       </c>
       <c r="C254" s="6">
-        <v>1.7452404462925799</v>
+        <v>1.7491058688250101</v>
       </c>
       <c r="D254" s="6">
         <v>1.8271807792521499</v>
@@ -16221,16 +16221,16 @@
         <v>2.2424470967867318</v>
       </c>
       <c r="F254" s="6">
-        <v>1.6725169901000601</v>
+        <v>1.8716351487621501</v>
       </c>
       <c r="G254" s="6">
-        <v>-1.9792238162927401E-2</v>
+        <v>-1.6797294932378401E-2</v>
       </c>
       <c r="H254" s="6">
         <v>3.7460166900804101E-2</v>
       </c>
       <c r="I254" s="6">
-        <v>1.04182880286924</v>
+        <v>1.04281503085431</v>
       </c>
       <c r="J254" s="6">
         <v>2.0663855707458598</v>
@@ -16271,10 +16271,10 @@
         <v>45383</v>
       </c>
       <c r="B255" s="6">
-        <v>1.7727450098520201</v>
+        <v>1.7469025674671399</v>
       </c>
       <c r="C255" s="6">
-        <v>1.7450718012759201</v>
+        <v>1.74940273269409</v>
       </c>
       <c r="D255" s="6">
         <v>1.8262973314398601</v>
@@ -16283,16 +16283,16 @@
         <v>2.2912088287390522</v>
       </c>
       <c r="F255" s="6">
-        <v>1.0851130517587499</v>
+        <v>1.5297746746491601</v>
       </c>
       <c r="G255" s="6">
-        <v>-1.9209998752672E-2</v>
+        <v>-1.6463125012234701E-2</v>
       </c>
       <c r="H255" s="6">
         <v>3.7403774483407398E-2</v>
       </c>
       <c r="I255" s="6">
-        <v>0.96262146875610499</v>
+        <v>0.96940184370043303</v>
       </c>
       <c r="J255" s="6">
         <v>1.8143472332828201</v>
@@ -16333,10 +16333,10 @@
         <v>45474</v>
       </c>
       <c r="B256" s="6">
-        <v>1.84022600871804</v>
+        <v>1.79680743746862</v>
       </c>
       <c r="C256" s="6">
-        <v>1.7396198881429601</v>
+        <v>1.7476642486382099</v>
       </c>
       <c r="D256" s="6">
         <v>1.82409250439844</v>
@@ -16345,16 +16345,16 @@
         <v>2.3342297687644278</v>
       </c>
       <c r="F256" s="6">
-        <v>0.770112135297495</v>
+        <v>1.3696107096897101</v>
       </c>
       <c r="G256" s="6">
-        <v>-1.8905342249759899E-2</v>
+        <v>-1.6248172727821499E-2</v>
       </c>
       <c r="H256" s="6">
         <v>3.7347514567364702E-2</v>
       </c>
       <c r="I256" s="6">
-        <v>0.89201975889249696</v>
+        <v>0.90062375553811003</v>
       </c>
       <c r="J256" s="6">
         <v>1.2915457252012399</v>
@@ -16395,10 +16395,10 @@
         <v>45566</v>
       </c>
       <c r="B257" s="6">
-        <v>1.8002005198862301</v>
+        <v>1.7755378985044501</v>
       </c>
       <c r="C257" s="6">
-        <v>1.73387072739589</v>
+        <v>1.7459682427908301</v>
       </c>
       <c r="D257" s="6">
         <v>1.8209222791108099</v>
@@ -16407,16 +16407,16 @@
         <v>2.3395366435340761</v>
       </c>
       <c r="F257" s="6">
-        <v>0.83522685928340901</v>
+        <v>1.39363939088605</v>
       </c>
       <c r="G257" s="6">
-        <v>-1.9072321211680902E-2</v>
+        <v>-1.6342677422631301E-2</v>
       </c>
       <c r="H257" s="6">
         <v>3.7367070505527997E-2</v>
       </c>
       <c r="I257" s="6">
-        <v>0.81312618018643101</v>
+        <v>0.82454392958797396</v>
       </c>
       <c r="J257" s="6">
         <v>1.63501482612077</v>
@@ -16457,10 +16457,10 @@
         <v>45658</v>
       </c>
       <c r="B258" s="6">
-        <v>1.5894495758098</v>
+        <v>1.6497210749376301</v>
       </c>
       <c r="C258" s="6">
-        <v>1.7440082705145901</v>
+        <v>1.74982291266333</v>
       </c>
       <c r="D258" s="6">
         <v>1.8209222791108099</v>
@@ -16469,16 +16469,16 @@
         <v>2.2329285883727961</v>
       </c>
       <c r="F258" s="6">
-        <v>1.14319225896514</v>
+        <v>1.5016745029523699</v>
       </c>
       <c r="G258" s="6">
-        <v>-1.9664265819615102E-2</v>
+        <v>-1.6696767059742799E-2</v>
       </c>
       <c r="H258" s="6">
         <v>3.7474644118299899E-2</v>
       </c>
       <c r="I258" s="6">
-        <v>0.75373131063289101</v>
+        <v>0.76890416258792005</v>
       </c>
       <c r="J258" s="6">
         <v>2.0418983769034398</v>
@@ -16519,19 +16519,19 @@
         <v>45748</v>
       </c>
       <c r="B259" s="6">
-        <v>1.7511179271824799</v>
+        <v>1.75813899161013</v>
       </c>
       <c r="C259" s="6">
-        <v>1.7450797146688299</v>
+        <v>1.7501615855644901</v>
       </c>
       <c r="F259" s="6">
-        <v>0.56106197000087799</v>
+        <v>1.0534119660683201</v>
       </c>
       <c r="G259" s="6">
-        <v>-1.9446536435232701E-2</v>
+        <v>-1.6600013206216999E-2</v>
       </c>
       <c r="I259" s="6">
-        <v>0.71584456544516994</v>
+        <v>0.731502035658948</v>
       </c>
       <c r="J259" s="6">
         <v>1.5614775592133501</v>
@@ -16572,19 +16572,19 @@
         <v>45839</v>
       </c>
       <c r="B260" s="6">
-        <v>1.8538428706840899</v>
+        <v>1.83376119940806</v>
       </c>
       <c r="C260" s="6">
-        <v>1.7382667760777399</v>
+        <v>1.74714864674189</v>
       </c>
       <c r="F260" s="6">
-        <v>0.64815362954811895</v>
+        <v>1.03540090386844</v>
       </c>
       <c r="G260" s="6">
-        <v>-1.94504227246073E-2</v>
+        <v>-1.6601791226406901E-2</v>
       </c>
       <c r="I260" s="6">
-        <v>0.66915309794814004</v>
+        <v>0.68625083609140902</v>
       </c>
       <c r="J260" s="6">
         <v>1.87887672754168</v>
@@ -16625,19 +16625,19 @@
         <v>45931</v>
       </c>
       <c r="B261" s="6">
-        <v>1.7382667760777399</v>
+        <v>1.7544711434259099</v>
       </c>
       <c r="C261" s="6">
-        <v>1.7382667760777399</v>
+        <v>1.74696385408128</v>
       </c>
       <c r="F261" s="6">
-        <v>0.643800701148734</v>
+        <v>1.05575262916955</v>
       </c>
       <c r="G261" s="6">
-        <v>-1.9357737682075798E-2</v>
+        <v>-1.6542016802316699E-2</v>
       </c>
       <c r="I261" s="6">
-        <v>0.63340011885403202</v>
+        <v>0.65197460606889701</v>
       </c>
       <c r="J261" s="6">
         <v>1.6856709795678799</v>
@@ -16671,6 +16671,26 @@
       </c>
       <c r="T261" s="6">
         <v>6.7345555746429102E-3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A262" s="2">
+        <v>46023</v>
+      </c>
+      <c r="B262" s="6">
+        <v>1.74696385408128</v>
+      </c>
+      <c r="C262" s="6">
+        <v>1.74696385408128</v>
+      </c>
+      <c r="F262" s="6">
+        <v>1.3589283811744499</v>
+      </c>
+      <c r="G262" s="6">
+        <v>-1.6532939746984301E-2</v>
+      </c>
+      <c r="I262" s="6">
+        <v>0.87525078456872196</v>
       </c>
     </row>
   </sheetData>

--- a/estimates_PS2025.xlsx
+++ b/estimates_PS2025.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\GitHub\tibor-pal.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F2597C-608C-4CED-8C74-F252BECE5AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A119400-E635-4BD9-B063-3F5F1AB07DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{898E4DB8-E74C-49BD-9493-76D0D230C2FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
-    <sheet name="info_READ IT" sheetId="3" r:id="rId3"/>
+    <sheet name="info_READ IT" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -16699,3926 +16698,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06608B4E-EAA6-452E-B862-B69EDA33F1C2}">
-  <dimension ref="A1:IZ5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:260" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>9.0445374117341104E-2</v>
-      </c>
-      <c r="B1">
-        <v>6.8774425146596693E-2</v>
-      </c>
-      <c r="C1">
-        <v>7.1188816541932695E-2</v>
-      </c>
-      <c r="D1">
-        <v>7.3202624204753403E-2</v>
-      </c>
-      <c r="E1">
-        <v>7.4697687840799901E-2</v>
-      </c>
-      <c r="F1">
-        <v>7.5856271099876693E-2</v>
-      </c>
-      <c r="G1">
-        <v>7.6976002482605804E-2</v>
-      </c>
-      <c r="H1">
-        <v>7.7942761067055596E-2</v>
-      </c>
-      <c r="I1">
-        <v>7.9150876900161204E-2</v>
-      </c>
-      <c r="J1">
-        <v>8.0274953069030902E-2</v>
-      </c>
-      <c r="K1">
-        <v>8.1309791980819196E-2</v>
-      </c>
-      <c r="L1">
-        <v>8.1767797152881697E-2</v>
-      </c>
-      <c r="M1">
-        <v>8.2391330826118103E-2</v>
-      </c>
-      <c r="N1">
-        <v>8.2481870045831199E-2</v>
-      </c>
-      <c r="O1">
-        <v>8.2565236916010407E-2</v>
-      </c>
-      <c r="P1">
-        <v>8.2412498494380398E-2</v>
-      </c>
-      <c r="Q1">
-        <v>8.2643071224551695E-2</v>
-      </c>
-      <c r="R1">
-        <v>8.2232564830626007E-2</v>
-      </c>
-      <c r="S1">
-        <v>8.1770354900772099E-2</v>
-      </c>
-      <c r="T1">
-        <v>8.0835816163277299E-2</v>
-      </c>
-      <c r="U1">
-        <v>7.94747953087383E-2</v>
-      </c>
-      <c r="V1">
-        <v>7.7730253753580003E-2</v>
-      </c>
-      <c r="W1">
-        <v>7.6536104294358406E-2</v>
-      </c>
-      <c r="X1">
-        <v>7.5594104239680507E-2</v>
-      </c>
-      <c r="Y1">
-        <v>7.4878785298722605E-2</v>
-      </c>
-      <c r="Z1">
-        <v>0.114161695341829</v>
-      </c>
-      <c r="AA1">
-        <v>0.109166339459949</v>
-      </c>
-      <c r="AB1">
-        <v>0.10501778554728899</v>
-      </c>
-      <c r="AC1">
-        <v>0.101702981983993</v>
-      </c>
-      <c r="AD1">
-        <v>9.8179203290138198E-2</v>
-      </c>
-      <c r="AE1">
-        <v>9.4772318354776494E-2</v>
-      </c>
-      <c r="AF1">
-        <v>9.2045046750306905E-2</v>
-      </c>
-      <c r="AG1">
-        <v>9.0080034176316201E-2</v>
-      </c>
-      <c r="AH1">
-        <v>8.8082994138567502E-2</v>
-      </c>
-      <c r="AI1">
-        <v>8.6710039640746195E-2</v>
-      </c>
-      <c r="AJ1">
-        <v>8.5645034509310894E-2</v>
-      </c>
-      <c r="AK1">
-        <v>8.5387876190850698E-2</v>
-      </c>
-      <c r="AL1">
-        <v>8.5660187613700103E-2</v>
-      </c>
-      <c r="AM1">
-        <v>8.6264715096007499E-2</v>
-      </c>
-      <c r="AN1">
-        <v>8.6791072738770597E-2</v>
-      </c>
-      <c r="AO1">
-        <v>8.8226561115741897E-2</v>
-      </c>
-      <c r="AP1">
-        <v>8.8620065311926705E-2</v>
-      </c>
-      <c r="AQ1">
-        <v>8.9124662198983198E-2</v>
-      </c>
-      <c r="AR1">
-        <v>8.9563787838392805E-2</v>
-      </c>
-      <c r="AS1">
-        <v>7.8550437846002796E-2</v>
-      </c>
-      <c r="AT1">
-        <v>7.9501483508608195E-2</v>
-      </c>
-      <c r="AU1">
-        <v>8.3594668860570501E-2</v>
-      </c>
-      <c r="AV1">
-        <v>8.3434010513750503E-2</v>
-      </c>
-      <c r="AW1">
-        <v>8.2823232113683795E-2</v>
-      </c>
-      <c r="AX1">
-        <v>8.1532970974785998E-2</v>
-      </c>
-      <c r="AY1">
-        <v>8.0303469262417798E-2</v>
-      </c>
-      <c r="AZ1">
-        <v>7.9856034696382597E-2</v>
-      </c>
-      <c r="BA1">
-        <v>7.9424631725675404E-2</v>
-      </c>
-      <c r="BB1">
-        <v>7.9801860578208594E-2</v>
-      </c>
-      <c r="BC1">
-        <v>8.0432796174060295E-2</v>
-      </c>
-      <c r="BD1">
-        <v>8.1826004003687794E-2</v>
-      </c>
-      <c r="BE1">
-        <v>8.37166915321709E-2</v>
-      </c>
-      <c r="BF1">
-        <v>8.6701138175599296E-2</v>
-      </c>
-      <c r="BG1">
-        <v>9.0052517747227501E-2</v>
-      </c>
-      <c r="BH1">
-        <v>9.2298706771706596E-2</v>
-      </c>
-      <c r="BI1">
-        <v>9.4173440835661995E-2</v>
-      </c>
-      <c r="BJ1">
-        <v>9.5084222381932204E-2</v>
-      </c>
-      <c r="BK1">
-        <v>7.9662667677503907E-2</v>
-      </c>
-      <c r="BL1">
-        <v>8.1581380891965399E-2</v>
-      </c>
-      <c r="BM1">
-        <v>8.3453073471340802E-2</v>
-      </c>
-      <c r="BN1">
-        <v>8.4756058471633006E-2</v>
-      </c>
-      <c r="BO1">
-        <v>8.5579495096101396E-2</v>
-      </c>
-      <c r="BP1">
-        <v>8.5837489114667098E-2</v>
-      </c>
-      <c r="BQ1">
-        <v>8.6441780559886397E-2</v>
-      </c>
-      <c r="BR1">
-        <v>8.7448172085484194E-2</v>
-      </c>
-      <c r="BS1">
-        <v>8.6859851733783897E-2</v>
-      </c>
-      <c r="BT1">
-        <v>8.5973436367112702E-2</v>
-      </c>
-      <c r="BU1">
-        <v>8.5090438852318803E-2</v>
-      </c>
-      <c r="BV1">
-        <v>0.101629950160303</v>
-      </c>
-      <c r="BW1">
-        <v>0.100084199398926</v>
-      </c>
-      <c r="BX1">
-        <v>9.8741952284549794E-2</v>
-      </c>
-      <c r="BY1">
-        <v>9.7871329358345097E-2</v>
-      </c>
-      <c r="BZ1">
-        <v>9.7315197170671594E-2</v>
-      </c>
-      <c r="CA1">
-        <v>9.8579500806110304E-2</v>
-      </c>
-      <c r="CB1">
-        <v>0.100556698352583</v>
-      </c>
-      <c r="CC1">
-        <v>0.100949140916579</v>
-      </c>
-      <c r="CD1">
-        <v>0.10056679505701301</v>
-      </c>
-      <c r="CE1">
-        <v>8.4074955557960296E-2</v>
-      </c>
-      <c r="CF1">
-        <v>8.5284890603212399E-2</v>
-      </c>
-      <c r="CG1">
-        <v>8.7413610746257503E-2</v>
-      </c>
-      <c r="CH1">
-        <v>6.1834588953356501E-2</v>
-      </c>
-      <c r="CI1">
-        <v>6.5129320560502801E-2</v>
-      </c>
-      <c r="CJ1">
-        <v>6.8736619513303093E-2</v>
-      </c>
-      <c r="CK1">
-        <v>7.2598379812860506E-2</v>
-      </c>
-      <c r="CL1">
-        <v>7.6316873101567803E-2</v>
-      </c>
-      <c r="CM1">
-        <v>3.3108696364596998E-2</v>
-      </c>
-      <c r="CN1">
-        <v>3.6075219039786902E-2</v>
-      </c>
-      <c r="CO1">
-        <v>3.1407604382902701E-2</v>
-      </c>
-      <c r="CP1">
-        <v>3.41884767176759E-2</v>
-      </c>
-      <c r="CQ1">
-        <v>3.6906344148138003E-2</v>
-      </c>
-      <c r="CR1">
-        <v>3.9350097035376903E-2</v>
-      </c>
-      <c r="CS1">
-        <v>4.1638461227038501E-2</v>
-      </c>
-      <c r="CT1">
-        <v>4.4307484548915699E-2</v>
-      </c>
-      <c r="CU1">
-        <v>4.6860108507967201E-2</v>
-      </c>
-      <c r="CV1">
-        <v>4.9317455834730302E-2</v>
-      </c>
-      <c r="CW1">
-        <v>5.1545972803514202E-2</v>
-      </c>
-      <c r="CX1">
-        <v>5.3861000343945302E-2</v>
-      </c>
-      <c r="CY1">
-        <v>5.5485257289964798E-2</v>
-      </c>
-      <c r="CZ1">
-        <v>5.7706586820647998E-2</v>
-      </c>
-      <c r="DA1">
-        <v>5.9905497074500901E-2</v>
-      </c>
-      <c r="DB1">
-        <v>6.2018805097086897E-2</v>
-      </c>
-      <c r="DC1">
-        <v>6.3979056704491194E-2</v>
-      </c>
-      <c r="DD1">
-        <v>6.5821352577582606E-2</v>
-      </c>
-      <c r="DE1">
-        <v>6.7283266412504497E-2</v>
-      </c>
-      <c r="DF1">
-        <v>6.8733916051999397E-2</v>
-      </c>
-      <c r="DG1">
-        <v>6.9909547997095298E-2</v>
-      </c>
-      <c r="DH1">
-        <v>7.1059413535492402E-2</v>
-      </c>
-      <c r="DI1">
-        <v>7.1919302102888494E-2</v>
-      </c>
-      <c r="DJ1">
-        <v>7.2612406459455894E-2</v>
-      </c>
-      <c r="DK1">
-        <v>7.3473365331299903E-2</v>
-      </c>
-      <c r="DL1">
-        <v>7.4090894965952406E-2</v>
-      </c>
-      <c r="DM1">
-        <v>7.47103157051862E-2</v>
-      </c>
-      <c r="DN1">
-        <v>7.5102829509343799E-2</v>
-      </c>
-      <c r="DO1">
-        <v>7.5676346812484793E-2</v>
-      </c>
-      <c r="DP1">
-        <v>7.6454163481553095E-2</v>
-      </c>
-      <c r="DQ1">
-        <v>7.7823496838163406E-2</v>
-      </c>
-      <c r="DR1">
-        <v>7.9592399429392405E-2</v>
-      </c>
-      <c r="DS1">
-        <v>8.1223444458114802E-2</v>
-      </c>
-      <c r="DT1">
-        <v>8.2965909940325697E-2</v>
-      </c>
-      <c r="DU1">
-        <v>8.4464662225018902E-2</v>
-      </c>
-      <c r="DV1">
-        <v>8.5661134772891001E-2</v>
-      </c>
-      <c r="DW1">
-        <v>8.6721360168553696E-2</v>
-      </c>
-      <c r="DX1">
-        <v>8.7545068791967703E-2</v>
-      </c>
-      <c r="DY1">
-        <v>8.8050735826225093E-2</v>
-      </c>
-      <c r="DZ1">
-        <v>8.8765630486024497E-2</v>
-      </c>
-      <c r="EA1">
-        <v>8.9608946993323502E-2</v>
-      </c>
-      <c r="EB1">
-        <v>8.9998155171779504E-2</v>
-      </c>
-      <c r="EC1">
-        <v>9.0571165682299698E-2</v>
-      </c>
-      <c r="ED1">
-        <v>9.1004924981950702E-2</v>
-      </c>
-      <c r="EE1">
-        <v>9.0897640486387404E-2</v>
-      </c>
-      <c r="EF1">
-        <v>9.0898558495376203E-2</v>
-      </c>
-      <c r="EG1">
-        <v>9.0601631362193902E-2</v>
-      </c>
-      <c r="EH1">
-        <v>9.0582185899649406E-2</v>
-      </c>
-      <c r="EI1">
-        <v>9.0851578659721197E-2</v>
-      </c>
-      <c r="EJ1">
-        <v>9.1104540548787402E-2</v>
-      </c>
-      <c r="EK1">
-        <v>9.1301763670682101E-2</v>
-      </c>
-      <c r="EL1">
-        <v>9.1583763200018001E-2</v>
-      </c>
-      <c r="EM1">
-        <v>9.1162108693509006E-2</v>
-      </c>
-      <c r="EN1">
-        <v>9.0730043507647296E-2</v>
-      </c>
-      <c r="EO1">
-        <v>9.0301355810577993E-2</v>
-      </c>
-      <c r="EP1">
-        <v>9.0560237342266106E-2</v>
-      </c>
-      <c r="EQ1">
-        <v>8.9795110053120006E-2</v>
-      </c>
-      <c r="ER1">
-        <v>0.10133108859859</v>
-      </c>
-      <c r="ES1">
-        <v>9.9383955911313507E-2</v>
-      </c>
-      <c r="ET1">
-        <v>9.7781701753864803E-2</v>
-      </c>
-      <c r="EU1">
-        <v>9.6426704980631897E-2</v>
-      </c>
-      <c r="EV1">
-        <v>9.5070858949086595E-2</v>
-      </c>
-      <c r="EW1">
-        <v>9.3495224235628296E-2</v>
-      </c>
-      <c r="EX1">
-        <v>9.2186469461295703E-2</v>
-      </c>
-      <c r="EY1">
-        <v>9.1149227192112006E-2</v>
-      </c>
-      <c r="EZ1">
-        <v>9.0065690444412302E-2</v>
-      </c>
-      <c r="FA1">
-        <v>8.8778332323100201E-2</v>
-      </c>
-      <c r="FB1">
-        <v>8.80067074896526E-2</v>
-      </c>
-      <c r="FC1">
-        <v>8.7337858798344201E-2</v>
-      </c>
-      <c r="FD1">
-        <v>8.6732203900841104E-2</v>
-      </c>
-      <c r="FE1">
-        <v>8.6360184738031698E-2</v>
-      </c>
-      <c r="FF1">
-        <v>8.6650886859119897E-2</v>
-      </c>
-      <c r="FG1">
-        <v>8.6282504583214598E-2</v>
-      </c>
-      <c r="FH1">
-        <v>8.7256078116678196E-2</v>
-      </c>
-      <c r="FI1">
-        <v>8.8414335470980696E-2</v>
-      </c>
-      <c r="FJ1">
-        <v>8.9393113022620596E-2</v>
-      </c>
-      <c r="FK1">
-        <v>9.0334816463102E-2</v>
-      </c>
-      <c r="FL1">
-        <v>9.1332447787331905E-2</v>
-      </c>
-      <c r="FM1">
-        <v>9.2192243284134806E-2</v>
-      </c>
-      <c r="FN1">
-        <v>9.3369827595381497E-2</v>
-      </c>
-      <c r="FO1">
-        <v>9.4325612679757101E-2</v>
-      </c>
-      <c r="FP1">
-        <v>9.4576363206739705E-2</v>
-      </c>
-      <c r="FQ1">
-        <v>9.4466664041967296E-2</v>
-      </c>
-      <c r="FR1">
-        <v>9.4399978020285505E-2</v>
-      </c>
-      <c r="FS1">
-        <v>9.4248890882717096E-2</v>
-      </c>
-      <c r="FT1">
-        <v>9.4026171490874999E-2</v>
-      </c>
-      <c r="FU1">
-        <v>9.3486948547244805E-2</v>
-      </c>
-      <c r="FV1">
-        <v>9.2707224517624198E-2</v>
-      </c>
-      <c r="FW1">
-        <v>9.4564590649703503E-2</v>
-      </c>
-      <c r="FX1">
-        <v>9.3306371512319894E-2</v>
-      </c>
-      <c r="FY1">
-        <v>9.2625272872836603E-2</v>
-      </c>
-      <c r="FZ1">
-        <v>9.12800825271919E-2</v>
-      </c>
-      <c r="GA1">
-        <v>9.0443303293523597E-2</v>
-      </c>
-      <c r="GB1">
-        <v>9.3789630574326502E-2</v>
-      </c>
-      <c r="GC1">
-        <v>9.2179946063148499E-2</v>
-      </c>
-      <c r="GD1">
-        <v>9.13982144853724E-2</v>
-      </c>
-      <c r="GE1">
-        <v>9.26024636143047E-2</v>
-      </c>
-      <c r="GF1">
-        <v>9.1662355529595396E-2</v>
-      </c>
-      <c r="GG1">
-        <v>9.0743937496232205E-2</v>
-      </c>
-      <c r="GH1">
-        <v>9.0537243643496801E-2</v>
-      </c>
-      <c r="GI1">
-        <v>9.0214608338500604E-2</v>
-      </c>
-      <c r="GJ1">
-        <v>9.0497025916028803E-2</v>
-      </c>
-      <c r="GK1">
-        <v>5.0334008386115299E-2</v>
-      </c>
-      <c r="GL1">
-        <v>5.3123136271060897E-2</v>
-      </c>
-      <c r="GM1">
-        <v>5.6371871721573902E-2</v>
-      </c>
-      <c r="GN1">
-        <v>5.9756526253782902E-2</v>
-      </c>
-      <c r="GO1">
-        <v>6.2773816279892106E-2</v>
-      </c>
-      <c r="GP1">
-        <v>6.4357130949793798E-2</v>
-      </c>
-      <c r="GQ1">
-        <v>6.7083588086327098E-2</v>
-      </c>
-      <c r="GR1">
-        <v>6.9450717097172598E-2</v>
-      </c>
-      <c r="GS1">
-        <v>7.1853545360918203E-2</v>
-      </c>
-      <c r="GT1">
-        <v>7.4402601535044105E-2</v>
-      </c>
-      <c r="GU1">
-        <v>7.6781115981318204E-2</v>
-      </c>
-      <c r="GV1">
-        <v>7.9033660838019507E-2</v>
-      </c>
-      <c r="GW1">
-        <v>8.1141176825042502E-2</v>
-      </c>
-      <c r="GX1">
-        <v>8.2980459385771102E-2</v>
-      </c>
-      <c r="GY1">
-        <v>8.4522393121375897E-2</v>
-      </c>
-      <c r="GZ1">
-        <v>8.6517938817153001E-2</v>
-      </c>
-      <c r="HA1">
-        <v>8.8424686341394901E-2</v>
-      </c>
-      <c r="HB1">
-        <v>8.9988758534976301E-2</v>
-      </c>
-      <c r="HC1">
-        <v>9.2473867250927197E-2</v>
-      </c>
-      <c r="HD1">
-        <v>9.3926238913541599E-2</v>
-      </c>
-      <c r="HE1">
-        <v>9.5014334757685198E-2</v>
-      </c>
-      <c r="HF1">
-        <v>9.74309717206749E-2</v>
-      </c>
-      <c r="HG1">
-        <v>9.8343823789619006E-2</v>
-      </c>
-      <c r="HH1">
-        <v>9.8728189641100597E-2</v>
-      </c>
-      <c r="HI1">
-        <v>9.9353920633906995E-2</v>
-      </c>
-      <c r="HJ1">
-        <v>9.9421650965629396E-2</v>
-      </c>
-      <c r="HK1">
-        <v>9.9221488468815996E-2</v>
-      </c>
-      <c r="HL1">
-        <v>9.9277536867103403E-2</v>
-      </c>
-      <c r="HM1">
-        <v>9.9508638469980606E-2</v>
-      </c>
-      <c r="HN1">
-        <v>9.9600567724879505E-2</v>
-      </c>
-      <c r="HO1">
-        <v>9.9837210481090094E-2</v>
-      </c>
-      <c r="HP1">
-        <v>0.10018094816878501</v>
-      </c>
-      <c r="HQ1">
-        <v>0.100311287938882</v>
-      </c>
-      <c r="HR1">
-        <v>0.100301600043721</v>
-      </c>
-      <c r="HS1">
-        <v>0.100568370239373</v>
-      </c>
-      <c r="HT1">
-        <v>0.10025716771026399</v>
-      </c>
-      <c r="HU1">
-        <v>9.9452004487817505E-2</v>
-      </c>
-      <c r="HV1">
-        <v>9.8469554975313803E-2</v>
-      </c>
-      <c r="HW1">
-        <v>9.7479375722934095E-2</v>
-      </c>
-      <c r="HX1">
-        <v>9.7912776473394594E-2</v>
-      </c>
-      <c r="HY1">
-        <v>9.7265236686170403E-2</v>
-      </c>
-      <c r="HZ1">
-        <v>9.6583744675247205E-2</v>
-      </c>
-      <c r="IA1">
-        <v>9.5747170680535496E-2</v>
-      </c>
-      <c r="IB1">
-        <v>9.4469307133330294E-2</v>
-      </c>
-      <c r="IC1">
-        <v>9.3348413968896607E-2</v>
-      </c>
-      <c r="ID1">
-        <v>9.3462202517938395E-2</v>
-      </c>
-      <c r="IE1">
-        <v>1.7092691606898101E-2</v>
-      </c>
-      <c r="IF1">
-        <v>1.93357889476206E-2</v>
-      </c>
-      <c r="IG1">
-        <v>2.1698790942874299E-2</v>
-      </c>
-      <c r="IH1">
-        <v>2.4148633245539501E-2</v>
-      </c>
-      <c r="II1">
-        <v>2.6640916929269998E-2</v>
-      </c>
-      <c r="IJ1">
-        <v>2.9174696935404299E-2</v>
-      </c>
-      <c r="IK1">
-        <v>3.1673716246914903E-2</v>
-      </c>
-      <c r="IL1">
-        <v>3.4227650344732803E-2</v>
-      </c>
-      <c r="IM1">
-        <v>3.6843992394557802E-2</v>
-      </c>
-      <c r="IN1">
-        <v>3.93912778693771E-2</v>
-      </c>
-      <c r="IO1">
-        <v>4.1893914677098798E-2</v>
-      </c>
-      <c r="IP1">
-        <v>4.4336008301389701E-2</v>
-      </c>
-      <c r="IQ1">
-        <v>4.6680302051140002E-2</v>
-      </c>
-      <c r="IR1">
-        <v>5.1819545409306299E-2</v>
-      </c>
-      <c r="IS1">
-        <v>5.3749117018008899E-2</v>
-      </c>
-      <c r="IT1">
-        <v>5.5738161497399401E-2</v>
-      </c>
-      <c r="IU1">
-        <v>5.7561510414593599E-2</v>
-      </c>
-      <c r="IV1">
-        <v>5.91186719210781E-2</v>
-      </c>
-      <c r="IW1">
-        <v>6.0780028909221899E-2</v>
-      </c>
-      <c r="IX1">
-        <v>6.2543124429238803E-2</v>
-      </c>
-      <c r="IY1">
-        <v>6.40023839309041E-2</v>
-      </c>
-      <c r="IZ1">
-        <v>6.5335014123811597E-2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:260" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>8.6315323395899105E-2</v>
-      </c>
-      <c r="B2">
-        <v>5.43578129298804E-2</v>
-      </c>
-      <c r="C2">
-        <v>5.9700287390098701E-2</v>
-      </c>
-      <c r="D2">
-        <v>6.4075652663236907E-2</v>
-      </c>
-      <c r="E2">
-        <v>6.3001388504335606E-2</v>
-      </c>
-      <c r="F2">
-        <v>6.4698617689827806E-2</v>
-      </c>
-      <c r="G2">
-        <v>6.6446970798135496E-2</v>
-      </c>
-      <c r="H2">
-        <v>6.7778950474035995E-2</v>
-      </c>
-      <c r="I2">
-        <v>6.8550956255012604E-2</v>
-      </c>
-      <c r="J2">
-        <v>7.0990271821141093E-2</v>
-      </c>
-      <c r="K2">
-        <v>7.3272820064957597E-2</v>
-      </c>
-      <c r="L2">
-        <v>7.3263090274785794E-2</v>
-      </c>
-      <c r="M2">
-        <v>7.4104070362088506E-2</v>
-      </c>
-      <c r="N2">
-        <v>7.2942848256478995E-2</v>
-      </c>
-      <c r="O2">
-        <v>7.5204824639873505E-2</v>
-      </c>
-      <c r="P2">
-        <v>7.2826836347208296E-2</v>
-      </c>
-      <c r="Q2">
-        <v>7.2336884838039101E-2</v>
-      </c>
-      <c r="R2">
-        <v>6.9236786045212606E-2</v>
-      </c>
-      <c r="S2">
-        <v>6.7791023124460906E-2</v>
-      </c>
-      <c r="T2">
-        <v>6.3225347659501899E-2</v>
-      </c>
-      <c r="U2">
-        <v>5.7760150607457997E-2</v>
-      </c>
-      <c r="V2">
-        <v>5.1780204243870101E-2</v>
-      </c>
-      <c r="W2">
-        <v>4.8476931989371697E-2</v>
-      </c>
-      <c r="X2">
-        <v>4.6223617525353401E-2</v>
-      </c>
-      <c r="Y2">
-        <v>4.4573188400741398E-2</v>
-      </c>
-      <c r="Z2">
-        <v>6.6183853296252801E-2</v>
-      </c>
-      <c r="AA2">
-        <v>6.17803480418498E-2</v>
-      </c>
-      <c r="AB2">
-        <v>5.858093984519E-2</v>
-      </c>
-      <c r="AC2">
-        <v>5.64976340733934E-2</v>
-      </c>
-      <c r="AD2">
-        <v>5.3663937756868098E-2</v>
-      </c>
-      <c r="AE2">
-        <v>5.07162164336128E-2</v>
-      </c>
-      <c r="AF2">
-        <v>4.8756042000870602E-2</v>
-      </c>
-      <c r="AG2">
-        <v>4.7829167106566997E-2</v>
-      </c>
-      <c r="AH2">
-        <v>4.6621532407026302E-2</v>
-      </c>
-      <c r="AI2">
-        <v>4.6226524317497401E-2</v>
-      </c>
-      <c r="AJ2">
-        <v>4.6168616740062299E-2</v>
-      </c>
-      <c r="AK2">
-        <v>4.7339020388491797E-2</v>
-      </c>
-      <c r="AL2">
-        <v>4.9377801864340098E-2</v>
-      </c>
-      <c r="AM2">
-        <v>5.2045968142750303E-2</v>
-      </c>
-      <c r="AN2">
-        <v>5.4579764082719397E-2</v>
-      </c>
-      <c r="AO2">
-        <v>5.9300949168192403E-2</v>
-      </c>
-      <c r="AP2">
-        <v>6.1639592491604403E-2</v>
-      </c>
-      <c r="AQ2">
-        <v>6.4148540209668994E-2</v>
-      </c>
-      <c r="AR2">
-        <v>6.4331704761572406E-2</v>
-      </c>
-      <c r="AS2">
-        <v>5.76104154281026E-2</v>
-      </c>
-      <c r="AT2">
-        <v>5.9692506748383403E-2</v>
-      </c>
-      <c r="AU2">
-        <v>7.0066283068105195E-2</v>
-      </c>
-      <c r="AV2">
-        <v>6.8720242794238606E-2</v>
-      </c>
-      <c r="AW2">
-        <v>7.3135503950345904E-2</v>
-      </c>
-      <c r="AX2">
-        <v>6.6775433023509606E-2</v>
-      </c>
-      <c r="AY2">
-        <v>6.1568192775934998E-2</v>
-      </c>
-      <c r="AZ2">
-        <v>5.9474404641438897E-2</v>
-      </c>
-      <c r="BA2">
-        <v>5.7632937890406702E-2</v>
-      </c>
-      <c r="BB2">
-        <v>5.8226614736304999E-2</v>
-      </c>
-      <c r="BC2">
-        <v>5.95880102141454E-2</v>
-      </c>
-      <c r="BD2">
-        <v>6.3310590145066903E-2</v>
-      </c>
-      <c r="BE2">
-        <v>6.8988456268097201E-2</v>
-      </c>
-      <c r="BF2">
-        <v>7.2771543393024496E-2</v>
-      </c>
-      <c r="BG2">
-        <v>6.6970042655543904E-2</v>
-      </c>
-      <c r="BH2">
-        <v>7.4946362861918095E-2</v>
-      </c>
-      <c r="BI2">
-        <v>8.27615676847233E-2</v>
-      </c>
-      <c r="BJ2">
-        <v>8.7649122728523196E-2</v>
-      </c>
-      <c r="BK2">
-        <v>7.4829136294151402E-2</v>
-      </c>
-      <c r="BL2">
-        <v>7.9343069984861694E-2</v>
-      </c>
-      <c r="BM2">
-        <v>8.4159510640129401E-2</v>
-      </c>
-      <c r="BN2">
-        <v>8.9571117497215302E-2</v>
-      </c>
-      <c r="BO2">
-        <v>9.1409040190799207E-2</v>
-      </c>
-      <c r="BP2">
-        <v>9.0374173539135794E-2</v>
-      </c>
-      <c r="BQ2">
-        <v>8.6117301737632101E-2</v>
-      </c>
-      <c r="BR2">
-        <v>8.8810621116152497E-2</v>
-      </c>
-      <c r="BS2">
-        <v>8.3295962340667801E-2</v>
-      </c>
-      <c r="BT2">
-        <v>7.9208294313581604E-2</v>
-      </c>
-      <c r="BU2">
-        <v>7.4492830343077396E-2</v>
-      </c>
-      <c r="BV2">
-        <v>9.04694539892692E-2</v>
-      </c>
-      <c r="BW2">
-        <v>8.7654341019750795E-2</v>
-      </c>
-      <c r="BX2">
-        <v>8.5391429857317097E-2</v>
-      </c>
-      <c r="BY2">
-        <v>8.4719997674556097E-2</v>
-      </c>
-      <c r="BZ2">
-        <v>8.5028642930265796E-2</v>
-      </c>
-      <c r="CA2">
-        <v>9.2645748129357705E-2</v>
-      </c>
-      <c r="CB2">
-        <v>0.10147467107812901</v>
-      </c>
-      <c r="CC2">
-        <v>0.10857978530047099</v>
-      </c>
-      <c r="CD2">
-        <v>0.108982786848349</v>
-      </c>
-      <c r="CE2">
-        <v>7.7430644450914896E-2</v>
-      </c>
-      <c r="CF2">
-        <v>8.1019499432693196E-2</v>
-      </c>
-      <c r="CG2">
-        <v>8.8038989126317302E-2</v>
-      </c>
-      <c r="CH2">
-        <v>3.8730956751346003E-2</v>
-      </c>
-      <c r="CI2">
-        <v>4.2001768642616302E-2</v>
-      </c>
-      <c r="CJ2">
-        <v>4.92245868298287E-2</v>
-      </c>
-      <c r="CK2">
-        <v>4.7004196791116101E-2</v>
-      </c>
-      <c r="CL2">
-        <v>5.5006003698797497E-2</v>
-      </c>
-      <c r="CM2">
-        <v>3.5889552675530498E-2</v>
-      </c>
-      <c r="CN2">
-        <v>4.0337291769883002E-2</v>
-      </c>
-      <c r="CO2">
-        <v>3.5954797912130798E-2</v>
-      </c>
-      <c r="CP2">
-        <v>3.8144198697635801E-2</v>
-      </c>
-      <c r="CQ2">
-        <v>4.1094730453337301E-2</v>
-      </c>
-      <c r="CR2">
-        <v>4.1585851922658998E-2</v>
-      </c>
-      <c r="CS2">
-        <v>4.1910513143627398E-2</v>
-      </c>
-      <c r="CT2">
-        <v>4.4751395128633097E-2</v>
-      </c>
-      <c r="CU2">
-        <v>4.5882622780727501E-2</v>
-      </c>
-      <c r="CV2">
-        <v>4.82485681607994E-2</v>
-      </c>
-      <c r="CW2">
-        <v>4.9795216941308403E-2</v>
-      </c>
-      <c r="CX2">
-        <v>5.2055882588634098E-2</v>
-      </c>
-      <c r="CY2">
-        <v>5.22143794047965E-2</v>
-      </c>
-      <c r="CZ2">
-        <v>5.4492048120569403E-2</v>
-      </c>
-      <c r="DA2">
-        <v>5.7163876166543497E-2</v>
-      </c>
-      <c r="DB2">
-        <v>5.7794023766536501E-2</v>
-      </c>
-      <c r="DC2">
-        <v>6.0133236795870397E-2</v>
-      </c>
-      <c r="DD2">
-        <v>6.2280536463687697E-2</v>
-      </c>
-      <c r="DE2">
-        <v>6.3011917032779405E-2</v>
-      </c>
-      <c r="DF2">
-        <v>6.4032609217466799E-2</v>
-      </c>
-      <c r="DG2">
-        <v>6.4140414210958202E-2</v>
-      </c>
-      <c r="DH2">
-        <v>6.4338495280504407E-2</v>
-      </c>
-      <c r="DI2">
-        <v>6.3391732543089094E-2</v>
-      </c>
-      <c r="DJ2">
-        <v>6.2559625240011602E-2</v>
-      </c>
-      <c r="DK2">
-        <v>7.0344326693030201E-2</v>
-      </c>
-      <c r="DL2">
-        <v>7.7210379406574603E-2</v>
-      </c>
-      <c r="DM2">
-        <v>7.5506396387771901E-2</v>
-      </c>
-      <c r="DN2">
-        <v>7.3343915488567807E-2</v>
-      </c>
-      <c r="DO2">
-        <v>7.1323298214378106E-2</v>
-      </c>
-      <c r="DP2">
-        <v>7.1541853485627499E-2</v>
-      </c>
-      <c r="DQ2">
-        <v>7.1070268823942795E-2</v>
-      </c>
-      <c r="DR2">
-        <v>7.59616670872474E-2</v>
-      </c>
-      <c r="DS2">
-        <v>7.9025170775369802E-2</v>
-      </c>
-      <c r="DT2">
-        <v>8.3497008795980293E-2</v>
-      </c>
-      <c r="DU2">
-        <v>8.8495454333670898E-2</v>
-      </c>
-      <c r="DV2">
-        <v>9.3985194819147397E-2</v>
-      </c>
-      <c r="DW2">
-        <v>9.6608466626067105E-2</v>
-      </c>
-      <c r="DX2">
-        <v>9.44086928971275E-2</v>
-      </c>
-      <c r="DY2">
-        <v>9.58297433120395E-2</v>
-      </c>
-      <c r="DZ2">
-        <v>9.9149509147190895E-2</v>
-      </c>
-      <c r="EA2">
-        <v>0.10240207183137801</v>
-      </c>
-      <c r="EB2">
-        <v>8.8080562394497894E-2</v>
-      </c>
-      <c r="EC2">
-        <v>8.9800112061868803E-2</v>
-      </c>
-      <c r="ED2">
-        <v>8.9940473978330701E-2</v>
-      </c>
-      <c r="EE2">
-        <v>8.9420671883272199E-2</v>
-      </c>
-      <c r="EF2">
-        <v>8.9101524442151095E-2</v>
-      </c>
-      <c r="EG2">
-        <v>8.7990059332400797E-2</v>
-      </c>
-      <c r="EH2">
-        <v>8.7830697673587393E-2</v>
-      </c>
-      <c r="EI2">
-        <v>8.8729150997564801E-2</v>
-      </c>
-      <c r="EJ2">
-        <v>8.7730087414363805E-2</v>
-      </c>
-      <c r="EK2">
-        <v>8.8546035104806298E-2</v>
-      </c>
-      <c r="EL2">
-        <v>8.7561532454690699E-2</v>
-      </c>
-      <c r="EM2">
-        <v>8.6309175292286197E-2</v>
-      </c>
-      <c r="EN2">
-        <v>8.5133811599823001E-2</v>
-      </c>
-      <c r="EO2">
-        <v>8.3401451454898606E-2</v>
-      </c>
-      <c r="EP2">
-        <v>8.7369547639582101E-2</v>
-      </c>
-      <c r="EQ2">
-        <v>8.4658460990283999E-2</v>
-      </c>
-      <c r="ER2">
-        <v>9.5252573809335397E-2</v>
-      </c>
-      <c r="ES2">
-        <v>9.0965374569034502E-2</v>
-      </c>
-      <c r="ET2">
-        <v>8.6903040782383006E-2</v>
-      </c>
-      <c r="EU2">
-        <v>8.3658842557811003E-2</v>
-      </c>
-      <c r="EV2">
-        <v>8.0381743492809798E-2</v>
-      </c>
-      <c r="EW2">
-        <v>7.6855164318460706E-2</v>
-      </c>
-      <c r="EX2">
-        <v>7.5886630406427694E-2</v>
-      </c>
-      <c r="EY2">
-        <v>7.3323233566680801E-2</v>
-      </c>
-      <c r="EZ2">
-        <v>7.03346895105222E-2</v>
-      </c>
-      <c r="FA2">
-        <v>6.7194099421957199E-2</v>
-      </c>
-      <c r="FB2">
-        <v>6.5142649042183601E-2</v>
-      </c>
-      <c r="FC2">
-        <v>7.6672836712344997E-2</v>
-      </c>
-      <c r="FD2">
-        <v>7.4242298470049303E-2</v>
-      </c>
-      <c r="FE2">
-        <v>7.2602394551530905E-2</v>
-      </c>
-      <c r="FF2">
-        <v>7.3506133729747195E-2</v>
-      </c>
-      <c r="FG2">
-        <v>7.3082956776979194E-2</v>
-      </c>
-      <c r="FH2">
-        <v>7.1261369906972696E-2</v>
-      </c>
-      <c r="FI2">
-        <v>7.5673647722332996E-2</v>
-      </c>
-      <c r="FJ2">
-        <v>7.2862296939930501E-2</v>
-      </c>
-      <c r="FK2">
-        <v>7.6958818951244998E-2</v>
-      </c>
-      <c r="FL2">
-        <v>8.1544619025140805E-2</v>
-      </c>
-      <c r="FM2">
-        <v>7.1458857601879006E-2</v>
-      </c>
-      <c r="FN2">
-        <v>7.6924595223422196E-2</v>
-      </c>
-      <c r="FO2">
-        <v>8.1997290414881893E-2</v>
-      </c>
-      <c r="FP2">
-        <v>8.4574917944426703E-2</v>
-      </c>
-      <c r="FQ2">
-        <v>8.5626315439430098E-2</v>
-      </c>
-      <c r="FR2">
-        <v>8.6774440920707505E-2</v>
-      </c>
-      <c r="FS2">
-        <v>8.7496327126603601E-2</v>
-      </c>
-      <c r="FT2">
-        <v>8.7851185743623897E-2</v>
-      </c>
-      <c r="FU2">
-        <v>8.6596537458988695E-2</v>
-      </c>
-      <c r="FV2">
-        <v>8.4225670712307493E-2</v>
-      </c>
-      <c r="FW2">
-        <v>9.2752045565452801E-2</v>
-      </c>
-      <c r="FX2">
-        <v>9.4077888063453102E-2</v>
-      </c>
-      <c r="FY2">
-        <v>9.0493375641976195E-2</v>
-      </c>
-      <c r="FZ2">
-        <v>8.6472175966865503E-2</v>
-      </c>
-      <c r="GA2">
-        <v>8.3024907576413107E-2</v>
-      </c>
-      <c r="GB2">
-        <v>9.3677130612539294E-2</v>
-      </c>
-      <c r="GC2">
-        <v>9.6155648550436498E-2</v>
-      </c>
-      <c r="GD2">
-        <v>9.1979209761255704E-2</v>
-      </c>
-      <c r="GE2">
-        <v>0.11006901167984599</v>
-      </c>
-      <c r="GF2">
-        <v>0.10284983555117599</v>
-      </c>
-      <c r="GG2">
-        <v>9.6627557037829201E-2</v>
-      </c>
-      <c r="GH2">
-        <v>9.88076268442169E-2</v>
-      </c>
-      <c r="GI2">
-        <v>9.6435558936374705E-2</v>
-      </c>
-      <c r="GJ2">
-        <v>9.7091562832332307E-2</v>
-      </c>
-      <c r="GK2">
-        <v>6.2246957480945303E-2</v>
-      </c>
-      <c r="GL2">
-        <v>5.0601944065161102E-2</v>
-      </c>
-      <c r="GM2">
-        <v>5.7695114836403799E-2</v>
-      </c>
-      <c r="GN2">
-        <v>6.5231957690377304E-2</v>
-      </c>
-      <c r="GO2">
-        <v>7.3885503944917399E-2</v>
-      </c>
-      <c r="GP2">
-        <v>5.44867010278101E-2</v>
-      </c>
-      <c r="GQ2">
-        <v>6.0151474854133302E-2</v>
-      </c>
-      <c r="GR2">
-        <v>5.4588284980985301E-2</v>
-      </c>
-      <c r="GS2">
-        <v>5.9867829495097002E-2</v>
-      </c>
-      <c r="GT2">
-        <v>6.6490814187487202E-2</v>
-      </c>
-      <c r="GU2">
-        <v>7.3423837857614804E-2</v>
-      </c>
-      <c r="GV2">
-        <v>7.2399279258235805E-2</v>
-      </c>
-      <c r="GW2">
-        <v>7.8072519228778003E-2</v>
-      </c>
-      <c r="GX2">
-        <v>8.4315549187248595E-2</v>
-      </c>
-      <c r="GY2">
-        <v>7.4634009792752407E-2</v>
-      </c>
-      <c r="GZ2">
-        <v>7.4184361965681803E-2</v>
-      </c>
-      <c r="HA2">
-        <v>8.1387730818578502E-2</v>
-      </c>
-      <c r="HB2">
-        <v>8.7723400626332604E-2</v>
-      </c>
-      <c r="HC2">
-        <v>8.4390155995239302E-2</v>
-      </c>
-      <c r="HD2">
-        <v>8.9522727737690003E-2</v>
-      </c>
-      <c r="HE2">
-        <v>9.3983192786837699E-2</v>
-      </c>
-      <c r="HF2">
-        <v>9.0300439124021997E-2</v>
-      </c>
-      <c r="HG2">
-        <v>9.4686402263195399E-2</v>
-      </c>
-      <c r="HH2">
-        <v>9.6130812593367906E-2</v>
-      </c>
-      <c r="HI2">
-        <v>9.2980985203893196E-2</v>
-      </c>
-      <c r="HJ2">
-        <v>9.1886663893155807E-2</v>
-      </c>
-      <c r="HK2">
-        <v>9.3112630941761199E-2</v>
-      </c>
-      <c r="HL2">
-        <v>9.2331557932939304E-2</v>
-      </c>
-      <c r="HM2">
-        <v>9.37812086014021E-2</v>
-      </c>
-      <c r="HN2">
-        <v>9.5878411042679995E-2</v>
-      </c>
-      <c r="HO2">
-        <v>9.8477896299678097E-2</v>
-      </c>
-      <c r="HP2">
-        <v>9.6727519228440403E-2</v>
-      </c>
-      <c r="HQ2">
-        <v>9.6878387536869406E-2</v>
-      </c>
-      <c r="HR2">
-        <v>9.8766920244862597E-2</v>
-      </c>
-      <c r="HS2">
-        <v>9.4731056626623095E-2</v>
-      </c>
-      <c r="HT2">
-        <v>9.5673121208416007E-2</v>
-      </c>
-      <c r="HU2">
-        <v>9.4908968474161901E-2</v>
-      </c>
-      <c r="HV2">
-        <v>9.3381705881011898E-2</v>
-      </c>
-      <c r="HW2">
-        <v>9.3361250405555304E-2</v>
-      </c>
-      <c r="HX2">
-        <v>9.6388910800607797E-2</v>
-      </c>
-      <c r="HY2">
-        <v>9.5411261399929198E-2</v>
-      </c>
-      <c r="HZ2">
-        <v>9.4441788201127599E-2</v>
-      </c>
-      <c r="IA2">
-        <v>9.2484889966943901E-2</v>
-      </c>
-      <c r="IB2">
-        <v>8.9557261790498402E-2</v>
-      </c>
-      <c r="IC2">
-        <v>8.5489723394614997E-2</v>
-      </c>
-      <c r="ID2">
-        <v>8.70605480624419E-2</v>
-      </c>
-      <c r="IE2">
-        <v>2.5759320650292E-2</v>
-      </c>
-      <c r="IF2">
-        <v>2.8788306160243499E-2</v>
-      </c>
-      <c r="IG2">
-        <v>3.1795604385897798E-2</v>
-      </c>
-      <c r="IH2">
-        <v>3.4564735093059497E-2</v>
-      </c>
-      <c r="II2">
-        <v>3.68102971298543E-2</v>
-      </c>
-      <c r="IJ2">
-        <v>3.8849332085413003E-2</v>
-      </c>
-      <c r="IK2">
-        <v>4.0152134785636097E-2</v>
-      </c>
-      <c r="IL2">
-        <v>4.1883469604202202E-2</v>
-      </c>
-      <c r="IM2">
-        <v>4.5489165407062798E-2</v>
-      </c>
-      <c r="IN2">
-        <v>4.71675568587029E-2</v>
-      </c>
-      <c r="IO2">
-        <v>4.8708951612338298E-2</v>
-      </c>
-      <c r="IP2">
-        <v>5.0085398424166101E-2</v>
-      </c>
-      <c r="IQ2">
-        <v>5.2802011604845003E-2</v>
-      </c>
-      <c r="IR2">
-        <v>6.0620034232809601E-2</v>
-      </c>
-      <c r="IS2">
-        <v>6.2326903323394002E-2</v>
-      </c>
-      <c r="IT2">
-        <v>6.2334582086227303E-2</v>
-      </c>
-      <c r="IU2">
-        <v>6.2397748718477801E-2</v>
-      </c>
-      <c r="IV2">
-        <v>6.5735901284672701E-2</v>
-      </c>
-      <c r="IW2">
-        <v>6.4936687623017603E-2</v>
-      </c>
-      <c r="IX2">
-        <v>6.5484195495869799E-2</v>
-      </c>
-      <c r="IY2">
-        <v>6.7606921952117704E-2</v>
-      </c>
-      <c r="IZ2">
-        <v>6.6408082663590495E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:260" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>8.0412262509569496E-2</v>
-      </c>
-      <c r="B3">
-        <v>6.8114383081789895E-2</v>
-      </c>
-      <c r="C3">
-        <v>6.9459038718510793E-2</v>
-      </c>
-      <c r="D3">
-        <v>7.78581461950522E-2</v>
-      </c>
-      <c r="E3">
-        <v>7.34921022870825E-2</v>
-      </c>
-      <c r="F3">
-        <v>7.4378050213133304E-2</v>
-      </c>
-      <c r="G3">
-        <v>7.4691016129387597E-2</v>
-      </c>
-      <c r="H3">
-        <v>7.5172125892579794E-2</v>
-      </c>
-      <c r="I3">
-        <v>7.2076745494845301E-2</v>
-      </c>
-      <c r="J3">
-        <v>7.6273770812274502E-2</v>
-      </c>
-      <c r="K3">
-        <v>7.8323553558387701E-2</v>
-      </c>
-      <c r="L3">
-        <v>7.8900049193404598E-2</v>
-      </c>
-      <c r="M3">
-        <v>7.8740082018634902E-2</v>
-      </c>
-      <c r="N3">
-        <v>8.2520688893575597E-2</v>
-      </c>
-      <c r="O3">
-        <v>8.9308777644000997E-2</v>
-      </c>
-      <c r="P3">
-        <v>9.3371696766626697E-2</v>
-      </c>
-      <c r="Q3">
-        <v>9.6017016578975406E-2</v>
-      </c>
-      <c r="R3">
-        <v>7.7508499310819504E-2</v>
-      </c>
-      <c r="S3">
-        <v>9.0060037751781494E-2</v>
-      </c>
-      <c r="T3">
-        <v>9.7582307596855794E-2</v>
-      </c>
-      <c r="U3">
-        <v>0.110397607482437</v>
-      </c>
-      <c r="V3">
-        <v>6.4915497262227298E-2</v>
-      </c>
-      <c r="W3">
-        <v>5.0368442055243601E-2</v>
-      </c>
-      <c r="X3">
-        <v>5.5486372067909497E-2</v>
-      </c>
-      <c r="Y3">
-        <v>4.6033907819652602E-2</v>
-      </c>
-      <c r="Z3">
-        <v>5.4498548770953198E-2</v>
-      </c>
-      <c r="AA3">
-        <v>4.7802755981495901E-2</v>
-      </c>
-      <c r="AB3">
-        <v>4.4222075728205301E-2</v>
-      </c>
-      <c r="AC3">
-        <v>4.0980151773218697E-2</v>
-      </c>
-      <c r="AD3">
-        <v>3.81493771553389E-2</v>
-      </c>
-      <c r="AE3">
-        <v>3.7084277364334201E-2</v>
-      </c>
-      <c r="AF3">
-        <v>3.7423732058210001E-2</v>
-      </c>
-      <c r="AG3">
-        <v>3.6051175780210297E-2</v>
-      </c>
-      <c r="AH3">
-        <v>3.8991362706342E-2</v>
-      </c>
-      <c r="AI3">
-        <v>3.74877079570985E-2</v>
-      </c>
-      <c r="AJ3">
-        <v>4.0225874742104303E-2</v>
-      </c>
-      <c r="AK3">
-        <v>4.0791874340543301E-2</v>
-      </c>
-      <c r="AL3">
-        <v>4.3077264989655299E-2</v>
-      </c>
-      <c r="AM3">
-        <v>4.5970418815589102E-2</v>
-      </c>
-      <c r="AN3">
-        <v>4.8287914496835803E-2</v>
-      </c>
-      <c r="AO3">
-        <v>5.4558549491482901E-2</v>
-      </c>
-      <c r="AP3">
-        <v>5.6277459228902399E-2</v>
-      </c>
-      <c r="AQ3">
-        <v>5.6156177761322701E-2</v>
-      </c>
-      <c r="AR3">
-        <v>5.5714097629774799E-2</v>
-      </c>
-      <c r="AS3">
-        <v>5.6246392171006097E-2</v>
-      </c>
-      <c r="AT3">
-        <v>5.8310387983819101E-2</v>
-      </c>
-      <c r="AU3">
-        <v>6.0748706859581503E-2</v>
-      </c>
-      <c r="AV3">
-        <v>5.9565782419017901E-2</v>
-      </c>
-      <c r="AW3">
-        <v>6.9925104615074604E-2</v>
-      </c>
-      <c r="AX3">
-        <v>6.0152925478205402E-2</v>
-      </c>
-      <c r="AY3">
-        <v>5.0361559896089501E-2</v>
-      </c>
-      <c r="AZ3">
-        <v>4.7067865656518403E-2</v>
-      </c>
-      <c r="BA3">
-        <v>4.3580236786069197E-2</v>
-      </c>
-      <c r="BB3">
-        <v>4.4213205152333603E-2</v>
-      </c>
-      <c r="BC3">
-        <v>4.5761960794565598E-2</v>
-      </c>
-      <c r="BD3">
-        <v>5.0296194179796597E-2</v>
-      </c>
-      <c r="BE3">
-        <v>5.7815141399471297E-2</v>
-      </c>
-      <c r="BF3">
-        <v>4.4679945940811698E-2</v>
-      </c>
-      <c r="BG3">
-        <v>3.8031089056621899E-2</v>
-      </c>
-      <c r="BH3">
-        <v>4.2552628025776897E-2</v>
-      </c>
-      <c r="BI3">
-        <v>5.1657229030141902E-2</v>
-      </c>
-      <c r="BJ3">
-        <v>5.1512773028261703E-2</v>
-      </c>
-      <c r="BK3">
-        <v>4.8230585686746402E-2</v>
-      </c>
-      <c r="BL3">
-        <v>5.4563381713072998E-2</v>
-      </c>
-      <c r="BM3">
-        <v>6.4062163203844599E-2</v>
-      </c>
-      <c r="BN3">
-        <v>7.41189094443956E-2</v>
-      </c>
-      <c r="BO3">
-        <v>7.2161995693432401E-2</v>
-      </c>
-      <c r="BP3">
-        <v>7.1692323203137398E-2</v>
-      </c>
-      <c r="BQ3">
-        <v>6.9382450627631001E-2</v>
-      </c>
-      <c r="BR3">
-        <v>7.6452328360130301E-2</v>
-      </c>
-      <c r="BS3">
-        <v>6.7350983502477604E-2</v>
-      </c>
-      <c r="BT3">
-        <v>6.6995709412218496E-2</v>
-      </c>
-      <c r="BU3">
-        <v>5.9095264625725098E-2</v>
-      </c>
-      <c r="BV3">
-        <v>6.4281798672796903E-2</v>
-      </c>
-      <c r="BW3">
-        <v>6.2813931349028795E-2</v>
-      </c>
-      <c r="BX3">
-        <v>6.1520115924225099E-2</v>
-      </c>
-      <c r="BY3">
-        <v>6.19416199985654E-2</v>
-      </c>
-      <c r="BZ3">
-        <v>6.3422190947991994E-2</v>
-      </c>
-      <c r="CA3">
-        <v>7.0318173743967594E-2</v>
-      </c>
-      <c r="CB3">
-        <v>8.2470772684854601E-2</v>
-      </c>
-      <c r="CC3">
-        <v>9.6131894805018797E-2</v>
-      </c>
-      <c r="CD3">
-        <v>9.0539279815945603E-2</v>
-      </c>
-      <c r="CE3">
-        <v>7.9888892317827295E-2</v>
-      </c>
-      <c r="CF3">
-        <v>7.4357848846772295E-2</v>
-      </c>
-      <c r="CG3">
-        <v>6.2683913999372301E-2</v>
-      </c>
-      <c r="CH3">
-        <v>4.6098474388445297E-2</v>
-      </c>
-      <c r="CI3">
-        <v>3.8531441388039801E-2</v>
-      </c>
-      <c r="CJ3">
-        <v>5.0039602478243399E-2</v>
-      </c>
-      <c r="CK3">
-        <v>3.7288137380804401E-2</v>
-      </c>
-      <c r="CL3">
-        <v>3.4061759593704298E-2</v>
-      </c>
-      <c r="CM3">
-        <v>3.4424627797671498E-2</v>
-      </c>
-      <c r="CN3">
-        <v>4.0777271358494703E-2</v>
-      </c>
-      <c r="CO3">
-        <v>4.1319191553096497E-2</v>
-      </c>
-      <c r="CP3">
-        <v>4.0614418977424203E-2</v>
-      </c>
-      <c r="CQ3">
-        <v>4.41476804596415E-2</v>
-      </c>
-      <c r="CR3">
-        <v>4.5265781610698302E-2</v>
-      </c>
-      <c r="CS3">
-        <v>4.6166731207283297E-2</v>
-      </c>
-      <c r="CT3">
-        <v>4.9418414195628403E-2</v>
-      </c>
-      <c r="CU3">
-        <v>4.9758793340061398E-2</v>
-      </c>
-      <c r="CV3">
-        <v>5.1815555601508502E-2</v>
-      </c>
-      <c r="CW3">
-        <v>5.3254872439902103E-2</v>
-      </c>
-      <c r="CX3">
-        <v>5.5249764413682997E-2</v>
-      </c>
-      <c r="CY3">
-        <v>5.5858890401245503E-2</v>
-      </c>
-      <c r="CZ3">
-        <v>5.6546648205524699E-2</v>
-      </c>
-      <c r="DA3">
-        <v>5.9559138188203603E-2</v>
-      </c>
-      <c r="DB3">
-        <v>5.8746168215467E-2</v>
-      </c>
-      <c r="DC3">
-        <v>6.1423081494703401E-2</v>
-      </c>
-      <c r="DD3">
-        <v>6.2535059432468398E-2</v>
-      </c>
-      <c r="DE3">
-        <v>6.1960777616319102E-2</v>
-      </c>
-      <c r="DF3">
-        <v>6.4199450576394798E-2</v>
-      </c>
-      <c r="DG3">
-        <v>6.17871906376588E-2</v>
-      </c>
-      <c r="DH3">
-        <v>6.3757235346227001E-2</v>
-      </c>
-      <c r="DI3">
-        <v>6.7392852584853793E-2</v>
-      </c>
-      <c r="DJ3">
-        <v>7.2246001937914597E-2</v>
-      </c>
-      <c r="DK3">
-        <v>8.1202129069625095E-2</v>
-      </c>
-      <c r="DL3">
-        <v>9.2244345340760703E-2</v>
-      </c>
-      <c r="DM3">
-        <v>8.1006911253304101E-2</v>
-      </c>
-      <c r="DN3">
-        <v>7.2380137799712793E-2</v>
-      </c>
-      <c r="DO3">
-        <v>7.2403465304449299E-2</v>
-      </c>
-      <c r="DP3">
-        <v>7.6113677451424902E-2</v>
-      </c>
-      <c r="DQ3">
-        <v>7.1899506138129995E-2</v>
-      </c>
-      <c r="DR3">
-        <v>7.81870011390704E-2</v>
-      </c>
-      <c r="DS3">
-        <v>6.9449035661975606E-2</v>
-      </c>
-      <c r="DT3">
-        <v>7.9207798345135805E-2</v>
-      </c>
-      <c r="DU3">
-        <v>6.9320749709424506E-2</v>
-      </c>
-      <c r="DV3">
-        <v>6.8547838469994196E-2</v>
-      </c>
-      <c r="DW3">
-        <v>6.4888442715463707E-2</v>
-      </c>
-      <c r="DX3">
-        <v>6.1823531305803099E-2</v>
-      </c>
-      <c r="DY3">
-        <v>6.5537184379655999E-2</v>
-      </c>
-      <c r="DZ3">
-        <v>6.5737222100815798E-2</v>
-      </c>
-      <c r="EA3">
-        <v>7.0327075983761603E-2</v>
-      </c>
-      <c r="EB3">
-        <v>6.4749912347114594E-2</v>
-      </c>
-      <c r="EC3">
-        <v>6.4507187335108795E-2</v>
-      </c>
-      <c r="ED3">
-        <v>6.3702400508463597E-2</v>
-      </c>
-      <c r="EE3">
-        <v>6.44993516301616E-2</v>
-      </c>
-      <c r="EF3">
-        <v>6.5462736271049995E-2</v>
-      </c>
-      <c r="EG3">
-        <v>6.71784224926089E-2</v>
-      </c>
-      <c r="EH3">
-        <v>6.8130840411374002E-2</v>
-      </c>
-      <c r="EI3">
-        <v>7.0409152727839097E-2</v>
-      </c>
-      <c r="EJ3">
-        <v>6.9730595013302199E-2</v>
-      </c>
-      <c r="EK3">
-        <v>7.1056410513446105E-2</v>
-      </c>
-      <c r="EL3">
-        <v>6.9966897996453295E-2</v>
-      </c>
-      <c r="EM3">
-        <v>6.8738188592488106E-2</v>
-      </c>
-      <c r="EN3">
-        <v>7.0836526380826798E-2</v>
-      </c>
-      <c r="EO3">
-        <v>6.8071339248765905E-2</v>
-      </c>
-      <c r="EP3">
-        <v>7.0512802848333306E-2</v>
-      </c>
-      <c r="EQ3">
-        <v>6.5245074017470595E-2</v>
-      </c>
-      <c r="ER3">
-        <v>7.25218160134143E-2</v>
-      </c>
-      <c r="ES3">
-        <v>7.25856463351255E-2</v>
-      </c>
-      <c r="ET3">
-        <v>7.5124706583984097E-2</v>
-      </c>
-      <c r="EU3">
-        <v>7.6029117301079502E-2</v>
-      </c>
-      <c r="EV3">
-        <v>7.2892446073740402E-2</v>
-      </c>
-      <c r="EW3">
-        <v>8.0520734380711501E-2</v>
-      </c>
-      <c r="EX3">
-        <v>9.1171353466160704E-2</v>
-      </c>
-      <c r="EY3">
-        <v>7.8886875746069202E-2</v>
-      </c>
-      <c r="EZ3">
-        <v>8.0759447456570599E-2</v>
-      </c>
-      <c r="FA3">
-        <v>6.8460077115476706E-2</v>
-      </c>
-      <c r="FB3">
-        <v>6.8713521742040901E-2</v>
-      </c>
-      <c r="FC3">
-        <v>8.0000785161834606E-2</v>
-      </c>
-      <c r="FD3">
-        <v>7.0816769256526996E-2</v>
-      </c>
-      <c r="FE3">
-        <v>6.9150294353438002E-2</v>
-      </c>
-      <c r="FF3">
-        <v>6.9785759180693394E-2</v>
-      </c>
-      <c r="FG3">
-        <v>7.02818299550899E-2</v>
-      </c>
-      <c r="FH3">
-        <v>6.4492025974764597E-2</v>
-      </c>
-      <c r="FI3">
-        <v>7.1782294850801898E-2</v>
-      </c>
-      <c r="FJ3">
-        <v>6.4483224436535702E-2</v>
-      </c>
-      <c r="FK3">
-        <v>7.1224835693599595E-2</v>
-      </c>
-      <c r="FL3">
-        <v>7.1487544839950803E-2</v>
-      </c>
-      <c r="FM3">
-        <v>6.2878450106398795E-2</v>
-      </c>
-      <c r="FN3">
-        <v>6.1530280483732401E-2</v>
-      </c>
-      <c r="FO3">
-        <v>6.8408522165830501E-2</v>
-      </c>
-      <c r="FP3">
-        <v>7.2018909658204802E-2</v>
-      </c>
-      <c r="FQ3">
-        <v>7.2169558501021705E-2</v>
-      </c>
-      <c r="FR3">
-        <v>7.4843571809624296E-2</v>
-      </c>
-      <c r="FS3">
-        <v>7.5343245613807702E-2</v>
-      </c>
-      <c r="FT3">
-        <v>7.5876776504967602E-2</v>
-      </c>
-      <c r="FU3">
-        <v>7.4374607666311002E-2</v>
-      </c>
-      <c r="FV3">
-        <v>7.0410605348192407E-2</v>
-      </c>
-      <c r="FW3">
-        <v>7.3417207881463303E-2</v>
-      </c>
-      <c r="FX3">
-        <v>7.8907831934722297E-2</v>
-      </c>
-      <c r="FY3">
-        <v>7.4705734608150498E-2</v>
-      </c>
-      <c r="FZ3">
-        <v>8.0422864405055999E-2</v>
-      </c>
-      <c r="GA3">
-        <v>7.3692908007674598E-2</v>
-      </c>
-      <c r="GB3">
-        <v>7.6937953281358801E-2</v>
-      </c>
-      <c r="GC3">
-        <v>8.4411629672693694E-2</v>
-      </c>
-      <c r="GD3">
-        <v>7.8212733428918907E-2</v>
-      </c>
-      <c r="GE3">
-        <v>8.4897012824629997E-2</v>
-      </c>
-      <c r="GF3">
-        <v>7.9502777290545099E-2</v>
-      </c>
-      <c r="GG3">
-        <v>7.2732766886547298E-2</v>
-      </c>
-      <c r="GH3">
-        <v>7.5380057233865996E-2</v>
-      </c>
-      <c r="GI3">
-        <v>7.8229090884121305E-2</v>
-      </c>
-      <c r="GJ3">
-        <v>8.0723297079549505E-2</v>
-      </c>
-      <c r="GK3">
-        <v>6.8782529655361802E-2</v>
-      </c>
-      <c r="GL3">
-        <v>5.3541706547227799E-2</v>
-      </c>
-      <c r="GM3">
-        <v>6.7231428129439094E-2</v>
-      </c>
-      <c r="GN3">
-        <v>8.4736540816910802E-2</v>
-      </c>
-      <c r="GO3">
-        <v>0.112590255907631</v>
-      </c>
-      <c r="GP3">
-        <v>7.5320367989657702E-2</v>
-      </c>
-      <c r="GQ3">
-        <v>6.7426832834104902E-2</v>
-      </c>
-      <c r="GR3">
-        <v>5.7017893437401601E-2</v>
-      </c>
-      <c r="GS3">
-        <v>6.6861156060497695E-2</v>
-      </c>
-      <c r="GT3">
-        <v>8.7513394825962404E-2</v>
-      </c>
-      <c r="GU3">
-        <v>0.113642506195454</v>
-      </c>
-      <c r="GV3">
-        <v>7.8652832735388797E-2</v>
-      </c>
-      <c r="GW3">
-        <v>6.69832971412192E-2</v>
-      </c>
-      <c r="GX3">
-        <v>7.78413017874557E-2</v>
-      </c>
-      <c r="GY3">
-        <v>6.4796609021331594E-2</v>
-      </c>
-      <c r="GZ3">
-        <v>5.5320566168743202E-2</v>
-      </c>
-      <c r="HA3">
-        <v>6.5698649101143897E-2</v>
-      </c>
-      <c r="HB3">
-        <v>6.2252070429616703E-2</v>
-      </c>
-      <c r="HC3">
-        <v>5.4723601713159598E-2</v>
-      </c>
-      <c r="HD3">
-        <v>6.2754676097170101E-2</v>
-      </c>
-      <c r="HE3">
-        <v>6.7198171637221804E-2</v>
-      </c>
-      <c r="HF3">
-        <v>5.7181809087081599E-2</v>
-      </c>
-      <c r="HG3">
-        <v>6.6205512118146098E-2</v>
-      </c>
-      <c r="HH3">
-        <v>6.3486730595294499E-2</v>
-      </c>
-      <c r="HI3">
-        <v>5.9977834207037797E-2</v>
-      </c>
-      <c r="HJ3">
-        <v>5.8511167837382097E-2</v>
-      </c>
-      <c r="HK3">
-        <v>6.1866443032442001E-2</v>
-      </c>
-      <c r="HL3">
-        <v>6.0158343928544002E-2</v>
-      </c>
-      <c r="HM3">
-        <v>5.8660022885223199E-2</v>
-      </c>
-      <c r="HN3">
-        <v>6.3867286683798694E-2</v>
-      </c>
-      <c r="HO3">
-        <v>7.0928477531160106E-2</v>
-      </c>
-      <c r="HP3">
-        <v>6.6770246215576506E-2</v>
-      </c>
-      <c r="HQ3">
-        <v>6.4015257378480503E-2</v>
-      </c>
-      <c r="HR3">
-        <v>6.9640608149905303E-2</v>
-      </c>
-      <c r="HS3">
-        <v>6.6082654659158302E-2</v>
-      </c>
-      <c r="HT3">
-        <v>6.6127625445412105E-2</v>
-      </c>
-      <c r="HU3">
-        <v>6.7154841365048595E-2</v>
-      </c>
-      <c r="HV3">
-        <v>6.6843266537585697E-2</v>
-      </c>
-      <c r="HW3">
-        <v>6.93056553708115E-2</v>
-      </c>
-      <c r="HX3">
-        <v>7.2183225623216093E-2</v>
-      </c>
-      <c r="HY3">
-        <v>7.2538724396118998E-2</v>
-      </c>
-      <c r="HZ3">
-        <v>7.3736454013988095E-2</v>
-      </c>
-      <c r="IA3">
-        <v>7.4001922301065101E-2</v>
-      </c>
-      <c r="IB3">
-        <v>7.8143884829052296E-2</v>
-      </c>
-      <c r="IC3">
-        <v>8.14412137752904E-2</v>
-      </c>
-      <c r="ID3">
-        <v>8.4641994784528093E-2</v>
-      </c>
-      <c r="IE3">
-        <v>6.1989847642114501E-2</v>
-      </c>
-      <c r="IF3">
-        <v>6.9841849404114503E-2</v>
-      </c>
-      <c r="IG3">
-        <v>7.3541061105093897E-2</v>
-      </c>
-      <c r="IH3">
-        <v>7.65945241264816E-2</v>
-      </c>
-      <c r="II3">
-        <v>7.4585292821731403E-2</v>
-      </c>
-      <c r="IJ3">
-        <v>7.1211353000911901E-2</v>
-      </c>
-      <c r="IK3">
-        <v>6.2833048479952996E-2</v>
-      </c>
-      <c r="IL3">
-        <v>6.0675755749235803E-2</v>
-      </c>
-      <c r="IM3">
-        <v>6.4269537331031107E-2</v>
-      </c>
-      <c r="IN3">
-        <v>6.2794220107130705E-2</v>
-      </c>
-      <c r="IO3">
-        <v>6.4498869578919996E-2</v>
-      </c>
-      <c r="IP3">
-        <v>6.3145554608679405E-2</v>
-      </c>
-      <c r="IQ3">
-        <v>6.7833178949972706E-2</v>
-      </c>
-      <c r="IR3">
-        <v>7.3349325442376101E-2</v>
-      </c>
-      <c r="IS3">
-        <v>8.2442589183162093E-2</v>
-      </c>
-      <c r="IT3">
-        <v>7.6679777862155907E-2</v>
-      </c>
-      <c r="IU3">
-        <v>8.2429346065196599E-2</v>
-      </c>
-      <c r="IV3">
-        <v>9.2067968783158205E-2</v>
-      </c>
-      <c r="IW3">
-        <v>8.2008565393283606E-2</v>
-      </c>
-      <c r="IX3">
-        <v>7.8051148397214207E-2</v>
-      </c>
-      <c r="IY3">
-        <v>8.37248990583839E-2</v>
-      </c>
-      <c r="IZ3">
-        <v>7.6241930314511694E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:260" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>6.6995069777067595E-2</v>
-      </c>
-      <c r="B4">
-        <v>5.9383101983534997E-2</v>
-      </c>
-      <c r="C4">
-        <v>5.5052245780131397E-2</v>
-      </c>
-      <c r="D4">
-        <v>5.38982482817865E-2</v>
-      </c>
-      <c r="E4">
-        <v>5.3440617816242597E-2</v>
-      </c>
-      <c r="F4">
-        <v>5.4305174792082002E-2</v>
-      </c>
-      <c r="G4">
-        <v>5.4930500455099798E-2</v>
-      </c>
-      <c r="H4">
-        <v>5.5825090679014401E-2</v>
-      </c>
-      <c r="I4">
-        <v>5.5492148507642697E-2</v>
-      </c>
-      <c r="J4">
-        <v>5.6250263186023802E-2</v>
-      </c>
-      <c r="K4">
-        <v>5.6068468390209202E-2</v>
-      </c>
-      <c r="L4">
-        <v>5.7658158442343697E-2</v>
-      </c>
-      <c r="M4">
-        <v>5.8382491892244898E-2</v>
-      </c>
-      <c r="N4">
-        <v>6.0982409478506999E-2</v>
-      </c>
-      <c r="O4">
-        <v>6.3587232836654101E-2</v>
-      </c>
-      <c r="P4">
-        <v>6.7270801215682893E-2</v>
-      </c>
-      <c r="Q4">
-        <v>6.9141533836069594E-2</v>
-      </c>
-      <c r="R4">
-        <v>6.8209818059119701E-2</v>
-      </c>
-      <c r="S4">
-        <v>7.3798153433446201E-2</v>
-      </c>
-      <c r="T4">
-        <v>8.3553741389050196E-2</v>
-      </c>
-      <c r="U4">
-        <v>0.100491629353962</v>
-      </c>
-      <c r="V4">
-        <v>3.4045697193706398E-2</v>
-      </c>
-      <c r="W4">
-        <v>2.7426288902780701E-2</v>
-      </c>
-      <c r="X4">
-        <v>3.1370994087702497E-2</v>
-      </c>
-      <c r="Y4">
-        <v>3.3805616570239803E-2</v>
-      </c>
-      <c r="Z4">
-        <v>3.8254629206018798E-2</v>
-      </c>
-      <c r="AA4">
-        <v>4.0840198686045902E-2</v>
-      </c>
-      <c r="AB4">
-        <v>3.45349098321443E-2</v>
-      </c>
-      <c r="AC4">
-        <v>3.6104057268750198E-2</v>
-      </c>
-      <c r="AD4">
-        <v>3.1537513539868202E-2</v>
-      </c>
-      <c r="AE4">
-        <v>3.5609401970393299E-2</v>
-      </c>
-      <c r="AF4">
-        <v>4.0644827745274503E-2</v>
-      </c>
-      <c r="AG4">
-        <v>4.1702346210789699E-2</v>
-      </c>
-      <c r="AH4">
-        <v>4.6952152012803602E-2</v>
-      </c>
-      <c r="AI4">
-        <v>4.0652860530547903E-2</v>
-      </c>
-      <c r="AJ4">
-        <v>4.4792967832846899E-2</v>
-      </c>
-      <c r="AK4">
-        <v>4.6570913822641898E-2</v>
-      </c>
-      <c r="AL4">
-        <v>4.81816224190348E-2</v>
-      </c>
-      <c r="AM4">
-        <v>4.9439759542568802E-2</v>
-      </c>
-      <c r="AN4">
-        <v>5.00916247211406E-2</v>
-      </c>
-      <c r="AO4">
-        <v>6.2089591733109503E-2</v>
-      </c>
-      <c r="AP4">
-        <v>6.1577541717302599E-2</v>
-      </c>
-      <c r="AQ4">
-        <v>6.0589085808005101E-2</v>
-      </c>
-      <c r="AR4">
-        <v>5.9761025052178202E-2</v>
-      </c>
-      <c r="AS4">
-        <v>5.79675176656494E-2</v>
-      </c>
-      <c r="AT4">
-        <v>5.9768331419443599E-2</v>
-      </c>
-      <c r="AU4">
-        <v>6.2863090201846605E-2</v>
-      </c>
-      <c r="AV4">
-        <v>6.5972292640139596E-2</v>
-      </c>
-      <c r="AW4">
-        <v>7.1645511874048995E-2</v>
-      </c>
-      <c r="AX4">
-        <v>8.0892204740364196E-2</v>
-      </c>
-      <c r="AY4">
-        <v>4.5074322637864199E-2</v>
-      </c>
-      <c r="AZ4">
-        <v>3.8354695878006301E-2</v>
-      </c>
-      <c r="BA4">
-        <v>3.5957814420464203E-2</v>
-      </c>
-      <c r="BB4">
-        <v>3.5660123996270797E-2</v>
-      </c>
-      <c r="BC4">
-        <v>3.6707685995234003E-2</v>
-      </c>
-      <c r="BD4">
-        <v>4.1828054805465503E-2</v>
-      </c>
-      <c r="BE4">
-        <v>5.2005181997458898E-2</v>
-      </c>
-      <c r="BF4">
-        <v>4.7570774390710502E-2</v>
-      </c>
-      <c r="BG4">
-        <v>4.3438764271686602E-2</v>
-      </c>
-      <c r="BH4">
-        <v>4.1379514884589803E-2</v>
-      </c>
-      <c r="BI4">
-        <v>4.2506310048635101E-2</v>
-      </c>
-      <c r="BJ4">
-        <v>4.2106329574429502E-2</v>
-      </c>
-      <c r="BK4">
-        <v>4.2203755304713202E-2</v>
-      </c>
-      <c r="BL4">
-        <v>5.0748186337441298E-2</v>
-      </c>
-      <c r="BM4">
-        <v>5.1478035605734003E-2</v>
-      </c>
-      <c r="BN4">
-        <v>5.3188423845016097E-2</v>
-      </c>
-      <c r="BO4">
-        <v>5.3041235138825901E-2</v>
-      </c>
-      <c r="BP4">
-        <v>5.4064522133932598E-2</v>
-      </c>
-      <c r="BQ4">
-        <v>5.4090764840974699E-2</v>
-      </c>
-      <c r="BR4">
-        <v>5.5175527735737903E-2</v>
-      </c>
-      <c r="BS4">
-        <v>4.9898352131883601E-2</v>
-      </c>
-      <c r="BT4">
-        <v>5.3791734251976503E-2</v>
-      </c>
-      <c r="BU4">
-        <v>5.6631695577192699E-2</v>
-      </c>
-      <c r="BV4">
-        <v>5.9748887317752297E-2</v>
-      </c>
-      <c r="BW4">
-        <v>5.5114893500191602E-2</v>
-      </c>
-      <c r="BX4">
-        <v>5.6843348341571502E-2</v>
-      </c>
-      <c r="BY4">
-        <v>5.6205044886414E-2</v>
-      </c>
-      <c r="BZ4">
-        <v>5.7375549954828201E-2</v>
-      </c>
-      <c r="CA4">
-        <v>5.33687764652723E-2</v>
-      </c>
-      <c r="CB4">
-        <v>5.0060587368298902E-2</v>
-      </c>
-      <c r="CC4">
-        <v>5.7792178642157799E-2</v>
-      </c>
-      <c r="CD4">
-        <v>5.7292764080954697E-2</v>
-      </c>
-      <c r="CE4">
-        <v>5.4687429081918003E-2</v>
-      </c>
-      <c r="CF4">
-        <v>5.3306677244159897E-2</v>
-      </c>
-      <c r="CG4">
-        <v>4.9715519112385302E-2</v>
-      </c>
-      <c r="CH4">
-        <v>4.5012046693565698E-2</v>
-      </c>
-      <c r="CI4">
-        <v>4.1067983889803102E-2</v>
-      </c>
-      <c r="CJ4">
-        <v>4.8320857160178102E-2</v>
-      </c>
-      <c r="CK4">
-        <v>4.1794542191432298E-2</v>
-      </c>
-      <c r="CL4">
-        <v>3.7392429344441001E-2</v>
-      </c>
-      <c r="CM4">
-        <v>3.5248597551501601E-2</v>
-      </c>
-      <c r="CN4">
-        <v>4.7440867689193499E-2</v>
-      </c>
-      <c r="CO4">
-        <v>4.5272290568620303E-2</v>
-      </c>
-      <c r="CP4">
-        <v>4.4700169263701899E-2</v>
-      </c>
-      <c r="CQ4">
-        <v>4.5862112361122899E-2</v>
-      </c>
-      <c r="CR4">
-        <v>4.6295006838834502E-2</v>
-      </c>
-      <c r="CS4">
-        <v>4.6661869518262497E-2</v>
-      </c>
-      <c r="CT4">
-        <v>5.1162511042495501E-2</v>
-      </c>
-      <c r="CU4">
-        <v>5.1206256995581102E-2</v>
-      </c>
-      <c r="CV4">
-        <v>5.22458466087126E-2</v>
-      </c>
-      <c r="CW4">
-        <v>5.2993164751275801E-2</v>
-      </c>
-      <c r="CX4">
-        <v>5.4330317695726701E-2</v>
-      </c>
-      <c r="CY4">
-        <v>5.4518420185621003E-2</v>
-      </c>
-      <c r="CZ4">
-        <v>5.4884280925977101E-2</v>
-      </c>
-      <c r="DA4">
-        <v>5.4946262241070902E-2</v>
-      </c>
-      <c r="DB4">
-        <v>5.4753284636206601E-2</v>
-      </c>
-      <c r="DC4">
-        <v>5.74397708700101E-2</v>
-      </c>
-      <c r="DD4">
-        <v>5.7600045264809101E-2</v>
-      </c>
-      <c r="DE4">
-        <v>5.9104844938269903E-2</v>
-      </c>
-      <c r="DF4">
-        <v>6.0352763001317401E-2</v>
-      </c>
-      <c r="DG4">
-        <v>5.7032979716764499E-2</v>
-      </c>
-      <c r="DH4">
-        <v>5.9115586262394097E-2</v>
-      </c>
-      <c r="DI4">
-        <v>6.2211888372299802E-2</v>
-      </c>
-      <c r="DJ4">
-        <v>6.5950645950459894E-2</v>
-      </c>
-      <c r="DK4">
-        <v>6.9936408884607296E-2</v>
-      </c>
-      <c r="DL4">
-        <v>7.4207036445033306E-2</v>
-      </c>
-      <c r="DM4">
-        <v>7.3901752066990303E-2</v>
-      </c>
-      <c r="DN4">
-        <v>6.0542018656423502E-2</v>
-      </c>
-      <c r="DO4">
-        <v>6.3537478642594805E-2</v>
-      </c>
-      <c r="DP4">
-        <v>6.5263803656607694E-2</v>
-      </c>
-      <c r="DQ4">
-        <v>6.3519151794554807E-2</v>
-      </c>
-      <c r="DR4">
-        <v>6.0147609914841499E-2</v>
-      </c>
-      <c r="DS4">
-        <v>5.7273590158637797E-2</v>
-      </c>
-      <c r="DT4">
-        <v>5.5915077354956003E-2</v>
-      </c>
-      <c r="DU4">
-        <v>5.3090557389420201E-2</v>
-      </c>
-      <c r="DV4">
-        <v>5.1350768849352697E-2</v>
-      </c>
-      <c r="DW4">
-        <v>5.0659412157130101E-2</v>
-      </c>
-      <c r="DX4">
-        <v>5.0610732365365903E-2</v>
-      </c>
-      <c r="DY4">
-        <v>5.1444258158445597E-2</v>
-      </c>
-      <c r="DZ4">
-        <v>5.0757677630835198E-2</v>
-      </c>
-      <c r="EA4">
-        <v>5.0324827649696799E-2</v>
-      </c>
-      <c r="EB4">
-        <v>4.9702618007044397E-2</v>
-      </c>
-      <c r="EC4">
-        <v>4.9758289777202702E-2</v>
-      </c>
-      <c r="ED4">
-        <v>5.0247426906602902E-2</v>
-      </c>
-      <c r="EE4">
-        <v>5.1103747098816397E-2</v>
-      </c>
-      <c r="EF4">
-        <v>5.2145269642816301E-2</v>
-      </c>
-      <c r="EG4">
-        <v>5.3770883094527398E-2</v>
-      </c>
-      <c r="EH4">
-        <v>5.4719456158344497E-2</v>
-      </c>
-      <c r="EI4">
-        <v>5.5017883954930603E-2</v>
-      </c>
-      <c r="EJ4">
-        <v>5.5417344754917698E-2</v>
-      </c>
-      <c r="EK4">
-        <v>5.56103735213671E-2</v>
-      </c>
-      <c r="EL4">
-        <v>5.58498946477997E-2</v>
-      </c>
-      <c r="EM4">
-        <v>5.7203412076248301E-2</v>
-      </c>
-      <c r="EN4">
-        <v>5.8909759250011101E-2</v>
-      </c>
-      <c r="EO4">
-        <v>5.9797754309220401E-2</v>
-      </c>
-      <c r="EP4">
-        <v>6.1064349709746897E-2</v>
-      </c>
-      <c r="EQ4">
-        <v>5.9198795852612701E-2</v>
-      </c>
-      <c r="ER4">
-        <v>6.2108974036249598E-2</v>
-      </c>
-      <c r="ES4">
-        <v>6.5513833758270995E-2</v>
-      </c>
-      <c r="ET4">
-        <v>6.8861854642519801E-2</v>
-      </c>
-      <c r="EU4">
-        <v>7.1949471115278302E-2</v>
-      </c>
-      <c r="EV4">
-        <v>7.53403503505293E-2</v>
-      </c>
-      <c r="EW4">
-        <v>8.08454184436284E-2</v>
-      </c>
-      <c r="EX4">
-        <v>8.59788399250936E-2</v>
-      </c>
-      <c r="EY4">
-        <v>8.7299558209175801E-2</v>
-      </c>
-      <c r="EZ4">
-        <v>9.3775696975812298E-2</v>
-      </c>
-      <c r="FA4">
-        <v>8.9194465184427293E-2</v>
-      </c>
-      <c r="FB4">
-        <v>9.4495310789964801E-2</v>
-      </c>
-      <c r="FC4">
-        <v>0.104411834484557</v>
-      </c>
-      <c r="FD4">
-        <v>9.4791242128523398E-2</v>
-      </c>
-      <c r="FE4">
-        <v>9.8114216272922494E-2</v>
-      </c>
-      <c r="FF4">
-        <v>9.4678869281640099E-2</v>
-      </c>
-      <c r="FG4">
-        <v>9.1426610682942805E-2</v>
-      </c>
-      <c r="FH4">
-        <v>8.3653628590679194E-2</v>
-      </c>
-      <c r="FI4">
-        <v>0.10531290756320801</v>
-      </c>
-      <c r="FJ4">
-        <v>9.3185371263594302E-2</v>
-      </c>
-      <c r="FK4">
-        <v>0.11612370664732</v>
-      </c>
-      <c r="FL4">
-        <v>9.9987099388920406E-2</v>
-      </c>
-      <c r="FM4">
-        <v>8.61728278591741E-2</v>
-      </c>
-      <c r="FN4">
-        <v>7.6178513355876498E-2</v>
-      </c>
-      <c r="FO4">
-        <v>7.1502388734832098E-2</v>
-      </c>
-      <c r="FP4">
-        <v>6.9230848337348994E-2</v>
-      </c>
-      <c r="FQ4">
-        <v>6.8044169980476604E-2</v>
-      </c>
-      <c r="FR4">
-        <v>6.7488528071252593E-2</v>
-      </c>
-      <c r="FS4">
-        <v>6.6758371301447697E-2</v>
-      </c>
-      <c r="FT4">
-        <v>6.6863516483176802E-2</v>
-      </c>
-      <c r="FU4">
-        <v>6.3866831677318298E-2</v>
-      </c>
-      <c r="FV4">
-        <v>6.0029369184474601E-2</v>
-      </c>
-      <c r="FW4">
-        <v>6.18775079000616E-2</v>
-      </c>
-      <c r="FX4">
-        <v>6.39766806966722E-2</v>
-      </c>
-      <c r="FY4">
-        <v>5.8160251226447503E-2</v>
-      </c>
-      <c r="FZ4">
-        <v>6.18562612847132E-2</v>
-      </c>
-      <c r="GA4">
-        <v>5.4140629199297803E-2</v>
-      </c>
-      <c r="GB4">
-        <v>5.6468059101163898E-2</v>
-      </c>
-      <c r="GC4">
-        <v>5.9318541397087601E-2</v>
-      </c>
-      <c r="GD4">
-        <v>5.36775297734325E-2</v>
-      </c>
-      <c r="GE4">
-        <v>5.6371475735520801E-2</v>
-      </c>
-      <c r="GF4">
-        <v>5.8975076629246601E-2</v>
-      </c>
-      <c r="GG4">
-        <v>5.2631296067113503E-2</v>
-      </c>
-      <c r="GH4">
-        <v>5.4196723857296299E-2</v>
-      </c>
-      <c r="GI4">
-        <v>5.5919992494332202E-2</v>
-      </c>
-      <c r="GJ4">
-        <v>5.6290785278771502E-2</v>
-      </c>
-      <c r="GK4">
-        <v>5.2320500975223602E-2</v>
-      </c>
-      <c r="GL4">
-        <v>4.7262307445240202E-2</v>
-      </c>
-      <c r="GM4">
-        <v>7.3983658377475503E-2</v>
-      </c>
-      <c r="GN4">
-        <v>6.2447259160555699E-2</v>
-      </c>
-      <c r="GO4">
-        <v>9.7628222579004303E-2</v>
-      </c>
-      <c r="GP4">
-        <v>7.7363641049164794E-2</v>
-      </c>
-      <c r="GQ4">
-        <v>6.4693954031650402E-2</v>
-      </c>
-      <c r="GR4">
-        <v>5.8781051844230298E-2</v>
-      </c>
-      <c r="GS4">
-        <v>6.5828914058748203E-2</v>
-      </c>
-      <c r="GT4">
-        <v>6.5335578666708694E-2</v>
-      </c>
-      <c r="GU4">
-        <v>7.8035365727512102E-2</v>
-      </c>
-      <c r="GV4">
-        <v>6.6662411402037297E-2</v>
-      </c>
-      <c r="GW4">
-        <v>6.0580344316473397E-2</v>
-      </c>
-      <c r="GX4">
-        <v>7.6531470354456996E-2</v>
-      </c>
-      <c r="GY4">
-        <v>6.9672150876045294E-2</v>
-      </c>
-      <c r="GZ4">
-        <v>6.2699166553278604E-2</v>
-      </c>
-      <c r="HA4">
-        <v>6.8974946339366905E-2</v>
-      </c>
-      <c r="HB4">
-        <v>6.2679717757086001E-2</v>
-      </c>
-      <c r="HC4">
-        <v>5.7510604685762003E-2</v>
-      </c>
-      <c r="HD4">
-        <v>5.7190685181975003E-2</v>
-      </c>
-      <c r="HE4">
-        <v>5.4268000614563099E-2</v>
-      </c>
-      <c r="HF4">
-        <v>5.1578330300977797E-2</v>
-      </c>
-      <c r="HG4">
-        <v>5.2674362324404499E-2</v>
-      </c>
-      <c r="HH4">
-        <v>5.2006722275782603E-2</v>
-      </c>
-      <c r="HI4">
-        <v>5.1624948976845997E-2</v>
-      </c>
-      <c r="HJ4">
-        <v>5.1767427964415198E-2</v>
-      </c>
-      <c r="HK4">
-        <v>5.60785298596123E-2</v>
-      </c>
-      <c r="HL4">
-        <v>5.5795890990211802E-2</v>
-      </c>
-      <c r="HM4">
-        <v>5.4872882923649398E-2</v>
-      </c>
-      <c r="HN4">
-        <v>5.9117786460897902E-2</v>
-      </c>
-      <c r="HO4">
-        <v>5.9716167921888101E-2</v>
-      </c>
-      <c r="HP4">
-        <v>5.85954242410422E-2</v>
-      </c>
-      <c r="HQ4">
-        <v>5.7644256693045598E-2</v>
-      </c>
-      <c r="HR4">
-        <v>5.78916053560369E-2</v>
-      </c>
-      <c r="HS4">
-        <v>5.7165868230251403E-2</v>
-      </c>
-      <c r="HT4">
-        <v>5.6704732346240801E-2</v>
-      </c>
-      <c r="HU4">
-        <v>5.7449870658622899E-2</v>
-      </c>
-      <c r="HV4">
-        <v>5.6774670062228999E-2</v>
-      </c>
-      <c r="HW4">
-        <v>5.79960509179792E-2</v>
-      </c>
-      <c r="HX4">
-        <v>5.9338917508863998E-2</v>
-      </c>
-      <c r="HY4">
-        <v>5.9669728465723798E-2</v>
-      </c>
-      <c r="HZ4">
-        <v>6.0478868239432597E-2</v>
-      </c>
-      <c r="IA4">
-        <v>6.1941215013092098E-2</v>
-      </c>
-      <c r="IB4">
-        <v>6.4615945987091999E-2</v>
-      </c>
-      <c r="IC4">
-        <v>6.7738069637886894E-2</v>
-      </c>
-      <c r="ID4">
-        <v>6.6858937849569602E-2</v>
-      </c>
-      <c r="IE4">
-        <v>4.9464089255749799E-2</v>
-      </c>
-      <c r="IF4">
-        <v>6.1382644599150098E-2</v>
-      </c>
-      <c r="IG4">
-        <v>5.89481240892984E-2</v>
-      </c>
-      <c r="IH4">
-        <v>6.3820946637806006E-2</v>
-      </c>
-      <c r="II4">
-        <v>5.9909522106386497E-2</v>
-      </c>
-      <c r="IJ4">
-        <v>5.6076226347152397E-2</v>
-      </c>
-      <c r="IK4">
-        <v>5.1125606073112097E-2</v>
-      </c>
-      <c r="IL4">
-        <v>4.6887550977966701E-2</v>
-      </c>
-      <c r="IM4">
-        <v>4.9077492573730702E-2</v>
-      </c>
-      <c r="IN4">
-        <v>4.6919776796243998E-2</v>
-      </c>
-      <c r="IO4">
-        <v>4.9297560202466201E-2</v>
-      </c>
-      <c r="IP4">
-        <v>5.1529436095545701E-2</v>
-      </c>
-      <c r="IQ4">
-        <v>5.3887267504804499E-2</v>
-      </c>
-      <c r="IR4">
-        <v>5.7003359885135003E-2</v>
-      </c>
-      <c r="IS4">
-        <v>6.0504264136058902E-2</v>
-      </c>
-      <c r="IT4">
-        <v>5.4037773265895997E-2</v>
-      </c>
-      <c r="IU4">
-        <v>5.7067998103141802E-2</v>
-      </c>
-      <c r="IV4">
-        <v>6.0485458313519397E-2</v>
-      </c>
-      <c r="IW4">
-        <v>6.2140414921322898E-2</v>
-      </c>
-      <c r="IX4">
-        <v>6.2187389883091103E-2</v>
-      </c>
-      <c r="IY4">
-        <v>6.44674364999855E-2</v>
-      </c>
-      <c r="IZ4">
-        <v>6.7016315196676196E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:260" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>6.8916963130112897E-3</v>
-      </c>
-      <c r="B5">
-        <v>6.6947777537752296E-3</v>
-      </c>
-      <c r="C5">
-        <v>6.5694239528873398E-3</v>
-      </c>
-      <c r="D5">
-        <v>6.5066556469104897E-3</v>
-      </c>
-      <c r="E5">
-        <v>6.4968667874356302E-3</v>
-      </c>
-      <c r="F5">
-        <v>6.5225950092097501E-3</v>
-      </c>
-      <c r="G5">
-        <v>6.5426726953727501E-3</v>
-      </c>
-      <c r="H5">
-        <v>6.5700215474277096E-3</v>
-      </c>
-      <c r="I5">
-        <v>6.5627057647427598E-3</v>
-      </c>
-      <c r="J5">
-        <v>6.5561326845388398E-3</v>
-      </c>
-      <c r="K5">
-        <v>6.5530386207786704E-3</v>
-      </c>
-      <c r="L5">
-        <v>6.6002263600015102E-3</v>
-      </c>
-      <c r="M5">
-        <v>6.6248256577846098E-3</v>
-      </c>
-      <c r="N5">
-        <v>6.6965525752535303E-3</v>
-      </c>
-      <c r="O5">
-        <v>6.7654419200132796E-3</v>
-      </c>
-      <c r="P5">
-        <v>6.8558470713087202E-3</v>
-      </c>
-      <c r="Q5">
-        <v>6.9014328750802599E-3</v>
-      </c>
-      <c r="R5">
-        <v>7.02567040634556E-3</v>
-      </c>
-      <c r="S5">
-        <v>7.1554512661601097E-3</v>
-      </c>
-      <c r="T5">
-        <v>7.3605468688944303E-3</v>
-      </c>
-      <c r="U5">
-        <v>7.6753437563969497E-3</v>
-      </c>
-      <c r="V5">
-        <v>3.3878969012888999E-3</v>
-      </c>
-      <c r="W5">
-        <v>3.2595629017259701E-3</v>
-      </c>
-      <c r="X5">
-        <v>3.38397702251246E-3</v>
-      </c>
-      <c r="Y5">
-        <v>3.5203662386050702E-3</v>
-      </c>
-      <c r="Z5">
-        <v>3.6649091419942402E-3</v>
-      </c>
-      <c r="AA5">
-        <v>3.8137665707370801E-3</v>
-      </c>
-      <c r="AB5">
-        <v>3.61762218469969E-3</v>
-      </c>
-      <c r="AC5">
-        <v>3.7601863980357602E-3</v>
-      </c>
-      <c r="AD5">
-        <v>3.8645771998949601E-3</v>
-      </c>
-      <c r="AE5">
-        <v>4.02658610305116E-3</v>
-      </c>
-      <c r="AF5">
-        <v>4.1951182529578598E-3</v>
-      </c>
-      <c r="AG5">
-        <v>4.3641382991944999E-3</v>
-      </c>
-      <c r="AH5">
-        <v>4.5443902296030099E-3</v>
-      </c>
-      <c r="AI5">
-        <v>4.6800476898814199E-3</v>
-      </c>
-      <c r="AJ5">
-        <v>4.8484236863751496E-3</v>
-      </c>
-      <c r="AK5">
-        <v>4.9913731998443402E-3</v>
-      </c>
-      <c r="AL5">
-        <v>5.1095167867456596E-3</v>
-      </c>
-      <c r="AM5">
-        <v>5.2068339353799099E-3</v>
-      </c>
-      <c r="AN5">
-        <v>5.3012366114810298E-3</v>
-      </c>
-      <c r="AO5">
-        <v>6.6163053660651403E-3</v>
-      </c>
-      <c r="AP5">
-        <v>6.6157376688616197E-3</v>
-      </c>
-      <c r="AQ5">
-        <v>6.60240553156857E-3</v>
-      </c>
-      <c r="AR5">
-        <v>6.5917042766932103E-3</v>
-      </c>
-      <c r="AS5">
-        <v>6.5548862086808402E-3</v>
-      </c>
-      <c r="AT5">
-        <v>6.7512600190665004E-3</v>
-      </c>
-      <c r="AU5">
-        <v>6.8289268791818201E-3</v>
-      </c>
-      <c r="AV5">
-        <v>6.9114204533514299E-3</v>
-      </c>
-      <c r="AW5">
-        <v>7.0423833708673899E-3</v>
-      </c>
-      <c r="AX5">
-        <v>7.2823979115947098E-3</v>
-      </c>
-      <c r="AY5">
-        <v>4.1085739292283704E-3</v>
-      </c>
-      <c r="AZ5">
-        <v>3.8496027979110698E-3</v>
-      </c>
-      <c r="BA5">
-        <v>3.9889976002494302E-3</v>
-      </c>
-      <c r="BB5">
-        <v>3.9896399024624404E-3</v>
-      </c>
-      <c r="BC5">
-        <v>4.0741069654731303E-3</v>
-      </c>
-      <c r="BD5">
-        <v>4.4397006912700104E-3</v>
-      </c>
-      <c r="BE5">
-        <v>4.84747507448765E-3</v>
-      </c>
-      <c r="BF5">
-        <v>4.8750801398462903E-3</v>
-      </c>
-      <c r="BG5">
-        <v>4.9005974395379698E-3</v>
-      </c>
-      <c r="BH5">
-        <v>4.9436325377063698E-3</v>
-      </c>
-      <c r="BI5">
-        <v>4.99556146900265E-3</v>
-      </c>
-      <c r="BJ5">
-        <v>5.0720097223669498E-3</v>
-      </c>
-      <c r="BK5">
-        <v>5.1433536379995497E-3</v>
-      </c>
-      <c r="BL5">
-        <v>5.3905966231776901E-3</v>
-      </c>
-      <c r="BM5">
-        <v>5.4278130961179904E-3</v>
-      </c>
-      <c r="BN5">
-        <v>5.47186998612504E-3</v>
-      </c>
-      <c r="BO5">
-        <v>5.5437210734401001E-3</v>
-      </c>
-      <c r="BP5">
-        <v>5.6387311145832597E-3</v>
-      </c>
-      <c r="BQ5">
-        <v>5.7035442762964602E-3</v>
-      </c>
-      <c r="BR5">
-        <v>5.7465364452699398E-3</v>
-      </c>
-      <c r="BS5">
-        <v>5.8438193295668097E-3</v>
-      </c>
-      <c r="BT5">
-        <v>5.9780810223228498E-3</v>
-      </c>
-      <c r="BU5">
-        <v>6.1291152706115801E-3</v>
-      </c>
-      <c r="BV5">
-        <v>6.2493912931263001E-3</v>
-      </c>
-      <c r="BW5">
-        <v>5.6982523781464603E-3</v>
-      </c>
-      <c r="BX5">
-        <v>5.8041137598672399E-3</v>
-      </c>
-      <c r="BY5">
-        <v>5.8680249048631604E-3</v>
-      </c>
-      <c r="BZ5">
-        <v>5.95748293297255E-3</v>
-      </c>
-      <c r="CA5">
-        <v>5.9238175615437703E-3</v>
-      </c>
-      <c r="CB5">
-        <v>5.8783244886145601E-3</v>
-      </c>
-      <c r="CC5">
-        <v>5.92098989299645E-3</v>
-      </c>
-      <c r="CD5">
-        <v>5.9665083816388097E-3</v>
-      </c>
-      <c r="CE5">
-        <v>5.9625926738349003E-3</v>
-      </c>
-      <c r="CF5">
-        <v>5.9776112015365902E-3</v>
-      </c>
-      <c r="CG5">
-        <v>5.9322643465869298E-3</v>
-      </c>
-      <c r="CH5">
-        <v>5.8222307894452603E-3</v>
-      </c>
-      <c r="CI5">
-        <v>5.7211906095809301E-3</v>
-      </c>
-      <c r="CJ5">
-        <v>5.6099111027540297E-3</v>
-      </c>
-      <c r="CK5">
-        <v>5.48557531298323E-3</v>
-      </c>
-      <c r="CL5">
-        <v>5.4032774332702796E-3</v>
-      </c>
-      <c r="CM5">
-        <v>5.3723610481731902E-3</v>
-      </c>
-      <c r="CN5">
-        <v>5.8812911797139298E-3</v>
-      </c>
-      <c r="CO5">
-        <v>5.8536008698783096E-3</v>
-      </c>
-      <c r="CP5">
-        <v>5.8660316263044604E-3</v>
-      </c>
-      <c r="CQ5">
-        <v>5.9058227228564698E-3</v>
-      </c>
-      <c r="CR5">
-        <v>5.9462055001702997E-3</v>
-      </c>
-      <c r="CS5">
-        <v>5.9822658705446499E-3</v>
-      </c>
-      <c r="CT5">
-        <v>6.5838542351717797E-3</v>
-      </c>
-      <c r="CU5">
-        <v>6.57244175333495E-3</v>
-      </c>
-      <c r="CV5">
-        <v>6.5924711382335296E-3</v>
-      </c>
-      <c r="CW5">
-        <v>6.60607526680032E-3</v>
-      </c>
-      <c r="CX5">
-        <v>6.6271335569997704E-3</v>
-      </c>
-      <c r="CY5">
-        <v>6.6243438117165303E-3</v>
-      </c>
-      <c r="CZ5">
-        <v>6.6280596111742704E-3</v>
-      </c>
-      <c r="DA5">
-        <v>6.6180999417636702E-3</v>
-      </c>
-      <c r="DB5">
-        <v>6.6060839998976599E-3</v>
-      </c>
-      <c r="DC5">
-        <v>6.6378114861880702E-3</v>
-      </c>
-      <c r="DD5">
-        <v>6.6414164788397602E-3</v>
-      </c>
-      <c r="DE5">
-        <v>6.6908009396044197E-3</v>
-      </c>
-      <c r="DF5">
-        <v>6.7251096470685098E-3</v>
-      </c>
-      <c r="DG5">
-        <v>6.7551011235133301E-3</v>
-      </c>
-      <c r="DH5">
-        <v>6.8056596741560898E-3</v>
-      </c>
-      <c r="DI5">
-        <v>6.8858451987859502E-3</v>
-      </c>
-      <c r="DJ5">
-        <v>6.9800583056178903E-3</v>
-      </c>
-      <c r="DK5">
-        <v>7.0749550743524096E-3</v>
-      </c>
-      <c r="DL5">
-        <v>7.1691164270506601E-3</v>
-      </c>
-      <c r="DM5">
-        <v>7.2286095671607502E-3</v>
-      </c>
-      <c r="DN5">
-        <v>7.0448381918799697E-3</v>
-      </c>
-      <c r="DO5">
-        <v>7.1080125639987803E-3</v>
-      </c>
-      <c r="DP5">
-        <v>7.1326868359638798E-3</v>
-      </c>
-      <c r="DQ5">
-        <v>7.0606213757404201E-3</v>
-      </c>
-      <c r="DR5">
-        <v>6.9321652231977698E-3</v>
-      </c>
-      <c r="DS5">
-        <v>6.8310578681641297E-3</v>
-      </c>
-      <c r="DT5">
-        <v>6.7347364024947501E-3</v>
-      </c>
-      <c r="DU5">
-        <v>6.6402608067294101E-3</v>
-      </c>
-      <c r="DV5">
-        <v>6.5812392906639096E-3</v>
-      </c>
-      <c r="DW5">
-        <v>6.5479752914298396E-3</v>
-      </c>
-      <c r="DX5">
-        <v>6.5315685751099004E-3</v>
-      </c>
-      <c r="DY5">
-        <v>6.5318662338613E-3</v>
-      </c>
-      <c r="DZ5">
-        <v>6.5101796456222003E-3</v>
-      </c>
-      <c r="EA5">
-        <v>6.4858570639964204E-3</v>
-      </c>
-      <c r="EB5">
-        <v>6.4560346966607302E-3</v>
-      </c>
-      <c r="EC5">
-        <v>6.4552128800539404E-3</v>
-      </c>
-      <c r="ED5">
-        <v>6.46505625420387E-3</v>
-      </c>
-      <c r="EE5">
-        <v>6.4986057698537799E-3</v>
-      </c>
-      <c r="EF5">
-        <v>6.5264428833745102E-3</v>
-      </c>
-      <c r="EG5">
-        <v>6.5708346795631898E-3</v>
-      </c>
-      <c r="EH5">
-        <v>6.5955948608045099E-3</v>
-      </c>
-      <c r="EI5">
-        <v>6.5985257773488798E-3</v>
-      </c>
-      <c r="EJ5">
-        <v>6.6067709828188104E-3</v>
-      </c>
-      <c r="EK5">
-        <v>6.6111997519228303E-3</v>
-      </c>
-      <c r="EL5">
-        <v>6.61497998410267E-3</v>
-      </c>
-      <c r="EM5">
-        <v>6.6592973758628398E-3</v>
-      </c>
-      <c r="EN5">
-        <v>6.7036152959391001E-3</v>
-      </c>
-      <c r="EO5">
-        <v>6.7536820592526301E-3</v>
-      </c>
-      <c r="EP5">
-        <v>6.7864067649577196E-3</v>
-      </c>
-      <c r="EQ5">
-        <v>6.8539653940708099E-3</v>
-      </c>
-      <c r="ER5">
-        <v>6.9331334168228802E-3</v>
-      </c>
-      <c r="ES5">
-        <v>7.0007595164819801E-3</v>
-      </c>
-      <c r="ET5">
-        <v>7.0659532877307904E-3</v>
-      </c>
-      <c r="EU5">
-        <v>7.1222698309908704E-3</v>
-      </c>
-      <c r="EV5">
-        <v>7.1909153674351396E-3</v>
-      </c>
-      <c r="EW5">
-        <v>7.29664546463492E-3</v>
-      </c>
-      <c r="EX5">
-        <v>7.3924671028587803E-3</v>
-      </c>
-      <c r="EY5">
-        <v>7.4685980682736202E-3</v>
-      </c>
-      <c r="EZ5">
-        <v>7.5643173785952802E-3</v>
-      </c>
-      <c r="FA5">
-        <v>7.7108459642696199E-3</v>
-      </c>
-      <c r="FB5">
-        <v>7.7870456348018199E-3</v>
-      </c>
-      <c r="FC5">
-        <v>7.9378180328899609E-3</v>
-      </c>
-      <c r="FD5">
-        <v>8.0046580816271404E-3</v>
-      </c>
-      <c r="FE5">
-        <v>8.0288845255704101E-3</v>
-      </c>
-      <c r="FF5">
-        <v>7.9299793338878394E-3</v>
-      </c>
-      <c r="FG5">
-        <v>7.8263949945210007E-3</v>
-      </c>
-      <c r="FH5">
-        <v>7.6320589006028203E-3</v>
-      </c>
-      <c r="FI5">
-        <v>8.1928450717959206E-3</v>
-      </c>
-      <c r="FJ5">
-        <v>7.9192214004272996E-3</v>
-      </c>
-      <c r="FK5">
-        <v>8.4745317726981993E-3</v>
-      </c>
-      <c r="FL5">
-        <v>8.1316963262731898E-3</v>
-      </c>
-      <c r="FM5">
-        <v>7.80785513217447E-3</v>
-      </c>
-      <c r="FN5">
-        <v>7.5401922309553298E-3</v>
-      </c>
-      <c r="FO5">
-        <v>7.3412429232699401E-3</v>
-      </c>
-      <c r="FP5">
-        <v>7.2429471371094302E-3</v>
-      </c>
-      <c r="FQ5">
-        <v>7.1915695563063197E-3</v>
-      </c>
-      <c r="FR5">
-        <v>7.1415175106323697E-3</v>
-      </c>
-      <c r="FS5">
-        <v>7.1051198602951303E-3</v>
-      </c>
-      <c r="FT5">
-        <v>7.0904855162907798E-3</v>
-      </c>
-      <c r="FU5">
-        <v>7.0165214157688503E-3</v>
-      </c>
-      <c r="FV5">
-        <v>7.0253018523493901E-3</v>
-      </c>
-      <c r="FW5">
-        <v>7.0570517385419498E-3</v>
-      </c>
-      <c r="FX5">
-        <v>7.0970926568076197E-3</v>
-      </c>
-      <c r="FY5">
-        <v>6.4942754447436298E-3</v>
-      </c>
-      <c r="FZ5">
-        <v>6.5988839751244602E-3</v>
-      </c>
-      <c r="GA5">
-        <v>6.4049956780651398E-3</v>
-      </c>
-      <c r="GB5">
-        <v>6.4802258212495302E-3</v>
-      </c>
-      <c r="GC5">
-        <v>6.5675147555739402E-3</v>
-      </c>
-      <c r="GD5">
-        <v>6.2894004704763598E-3</v>
-      </c>
-      <c r="GE5">
-        <v>6.37939484664477E-3</v>
-      </c>
-      <c r="GF5">
-        <v>6.4691239016216604E-3</v>
-      </c>
-      <c r="GG5">
-        <v>6.4194673602626503E-3</v>
-      </c>
-      <c r="GH5">
-        <v>6.47163383358148E-3</v>
-      </c>
-      <c r="GI5">
-        <v>6.5258876006490602E-3</v>
-      </c>
-      <c r="GJ5">
-        <v>6.5329805686459401E-3</v>
-      </c>
-      <c r="GK5">
-        <v>6.4270676794106396E-3</v>
-      </c>
-      <c r="GL5">
-        <v>6.2763638693070804E-3</v>
-      </c>
-      <c r="GM5">
-        <v>8.1415055031422209E-3</v>
-      </c>
-      <c r="GN5">
-        <v>7.60938406488004E-3</v>
-      </c>
-      <c r="GO5">
-        <v>8.0505724570653307E-3</v>
-      </c>
-      <c r="GP5">
-        <v>7.5786232613763403E-3</v>
-      </c>
-      <c r="GQ5">
-        <v>7.2639281117270098E-3</v>
-      </c>
-      <c r="GR5">
-        <v>7.0432357668316799E-3</v>
-      </c>
-      <c r="GS5">
-        <v>6.8695167217370304E-3</v>
-      </c>
-      <c r="GT5">
-        <v>6.6795451268817502E-3</v>
-      </c>
-      <c r="GU5">
-        <v>6.5578087468424404E-3</v>
-      </c>
-      <c r="GV5">
-        <v>6.4046566822221701E-3</v>
-      </c>
-      <c r="GW5">
-        <v>6.3083984714381799E-3</v>
-      </c>
-      <c r="GX5">
-        <v>6.4632069218761501E-3</v>
-      </c>
-      <c r="GY5">
-        <v>6.3703248682300201E-3</v>
-      </c>
-      <c r="GZ5">
-        <v>6.2794504294704902E-3</v>
-      </c>
-      <c r="HA5">
-        <v>6.19108798728035E-3</v>
-      </c>
-      <c r="HB5">
-        <v>6.1310373204186402E-3</v>
-      </c>
-      <c r="HC5">
-        <v>6.0747386750138197E-3</v>
-      </c>
-      <c r="HD5">
-        <v>6.0432392777578199E-3</v>
-      </c>
-      <c r="HE5">
-        <v>6.0314503427356496E-3</v>
-      </c>
-      <c r="HF5">
-        <v>5.9949401039264202E-3</v>
-      </c>
-      <c r="HG5">
-        <v>5.9901209258705701E-3</v>
-      </c>
-      <c r="HH5">
-        <v>6.0118269239058299E-3</v>
-      </c>
-      <c r="HI5">
-        <v>6.0322264563871303E-3</v>
-      </c>
-      <c r="HJ5">
-        <v>6.0649623061074902E-3</v>
-      </c>
-      <c r="HK5">
-        <v>6.2425754572881798E-3</v>
-      </c>
-      <c r="HL5">
-        <v>6.2580462536031703E-3</v>
-      </c>
-      <c r="HM5">
-        <v>6.2588737535790003E-3</v>
-      </c>
-      <c r="HN5">
-        <v>6.2810295374687202E-3</v>
-      </c>
-      <c r="HO5">
-        <v>6.2734041968153598E-3</v>
-      </c>
-      <c r="HP5">
-        <v>6.2755548785450701E-3</v>
-      </c>
-      <c r="HQ5">
-        <v>6.2797873803735098E-3</v>
-      </c>
-      <c r="HR5">
-        <v>6.28310369124741E-3</v>
-      </c>
-      <c r="HS5">
-        <v>6.2893732773660104E-3</v>
-      </c>
-      <c r="HT5">
-        <v>6.3071404813470197E-3</v>
-      </c>
-      <c r="HU5">
-        <v>6.3499017835324896E-3</v>
-      </c>
-      <c r="HV5">
-        <v>6.3869391844239903E-3</v>
-      </c>
-      <c r="HW5">
-        <v>6.4384321493038202E-3</v>
-      </c>
-      <c r="HX5">
-        <v>6.4916113430644601E-3</v>
-      </c>
-      <c r="HY5">
-        <v>6.5218293459596401E-3</v>
-      </c>
-      <c r="HZ5">
-        <v>6.5565143179210101E-3</v>
-      </c>
-      <c r="IA5">
-        <v>6.6034310897541198E-3</v>
-      </c>
-      <c r="IB5">
-        <v>6.6795526372382397E-3</v>
-      </c>
-      <c r="IC5">
-        <v>6.7614725974346201E-3</v>
-      </c>
-      <c r="ID5">
-        <v>6.7410969877561098E-3</v>
-      </c>
-      <c r="IE5">
-        <v>6.3102392388619203E-3</v>
-      </c>
-      <c r="IF5">
-        <v>8.4474307848104307E-3</v>
-      </c>
-      <c r="IG5">
-        <v>8.1742869736347607E-3</v>
-      </c>
-      <c r="IH5">
-        <v>9.1738114242806094E-3</v>
-      </c>
-      <c r="II5">
-        <v>7.8596439093180093E-3</v>
-      </c>
-      <c r="IJ5">
-        <v>7.7530150532886003E-3</v>
-      </c>
-      <c r="IK5">
-        <v>7.7912043799653096E-3</v>
-      </c>
-      <c r="IL5">
-        <v>7.4734711807585398E-3</v>
-      </c>
-      <c r="IM5">
-        <v>7.4680745341900601E-3</v>
-      </c>
-      <c r="IN5">
-        <v>7.3237803369725898E-3</v>
-      </c>
-      <c r="IO5">
-        <v>7.3375777087661296E-3</v>
-      </c>
-      <c r="IP5">
-        <v>7.3560759100139098E-3</v>
-      </c>
-      <c r="IQ5">
-        <v>7.3718892038574799E-3</v>
-      </c>
-      <c r="IR5">
-        <v>7.41700180440962E-3</v>
-      </c>
-      <c r="IS5">
-        <v>7.4722176514185699E-3</v>
-      </c>
-      <c r="IT5">
-        <v>6.2093975197165798E-3</v>
-      </c>
-      <c r="IU5">
-        <v>6.3108978888065598E-3</v>
-      </c>
-      <c r="IV5">
-        <v>6.4164393752811398E-3</v>
-      </c>
-      <c r="IW5">
-        <v>6.5141811082534704E-3</v>
-      </c>
-      <c r="IX5">
-        <v>6.5703619384055202E-3</v>
-      </c>
-      <c r="IY5">
-        <v>6.64055047308561E-3</v>
-      </c>
-      <c r="IZ5">
-        <v>6.7345555746429102E-3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8D75A12-56FE-494F-95BC-F47763DA8D7F}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
